--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,102 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>['43', '57', '71']</t>
+  </si>
+  <si>
+    <t>['4']</t>
+  </si>
+  <si>
+    <t>['3', '45+3']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['33', '50']</t>
+  </si>
+  <si>
+    <t>['5', '25']</t>
+  </si>
+  <si>
+    <t>['2', '9']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['45', '66', '72']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['11', '43']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +366,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +875,1448 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7785801</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q2">
+        <v>2.4</v>
+      </c>
+      <c r="R2">
+        <v>2.38</v>
+      </c>
+      <c r="S2">
+        <v>4</v>
+      </c>
+      <c r="T2">
+        <v>1.3</v>
+      </c>
+      <c r="U2">
+        <v>3.4</v>
+      </c>
+      <c r="V2">
+        <v>2.38</v>
+      </c>
+      <c r="W2">
+        <v>1.53</v>
+      </c>
+      <c r="X2">
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <v>1.13</v>
+      </c>
+      <c r="Z2">
+        <v>1.78</v>
+      </c>
+      <c r="AA2">
+        <v>3.91</v>
+      </c>
+      <c r="AB2">
+        <v>3.95</v>
+      </c>
+      <c r="AC2">
+        <v>1.01</v>
+      </c>
+      <c r="AD2">
+        <v>11</v>
+      </c>
+      <c r="AE2">
+        <v>1.15</v>
+      </c>
+      <c r="AF2">
+        <v>4.25</v>
+      </c>
+      <c r="AG2">
+        <v>1.55</v>
+      </c>
+      <c r="AH2">
+        <v>2.2</v>
+      </c>
+      <c r="AI2">
+        <v>1.57</v>
+      </c>
+      <c r="AJ2">
+        <v>2.25</v>
+      </c>
+      <c r="AK2">
+        <v>1.25</v>
+      </c>
+      <c r="AL2">
+        <v>1.25</v>
+      </c>
+      <c r="AM2">
+        <v>1.85</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>10</v>
+      </c>
+      <c r="AV2">
+        <v>4</v>
+      </c>
+      <c r="AW2">
+        <v>4</v>
+      </c>
+      <c r="AX2">
+        <v>6</v>
+      </c>
+      <c r="AY2">
+        <v>14</v>
+      </c>
+      <c r="AZ2">
+        <v>10</v>
+      </c>
+      <c r="BA2">
+        <v>4</v>
+      </c>
+      <c r="BB2">
+        <v>4</v>
+      </c>
+      <c r="BC2">
+        <v>8</v>
+      </c>
+      <c r="BD2">
+        <v>1.69</v>
+      </c>
+      <c r="BE2">
+        <v>8.5</v>
+      </c>
+      <c r="BF2">
+        <v>2.62</v>
+      </c>
+      <c r="BG2">
+        <v>1.12</v>
+      </c>
+      <c r="BH2">
+        <v>4.95</v>
+      </c>
+      <c r="BI2">
+        <v>1.24</v>
+      </c>
+      <c r="BJ2">
+        <v>3.45</v>
+      </c>
+      <c r="BK2">
+        <v>1.45</v>
+      </c>
+      <c r="BL2">
+        <v>2.55</v>
+      </c>
+      <c r="BM2">
+        <v>1.74</v>
+      </c>
+      <c r="BN2">
+        <v>2.02</v>
+      </c>
+      <c r="BO2">
+        <v>2.16</v>
+      </c>
+      <c r="BP2">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7785802</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3">
+        <v>2.25</v>
+      </c>
+      <c r="R3">
+        <v>2.38</v>
+      </c>
+      <c r="S3">
+        <v>4.75</v>
+      </c>
+      <c r="T3">
+        <v>1.3</v>
+      </c>
+      <c r="U3">
+        <v>3.4</v>
+      </c>
+      <c r="V3">
+        <v>2.5</v>
+      </c>
+      <c r="W3">
+        <v>1.5</v>
+      </c>
+      <c r="X3">
+        <v>6</v>
+      </c>
+      <c r="Y3">
+        <v>1.13</v>
+      </c>
+      <c r="Z3">
+        <v>1.67</v>
+      </c>
+      <c r="AA3">
+        <v>4</v>
+      </c>
+      <c r="AB3">
+        <v>4.5</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>11</v>
+      </c>
+      <c r="AE3">
+        <v>1.15</v>
+      </c>
+      <c r="AF3">
+        <v>4.25</v>
+      </c>
+      <c r="AG3">
+        <v>1.6</v>
+      </c>
+      <c r="AH3">
+        <v>2.1</v>
+      </c>
+      <c r="AI3">
+        <v>1.62</v>
+      </c>
+      <c r="AJ3">
+        <v>2.2</v>
+      </c>
+      <c r="AK3">
+        <v>1.2</v>
+      </c>
+      <c r="AL3">
+        <v>1.25</v>
+      </c>
+      <c r="AM3">
+        <v>2.1</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>6</v>
+      </c>
+      <c r="AV3">
+        <v>5</v>
+      </c>
+      <c r="AW3">
+        <v>13</v>
+      </c>
+      <c r="AX3">
+        <v>5</v>
+      </c>
+      <c r="AY3">
+        <v>19</v>
+      </c>
+      <c r="AZ3">
+        <v>10</v>
+      </c>
+      <c r="BA3">
+        <v>11</v>
+      </c>
+      <c r="BB3">
+        <v>4</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>1.46</v>
+      </c>
+      <c r="BE3">
+        <v>8.9</v>
+      </c>
+      <c r="BF3">
+        <v>3.32</v>
+      </c>
+      <c r="BG3">
+        <v>1.15</v>
+      </c>
+      <c r="BH3">
+        <v>4.45</v>
+      </c>
+      <c r="BI3">
+        <v>1.29</v>
+      </c>
+      <c r="BJ3">
+        <v>3.12</v>
+      </c>
+      <c r="BK3">
+        <v>1.53</v>
+      </c>
+      <c r="BL3">
+        <v>2.34</v>
+      </c>
+      <c r="BM3">
+        <v>1.87</v>
+      </c>
+      <c r="BN3">
+        <v>1.87</v>
+      </c>
+      <c r="BO3">
+        <v>2.35</v>
+      </c>
+      <c r="BP3">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7785803</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q4">
+        <v>2.1</v>
+      </c>
+      <c r="R4">
+        <v>2.4</v>
+      </c>
+      <c r="S4">
+        <v>5.5</v>
+      </c>
+      <c r="T4">
+        <v>1.33</v>
+      </c>
+      <c r="U4">
+        <v>3.25</v>
+      </c>
+      <c r="V4">
+        <v>2.5</v>
+      </c>
+      <c r="W4">
+        <v>1.5</v>
+      </c>
+      <c r="X4">
+        <v>6</v>
+      </c>
+      <c r="Y4">
+        <v>1.13</v>
+      </c>
+      <c r="Z4">
+        <v>1.55</v>
+      </c>
+      <c r="AA4">
+        <v>4.2</v>
+      </c>
+      <c r="AB4">
+        <v>5.4</v>
+      </c>
+      <c r="AC4">
+        <v>1.01</v>
+      </c>
+      <c r="AD4">
+        <v>11</v>
+      </c>
+      <c r="AE4">
+        <v>1.16</v>
+      </c>
+      <c r="AF4">
+        <v>4.1</v>
+      </c>
+      <c r="AG4">
+        <v>1.65</v>
+      </c>
+      <c r="AH4">
+        <v>2.11</v>
+      </c>
+      <c r="AI4">
+        <v>1.73</v>
+      </c>
+      <c r="AJ4">
+        <v>2</v>
+      </c>
+      <c r="AK4">
+        <v>1.17</v>
+      </c>
+      <c r="AL4">
+        <v>1.22</v>
+      </c>
+      <c r="AM4">
+        <v>2.3</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>5</v>
+      </c>
+      <c r="AW4">
+        <v>6</v>
+      </c>
+      <c r="AX4">
+        <v>1</v>
+      </c>
+      <c r="AY4">
+        <v>13</v>
+      </c>
+      <c r="AZ4">
+        <v>6</v>
+      </c>
+      <c r="BA4">
+        <v>6</v>
+      </c>
+      <c r="BB4">
+        <v>5</v>
+      </c>
+      <c r="BC4">
+        <v>11</v>
+      </c>
+      <c r="BD4">
+        <v>1.57</v>
+      </c>
+      <c r="BE4">
+        <v>8.5</v>
+      </c>
+      <c r="BF4">
+        <v>2.89</v>
+      </c>
+      <c r="BG4">
+        <v>1.17</v>
+      </c>
+      <c r="BH4">
+        <v>4.25</v>
+      </c>
+      <c r="BI4">
+        <v>1.33</v>
+      </c>
+      <c r="BJ4">
+        <v>3.05</v>
+      </c>
+      <c r="BK4">
+        <v>1.58</v>
+      </c>
+      <c r="BL4">
+        <v>2.29</v>
+      </c>
+      <c r="BM4">
+        <v>1.93</v>
+      </c>
+      <c r="BN4">
+        <v>1.82</v>
+      </c>
+      <c r="BO4">
+        <v>2.4</v>
+      </c>
+      <c r="BP4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7785804</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>2.38</v>
+      </c>
+      <c r="S5">
+        <v>3.2</v>
+      </c>
+      <c r="T5">
+        <v>1.3</v>
+      </c>
+      <c r="U5">
+        <v>3.4</v>
+      </c>
+      <c r="V5">
+        <v>2.38</v>
+      </c>
+      <c r="W5">
+        <v>1.53</v>
+      </c>
+      <c r="X5">
+        <v>6</v>
+      </c>
+      <c r="Y5">
+        <v>1.13</v>
+      </c>
+      <c r="Z5">
+        <v>2.46</v>
+      </c>
+      <c r="AA5">
+        <v>3.45</v>
+      </c>
+      <c r="AB5">
+        <v>2.67</v>
+      </c>
+      <c r="AC5">
+        <v>1.01</v>
+      </c>
+      <c r="AD5">
+        <v>13</v>
+      </c>
+      <c r="AE5">
+        <v>1.14</v>
+      </c>
+      <c r="AF5">
+        <v>4.35</v>
+      </c>
+      <c r="AG5">
+        <v>1.55</v>
+      </c>
+      <c r="AH5">
+        <v>2.2</v>
+      </c>
+      <c r="AI5">
+        <v>1.5</v>
+      </c>
+      <c r="AJ5">
+        <v>2.5</v>
+      </c>
+      <c r="AK5">
+        <v>1.44</v>
+      </c>
+      <c r="AL5">
+        <v>1.29</v>
+      </c>
+      <c r="AM5">
+        <v>1.55</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>8</v>
+      </c>
+      <c r="AW5">
+        <v>9</v>
+      </c>
+      <c r="AX5">
+        <v>9</v>
+      </c>
+      <c r="AY5">
+        <v>15</v>
+      </c>
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>9</v>
+      </c>
+      <c r="BB5">
+        <v>4</v>
+      </c>
+      <c r="BC5">
+        <v>13</v>
+      </c>
+      <c r="BD5">
+        <v>2.13</v>
+      </c>
+      <c r="BE5">
+        <v>6.65</v>
+      </c>
+      <c r="BF5">
+        <v>2.06</v>
+      </c>
+      <c r="BG5">
+        <v>1.13</v>
+      </c>
+      <c r="BH5">
+        <v>4.75</v>
+      </c>
+      <c r="BI5">
+        <v>1.24</v>
+      </c>
+      <c r="BJ5">
+        <v>3.34</v>
+      </c>
+      <c r="BK5">
+        <v>1.46</v>
+      </c>
+      <c r="BL5">
+        <v>2.45</v>
+      </c>
+      <c r="BM5">
+        <v>1.8</v>
+      </c>
+      <c r="BN5">
+        <v>1.9</v>
+      </c>
+      <c r="BO5">
+        <v>2.27</v>
+      </c>
+      <c r="BP5">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7785805</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6">
+        <v>2.2</v>
+      </c>
+      <c r="R6">
+        <v>2.5</v>
+      </c>
+      <c r="S6">
+        <v>4.5</v>
+      </c>
+      <c r="T6">
+        <v>1.29</v>
+      </c>
+      <c r="U6">
+        <v>3.5</v>
+      </c>
+      <c r="V6">
+        <v>2.25</v>
+      </c>
+      <c r="W6">
+        <v>1.57</v>
+      </c>
+      <c r="X6">
+        <v>5.5</v>
+      </c>
+      <c r="Y6">
+        <v>1.14</v>
+      </c>
+      <c r="Z6">
+        <v>1.7</v>
+      </c>
+      <c r="AA6">
+        <v>4</v>
+      </c>
+      <c r="AB6">
+        <v>4.3</v>
+      </c>
+      <c r="AC6">
+        <v>1.01</v>
+      </c>
+      <c r="AD6">
+        <v>13</v>
+      </c>
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>4.9</v>
+      </c>
+      <c r="AG6">
+        <v>1.49</v>
+      </c>
+      <c r="AH6">
+        <v>2.44</v>
+      </c>
+      <c r="AI6">
+        <v>1.57</v>
+      </c>
+      <c r="AJ6">
+        <v>2.25</v>
+      </c>
+      <c r="AK6">
+        <v>1.2</v>
+      </c>
+      <c r="AL6">
+        <v>1.22</v>
+      </c>
+      <c r="AM6">
+        <v>2.2</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>6</v>
+      </c>
+      <c r="AV6">
+        <v>4</v>
+      </c>
+      <c r="AW6">
+        <v>14</v>
+      </c>
+      <c r="AX6">
+        <v>3</v>
+      </c>
+      <c r="AY6">
+        <v>20</v>
+      </c>
+      <c r="AZ6">
+        <v>7</v>
+      </c>
+      <c r="BA6">
+        <v>9</v>
+      </c>
+      <c r="BB6">
+        <v>3</v>
+      </c>
+      <c r="BC6">
+        <v>12</v>
+      </c>
+      <c r="BD6">
+        <v>1.45</v>
+      </c>
+      <c r="BE6">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="BF6">
+        <v>3.36</v>
+      </c>
+      <c r="BG6">
+        <v>1.15</v>
+      </c>
+      <c r="BH6">
+        <v>4.45</v>
+      </c>
+      <c r="BI6">
+        <v>1.29</v>
+      </c>
+      <c r="BJ6">
+        <v>3.12</v>
+      </c>
+      <c r="BK6">
+        <v>1.53</v>
+      </c>
+      <c r="BL6">
+        <v>2.34</v>
+      </c>
+      <c r="BM6">
+        <v>1.87</v>
+      </c>
+      <c r="BN6">
+        <v>1.87</v>
+      </c>
+      <c r="BO6">
+        <v>2.35</v>
+      </c>
+      <c r="BP6">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7785806</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>89</v>
+      </c>
+      <c r="P7" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q7">
+        <v>2.5</v>
+      </c>
+      <c r="R7">
+        <v>2.38</v>
+      </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>1.3</v>
+      </c>
+      <c r="U7">
+        <v>3.4</v>
+      </c>
+      <c r="V7">
+        <v>2.38</v>
+      </c>
+      <c r="W7">
+        <v>1.53</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <v>1.13</v>
+      </c>
+      <c r="Z7">
+        <v>1.9</v>
+      </c>
+      <c r="AA7">
+        <v>3.62</v>
+      </c>
+      <c r="AB7">
+        <v>3.74</v>
+      </c>
+      <c r="AC7">
+        <v>1.01</v>
+      </c>
+      <c r="AD7">
+        <v>11</v>
+      </c>
+      <c r="AE7">
+        <v>1.13</v>
+      </c>
+      <c r="AF7">
+        <v>4.6</v>
+      </c>
+      <c r="AG7">
+        <v>1.55</v>
+      </c>
+      <c r="AH7">
+        <v>2.2</v>
+      </c>
+      <c r="AI7">
+        <v>1.53</v>
+      </c>
+      <c r="AJ7">
+        <v>2.38</v>
+      </c>
+      <c r="AK7">
+        <v>1.33</v>
+      </c>
+      <c r="AL7">
+        <v>1.29</v>
+      </c>
+      <c r="AM7">
+        <v>1.75</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>3</v>
+      </c>
+      <c r="AV7">
+        <v>6</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>9</v>
+      </c>
+      <c r="AY7">
+        <v>4</v>
+      </c>
+      <c r="AZ7">
+        <v>15</v>
+      </c>
+      <c r="BA7">
+        <v>2</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>4</v>
+      </c>
+      <c r="BD7">
+        <v>1.78</v>
+      </c>
+      <c r="BE7">
+        <v>8.9</v>
+      </c>
+      <c r="BF7">
+        <v>2.37</v>
+      </c>
+      <c r="BG7">
+        <v>1.14</v>
+      </c>
+      <c r="BH7">
+        <v>4.6</v>
+      </c>
+      <c r="BI7">
+        <v>1.24</v>
+      </c>
+      <c r="BJ7">
+        <v>3.34</v>
+      </c>
+      <c r="BK7">
+        <v>1.46</v>
+      </c>
+      <c r="BL7">
+        <v>2.45</v>
+      </c>
+      <c r="BM7">
+        <v>1.8</v>
+      </c>
+      <c r="BN7">
+        <v>1.9</v>
+      </c>
+      <c r="BO7">
+        <v>2.25</v>
+      </c>
+      <c r="BP7">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7785807</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q8">
+        <v>3.4</v>
+      </c>
+      <c r="R8">
+        <v>2.25</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>1.33</v>
+      </c>
+      <c r="U8">
+        <v>3.25</v>
+      </c>
+      <c r="V8">
+        <v>2.63</v>
+      </c>
+      <c r="W8">
+        <v>1.44</v>
+      </c>
+      <c r="X8">
+        <v>6.5</v>
+      </c>
+      <c r="Y8">
+        <v>1.11</v>
+      </c>
+      <c r="Z8">
+        <v>2.88</v>
+      </c>
+      <c r="AA8">
+        <v>3.29</v>
+      </c>
+      <c r="AB8">
+        <v>2.39</v>
+      </c>
+      <c r="AC8">
+        <v>1.01</v>
+      </c>
+      <c r="AD8">
+        <v>11</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>3.88</v>
+      </c>
+      <c r="AG8">
+        <v>1.65</v>
+      </c>
+      <c r="AH8">
+        <v>2.05</v>
+      </c>
+      <c r="AI8">
+        <v>1.57</v>
+      </c>
+      <c r="AJ8">
+        <v>2.25</v>
+      </c>
+      <c r="AK8">
+        <v>1.57</v>
+      </c>
+      <c r="AL8">
+        <v>1.3</v>
+      </c>
+      <c r="AM8">
+        <v>1.4</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>7</v>
+      </c>
+      <c r="AW8">
+        <v>2</v>
+      </c>
+      <c r="AX8">
+        <v>3</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>10</v>
+      </c>
+      <c r="BA8">
+        <v>5</v>
+      </c>
+      <c r="BB8">
+        <v>12</v>
+      </c>
+      <c r="BC8">
+        <v>17</v>
+      </c>
+      <c r="BD8">
+        <v>2.08</v>
+      </c>
+      <c r="BE8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF8">
+        <v>1.97</v>
+      </c>
+      <c r="BG8">
+        <v>1.12</v>
+      </c>
+      <c r="BH8">
+        <v>4.95</v>
+      </c>
+      <c r="BI8">
+        <v>1.24</v>
+      </c>
+      <c r="BJ8">
+        <v>3.45</v>
+      </c>
+      <c r="BK8">
+        <v>1.45</v>
+      </c>
+      <c r="BL8">
+        <v>2.55</v>
+      </c>
+      <c r="BM8">
+        <v>1.74</v>
+      </c>
+      <c r="BN8">
+        <v>2.02</v>
+      </c>
+      <c r="BO8">
+        <v>2.16</v>
+      </c>
+      <c r="BP8">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -247,6 +247,9 @@
     <t>Aalesund</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Mjøndalen</t>
   </si>
   <si>
@@ -268,6 +271,9 @@
     <t>Lillestrøm</t>
   </si>
   <si>
+    <t>Moss</t>
+  </si>
+  <si>
     <t>['43', '57', '71']</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>['5', '25']</t>
   </si>
   <si>
+    <t>['20', '35', '85']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -305,6 +314,9 @@
   </si>
   <si>
     <t>['11', '43']</t>
+  </si>
+  <si>
+    <t>['83', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -666,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -898,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -919,10 +931,10 @@
         <v>5</v>
       </c>
       <c r="O2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1104,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1125,10 +1137,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1310,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1331,10 +1343,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1516,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1537,10 +1549,10 @@
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1722,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1743,10 +1755,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1928,7 +1940,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -1949,10 +1961,10 @@
         <v>3</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2134,7 +2146,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -2155,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2314,6 +2326,212 @@
         <v>2.16</v>
       </c>
       <c r="BP8">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7785808</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45748.58333333334</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P9" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>3.25</v>
+      </c>
+      <c r="R9">
+        <v>2.25</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>1.33</v>
+      </c>
+      <c r="U9">
+        <v>3.25</v>
+      </c>
+      <c r="V9">
+        <v>2.63</v>
+      </c>
+      <c r="W9">
+        <v>1.44</v>
+      </c>
+      <c r="X9">
+        <v>7</v>
+      </c>
+      <c r="Y9">
+        <v>1.1</v>
+      </c>
+      <c r="Z9">
+        <v>2.94</v>
+      </c>
+      <c r="AA9">
+        <v>3.25</v>
+      </c>
+      <c r="AB9">
+        <v>2.37</v>
+      </c>
+      <c r="AC9">
+        <v>1.01</v>
+      </c>
+      <c r="AD9">
+        <v>11</v>
+      </c>
+      <c r="AE9">
+        <v>1.19</v>
+      </c>
+      <c r="AF9">
+        <v>3.84</v>
+      </c>
+      <c r="AG9">
+        <v>1.82</v>
+      </c>
+      <c r="AH9">
+        <v>1.92</v>
+      </c>
+      <c r="AI9">
+        <v>1.62</v>
+      </c>
+      <c r="AJ9">
+        <v>2.2</v>
+      </c>
+      <c r="AK9">
+        <v>1.55</v>
+      </c>
+      <c r="AL9">
+        <v>1.3</v>
+      </c>
+      <c r="AM9">
+        <v>1.44</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
+        <v>3</v>
+      </c>
+      <c r="AW9">
+        <v>8</v>
+      </c>
+      <c r="AX9">
+        <v>8</v>
+      </c>
+      <c r="AY9">
+        <v>15</v>
+      </c>
+      <c r="AZ9">
+        <v>11</v>
+      </c>
+      <c r="BA9">
+        <v>9</v>
+      </c>
+      <c r="BB9">
+        <v>7</v>
+      </c>
+      <c r="BC9">
+        <v>16</v>
+      </c>
+      <c r="BD9">
+        <v>2.43</v>
+      </c>
+      <c r="BE9">
+        <v>8.5</v>
+      </c>
+      <c r="BF9">
+        <v>1.75</v>
+      </c>
+      <c r="BG9">
+        <v>1.12</v>
+      </c>
+      <c r="BH9">
+        <v>4.95</v>
+      </c>
+      <c r="BI9">
+        <v>1.24</v>
+      </c>
+      <c r="BJ9">
+        <v>3.45</v>
+      </c>
+      <c r="BK9">
+        <v>1.45</v>
+      </c>
+      <c r="BL9">
+        <v>2.55</v>
+      </c>
+      <c r="BM9">
+        <v>1.74</v>
+      </c>
+      <c r="BN9">
+        <v>2.02</v>
+      </c>
+      <c r="BO9">
+        <v>2.16</v>
+      </c>
+      <c r="BP9">
         <v>1.65</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="111">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,30 +250,30 @@
     <t>Raufoss</t>
   </si>
   <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
     <t>Mjøndalen</t>
   </si>
   <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
     <t>['43', '57', '71']</t>
   </si>
   <si>
@@ -298,6 +298,21 @@
     <t>['20', '35', '85']</t>
   </si>
   <si>
+    <t>['35', '40', '90+3']</t>
+  </si>
+  <si>
+    <t>['36', '61']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -317,6 +332,21 @@
   </si>
   <si>
     <t>['83', '90+6']</t>
+  </si>
+  <si>
+    <t>['39', '45']</t>
+  </si>
+  <si>
+    <t>['30', '52', '72', '90+4']</t>
+  </si>
+  <si>
+    <t>['47', '60', '90+3']</t>
+  </si>
+  <si>
+    <t>['33', '90+1']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -910,7 +940,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -934,7 +964,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1116,7 +1146,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1322,7 +1352,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1346,7 +1376,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1528,7 +1558,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1552,7 +1582,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1734,7 +1764,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1758,7 +1788,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1940,7 +1970,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -1964,7 +1994,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2146,7 +2176,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -2170,7 +2200,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2352,7 +2382,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2376,7 +2406,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2533,6 +2563,1448 @@
       </c>
       <c r="BP9">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7785816</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>89</v>
+      </c>
+      <c r="P10" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q10">
+        <v>2.6</v>
+      </c>
+      <c r="R10">
+        <v>2.4</v>
+      </c>
+      <c r="S10">
+        <v>3.6</v>
+      </c>
+      <c r="T10">
+        <v>1.29</v>
+      </c>
+      <c r="U10">
+        <v>3.5</v>
+      </c>
+      <c r="V10">
+        <v>2.25</v>
+      </c>
+      <c r="W10">
+        <v>1.57</v>
+      </c>
+      <c r="X10">
+        <v>5.5</v>
+      </c>
+      <c r="Y10">
+        <v>1.14</v>
+      </c>
+      <c r="Z10">
+        <v>2.03</v>
+      </c>
+      <c r="AA10">
+        <v>3.74</v>
+      </c>
+      <c r="AB10">
+        <v>3.23</v>
+      </c>
+      <c r="AC10">
+        <v>1.01</v>
+      </c>
+      <c r="AD10">
+        <v>15</v>
+      </c>
+      <c r="AE10">
+        <v>1.12</v>
+      </c>
+      <c r="AF10">
+        <v>4.75</v>
+      </c>
+      <c r="AG10">
+        <v>1.5</v>
+      </c>
+      <c r="AH10">
+        <v>2.41</v>
+      </c>
+      <c r="AI10">
+        <v>1.5</v>
+      </c>
+      <c r="AJ10">
+        <v>2.5</v>
+      </c>
+      <c r="AK10">
+        <v>1.33</v>
+      </c>
+      <c r="AL10">
+        <v>1.26</v>
+      </c>
+      <c r="AM10">
+        <v>1.73</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>3</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>5</v>
+      </c>
+      <c r="AX10">
+        <v>9</v>
+      </c>
+      <c r="AY10">
+        <v>5</v>
+      </c>
+      <c r="AZ10">
+        <v>14</v>
+      </c>
+      <c r="BA10">
+        <v>4</v>
+      </c>
+      <c r="BB10">
+        <v>4</v>
+      </c>
+      <c r="BC10">
+        <v>8</v>
+      </c>
+      <c r="BD10">
+        <v>1.92</v>
+      </c>
+      <c r="BE10">
+        <v>6.65</v>
+      </c>
+      <c r="BF10">
+        <v>2.3</v>
+      </c>
+      <c r="BG10">
+        <v>1.24</v>
+      </c>
+      <c r="BH10">
+        <v>3.65</v>
+      </c>
+      <c r="BI10">
+        <v>1.25</v>
+      </c>
+      <c r="BJ10">
+        <v>3.28</v>
+      </c>
+      <c r="BK10">
+        <v>1.47</v>
+      </c>
+      <c r="BL10">
+        <v>2.42</v>
+      </c>
+      <c r="BM10">
+        <v>1.82</v>
+      </c>
+      <c r="BN10">
+        <v>1.88</v>
+      </c>
+      <c r="BO10">
+        <v>2.28</v>
+      </c>
+      <c r="BP10">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7785815</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>4</v>
+      </c>
+      <c r="N11">
+        <v>7</v>
+      </c>
+      <c r="O11" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q11">
+        <v>3.75</v>
+      </c>
+      <c r="R11">
+        <v>2.2</v>
+      </c>
+      <c r="S11">
+        <v>2.75</v>
+      </c>
+      <c r="T11">
+        <v>1.36</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>2.75</v>
+      </c>
+      <c r="W11">
+        <v>1.4</v>
+      </c>
+      <c r="X11">
+        <v>7</v>
+      </c>
+      <c r="Y11">
+        <v>1.1</v>
+      </c>
+      <c r="Z11">
+        <v>3.25</v>
+      </c>
+      <c r="AA11">
+        <v>3.47</v>
+      </c>
+      <c r="AB11">
+        <v>2.12</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE11">
+        <v>1.25</v>
+      </c>
+      <c r="AF11">
+        <v>3.6</v>
+      </c>
+      <c r="AG11">
+        <v>1.79</v>
+      </c>
+      <c r="AH11">
+        <v>1.95</v>
+      </c>
+      <c r="AI11">
+        <v>1.67</v>
+      </c>
+      <c r="AJ11">
+        <v>2.1</v>
+      </c>
+      <c r="AK11">
+        <v>1.63</v>
+      </c>
+      <c r="AL11">
+        <v>1.29</v>
+      </c>
+      <c r="AM11">
+        <v>1.35</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>3</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>9</v>
+      </c>
+      <c r="AV11">
+        <v>11</v>
+      </c>
+      <c r="AW11">
+        <v>6</v>
+      </c>
+      <c r="AX11">
+        <v>3</v>
+      </c>
+      <c r="AY11">
+        <v>15</v>
+      </c>
+      <c r="AZ11">
+        <v>14</v>
+      </c>
+      <c r="BA11">
+        <v>7</v>
+      </c>
+      <c r="BB11">
+        <v>8</v>
+      </c>
+      <c r="BC11">
+        <v>15</v>
+      </c>
+      <c r="BD11">
+        <v>2.39</v>
+      </c>
+      <c r="BE11">
+        <v>6.7</v>
+      </c>
+      <c r="BF11">
+        <v>1.86</v>
+      </c>
+      <c r="BG11">
+        <v>1.16</v>
+      </c>
+      <c r="BH11">
+        <v>4.6</v>
+      </c>
+      <c r="BI11">
+        <v>1.25</v>
+      </c>
+      <c r="BJ11">
+        <v>3.28</v>
+      </c>
+      <c r="BK11">
+        <v>1.47</v>
+      </c>
+      <c r="BL11">
+        <v>2.42</v>
+      </c>
+      <c r="BM11">
+        <v>1.81</v>
+      </c>
+      <c r="BN11">
+        <v>1.89</v>
+      </c>
+      <c r="BO11">
+        <v>2.28</v>
+      </c>
+      <c r="BP11">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7785813</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>95</v>
+      </c>
+      <c r="P12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12">
+        <v>2.5</v>
+      </c>
+      <c r="R12">
+        <v>2.25</v>
+      </c>
+      <c r="S12">
+        <v>4</v>
+      </c>
+      <c r="T12">
+        <v>1.36</v>
+      </c>
+      <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
+        <v>2.63</v>
+      </c>
+      <c r="W12">
+        <v>1.44</v>
+      </c>
+      <c r="X12">
+        <v>7</v>
+      </c>
+      <c r="Y12">
+        <v>1.1</v>
+      </c>
+      <c r="Z12">
+        <v>1.95</v>
+      </c>
+      <c r="AA12">
+        <v>3.5</v>
+      </c>
+      <c r="AB12">
+        <v>3.7</v>
+      </c>
+      <c r="AC12">
+        <v>1.04</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>1.25</v>
+      </c>
+      <c r="AF12">
+        <v>3.7</v>
+      </c>
+      <c r="AG12">
+        <v>1.7</v>
+      </c>
+      <c r="AH12">
+        <v>1.95</v>
+      </c>
+      <c r="AI12">
+        <v>1.67</v>
+      </c>
+      <c r="AJ12">
+        <v>2.1</v>
+      </c>
+      <c r="AK12">
+        <v>1.27</v>
+      </c>
+      <c r="AL12">
+        <v>1.28</v>
+      </c>
+      <c r="AM12">
+        <v>1.8</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>5</v>
+      </c>
+      <c r="AV12">
+        <v>8</v>
+      </c>
+      <c r="AW12">
+        <v>4</v>
+      </c>
+      <c r="AX12">
+        <v>6</v>
+      </c>
+      <c r="AY12">
+        <v>9</v>
+      </c>
+      <c r="AZ12">
+        <v>14</v>
+      </c>
+      <c r="BA12">
+        <v>3</v>
+      </c>
+      <c r="BB12">
+        <v>5</v>
+      </c>
+      <c r="BC12">
+        <v>8</v>
+      </c>
+      <c r="BD12">
+        <v>1.54</v>
+      </c>
+      <c r="BE12">
+        <v>7.2</v>
+      </c>
+      <c r="BF12">
+        <v>3.15</v>
+      </c>
+      <c r="BG12">
+        <v>1.23</v>
+      </c>
+      <c r="BH12">
+        <v>3.65</v>
+      </c>
+      <c r="BI12">
+        <v>1.26</v>
+      </c>
+      <c r="BJ12">
+        <v>3.22</v>
+      </c>
+      <c r="BK12">
+        <v>1.49</v>
+      </c>
+      <c r="BL12">
+        <v>2.38</v>
+      </c>
+      <c r="BM12">
+        <v>1.85</v>
+      </c>
+      <c r="BN12">
+        <v>1.85</v>
+      </c>
+      <c r="BO12">
+        <v>2.34</v>
+      </c>
+      <c r="BP12">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7785814</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>96</v>
+      </c>
+      <c r="P13" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q13">
+        <v>3.4</v>
+      </c>
+      <c r="R13">
+        <v>2.25</v>
+      </c>
+      <c r="S13">
+        <v>2.88</v>
+      </c>
+      <c r="T13">
+        <v>1.33</v>
+      </c>
+      <c r="U13">
+        <v>3.25</v>
+      </c>
+      <c r="V13">
+        <v>2.63</v>
+      </c>
+      <c r="W13">
+        <v>1.44</v>
+      </c>
+      <c r="X13">
+        <v>7</v>
+      </c>
+      <c r="Y13">
+        <v>1.1</v>
+      </c>
+      <c r="Z13">
+        <v>3.16</v>
+      </c>
+      <c r="AA13">
+        <v>3.37</v>
+      </c>
+      <c r="AB13">
+        <v>2.19</v>
+      </c>
+      <c r="AC13">
+        <v>1.04</v>
+      </c>
+      <c r="AD13">
+        <v>11</v>
+      </c>
+      <c r="AE13">
+        <v>1.25</v>
+      </c>
+      <c r="AF13">
+        <v>3.8</v>
+      </c>
+      <c r="AG13">
+        <v>1.69</v>
+      </c>
+      <c r="AH13">
+        <v>2.04</v>
+      </c>
+      <c r="AI13">
+        <v>1.62</v>
+      </c>
+      <c r="AJ13">
+        <v>2.2</v>
+      </c>
+      <c r="AK13">
+        <v>1.57</v>
+      </c>
+      <c r="AL13">
+        <v>1.29</v>
+      </c>
+      <c r="AM13">
+        <v>1.41</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>3</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>8</v>
+      </c>
+      <c r="AV13">
+        <v>14</v>
+      </c>
+      <c r="AW13">
+        <v>4</v>
+      </c>
+      <c r="AX13">
+        <v>5</v>
+      </c>
+      <c r="AY13">
+        <v>12</v>
+      </c>
+      <c r="AZ13">
+        <v>19</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>5</v>
+      </c>
+      <c r="BC13">
+        <v>9</v>
+      </c>
+      <c r="BD13">
+        <v>2.13</v>
+      </c>
+      <c r="BE13">
+        <v>6.55</v>
+      </c>
+      <c r="BF13">
+        <v>2.07</v>
+      </c>
+      <c r="BG13">
+        <v>1.24</v>
+      </c>
+      <c r="BH13">
+        <v>3.55</v>
+      </c>
+      <c r="BI13">
+        <v>1.29</v>
+      </c>
+      <c r="BJ13">
+        <v>3.04</v>
+      </c>
+      <c r="BK13">
+        <v>1.54</v>
+      </c>
+      <c r="BL13">
+        <v>2.25</v>
+      </c>
+      <c r="BM13">
+        <v>1.93</v>
+      </c>
+      <c r="BN13">
+        <v>1.78</v>
+      </c>
+      <c r="BO13">
+        <v>2.48</v>
+      </c>
+      <c r="BP13">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7785811</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P14" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14">
+        <v>2.25</v>
+      </c>
+      <c r="R14">
+        <v>2.4</v>
+      </c>
+      <c r="S14">
+        <v>4.5</v>
+      </c>
+      <c r="T14">
+        <v>1.29</v>
+      </c>
+      <c r="U14">
+        <v>3.5</v>
+      </c>
+      <c r="V14">
+        <v>2.38</v>
+      </c>
+      <c r="W14">
+        <v>1.53</v>
+      </c>
+      <c r="X14">
+        <v>5.5</v>
+      </c>
+      <c r="Y14">
+        <v>1.14</v>
+      </c>
+      <c r="Z14">
+        <v>1.68</v>
+      </c>
+      <c r="AA14">
+        <v>3.97</v>
+      </c>
+      <c r="AB14">
+        <v>4.5</v>
+      </c>
+      <c r="AC14">
+        <v>1.02</v>
+      </c>
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
+        <v>1.18</v>
+      </c>
+      <c r="AF14">
+        <v>4.5</v>
+      </c>
+      <c r="AG14">
+        <v>1.57</v>
+      </c>
+      <c r="AH14">
+        <v>2.25</v>
+      </c>
+      <c r="AI14">
+        <v>1.57</v>
+      </c>
+      <c r="AJ14">
+        <v>2.25</v>
+      </c>
+      <c r="AK14">
+        <v>1.2</v>
+      </c>
+      <c r="AL14">
+        <v>1.24</v>
+      </c>
+      <c r="AM14">
+        <v>2.1</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>6</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>4</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>10</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>10</v>
+      </c>
+      <c r="BC14">
+        <v>15</v>
+      </c>
+      <c r="BD14">
+        <v>1.4</v>
+      </c>
+      <c r="BE14">
+        <v>9.6</v>
+      </c>
+      <c r="BF14">
+        <v>3.48</v>
+      </c>
+      <c r="BG14">
+        <v>1.27</v>
+      </c>
+      <c r="BH14">
+        <v>3.3</v>
+      </c>
+      <c r="BI14">
+        <v>1.32</v>
+      </c>
+      <c r="BJ14">
+        <v>2.88</v>
+      </c>
+      <c r="BK14">
+        <v>1.59</v>
+      </c>
+      <c r="BL14">
+        <v>2.16</v>
+      </c>
+      <c r="BM14">
+        <v>1.99</v>
+      </c>
+      <c r="BN14">
+        <v>1.73</v>
+      </c>
+      <c r="BO14">
+        <v>2.57</v>
+      </c>
+      <c r="BP14">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7785810</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>89</v>
+      </c>
+      <c r="P15" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q15">
+        <v>3.4</v>
+      </c>
+      <c r="R15">
+        <v>2.25</v>
+      </c>
+      <c r="S15">
+        <v>2.88</v>
+      </c>
+      <c r="T15">
+        <v>1.33</v>
+      </c>
+      <c r="U15">
+        <v>3.25</v>
+      </c>
+      <c r="V15">
+        <v>2.63</v>
+      </c>
+      <c r="W15">
+        <v>1.44</v>
+      </c>
+      <c r="X15">
+        <v>6.5</v>
+      </c>
+      <c r="Y15">
+        <v>1.11</v>
+      </c>
+      <c r="Z15">
+        <v>2.91</v>
+      </c>
+      <c r="AA15">
+        <v>3.41</v>
+      </c>
+      <c r="AB15">
+        <v>2.3</v>
+      </c>
+      <c r="AC15">
+        <v>1.04</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>1.22</v>
+      </c>
+      <c r="AF15">
+        <v>3.9</v>
+      </c>
+      <c r="AG15">
+        <v>1.67</v>
+      </c>
+      <c r="AH15">
+        <v>2</v>
+      </c>
+      <c r="AI15">
+        <v>1.57</v>
+      </c>
+      <c r="AJ15">
+        <v>2.25</v>
+      </c>
+      <c r="AK15">
+        <v>1.57</v>
+      </c>
+      <c r="AL15">
+        <v>1.29</v>
+      </c>
+      <c r="AM15">
+        <v>1.41</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>3</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>2</v>
+      </c>
+      <c r="AV15">
+        <v>16</v>
+      </c>
+      <c r="AW15">
+        <v>3</v>
+      </c>
+      <c r="AX15">
+        <v>2</v>
+      </c>
+      <c r="AY15">
+        <v>5</v>
+      </c>
+      <c r="AZ15">
+        <v>18</v>
+      </c>
+      <c r="BA15">
+        <v>6</v>
+      </c>
+      <c r="BB15">
+        <v>6</v>
+      </c>
+      <c r="BC15">
+        <v>12</v>
+      </c>
+      <c r="BD15">
+        <v>2.18</v>
+      </c>
+      <c r="BE15">
+        <v>6.6</v>
+      </c>
+      <c r="BF15">
+        <v>2.02</v>
+      </c>
+      <c r="BG15">
+        <v>1.21</v>
+      </c>
+      <c r="BH15">
+        <v>3.9</v>
+      </c>
+      <c r="BI15">
+        <v>1.25</v>
+      </c>
+      <c r="BJ15">
+        <v>3.28</v>
+      </c>
+      <c r="BK15">
+        <v>1.48</v>
+      </c>
+      <c r="BL15">
+        <v>2.4</v>
+      </c>
+      <c r="BM15">
+        <v>1.83</v>
+      </c>
+      <c r="BN15">
+        <v>1.87</v>
+      </c>
+      <c r="BO15">
+        <v>2.3</v>
+      </c>
+      <c r="BP15">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7785812</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q16">
+        <v>3.1</v>
+      </c>
+      <c r="R16">
+        <v>2.1</v>
+      </c>
+      <c r="S16">
+        <v>3.6</v>
+      </c>
+      <c r="T16">
+        <v>1.44</v>
+      </c>
+      <c r="U16">
+        <v>2.63</v>
+      </c>
+      <c r="V16">
+        <v>3.25</v>
+      </c>
+      <c r="W16">
+        <v>1.33</v>
+      </c>
+      <c r="X16">
+        <v>9</v>
+      </c>
+      <c r="Y16">
+        <v>1.07</v>
+      </c>
+      <c r="Z16">
+        <v>2.5</v>
+      </c>
+      <c r="AA16">
+        <v>3.39</v>
+      </c>
+      <c r="AB16">
+        <v>2.66</v>
+      </c>
+      <c r="AC16">
+        <v>1.01</v>
+      </c>
+      <c r="AD16">
+        <v>8.6</v>
+      </c>
+      <c r="AE16">
+        <v>1.3</v>
+      </c>
+      <c r="AF16">
+        <v>3.25</v>
+      </c>
+      <c r="AG16">
+        <v>1.95</v>
+      </c>
+      <c r="AH16">
+        <v>1.79</v>
+      </c>
+      <c r="AI16">
+        <v>1.83</v>
+      </c>
+      <c r="AJ16">
+        <v>1.83</v>
+      </c>
+      <c r="AK16">
+        <v>1.47</v>
+      </c>
+      <c r="AL16">
+        <v>1.3</v>
+      </c>
+      <c r="AM16">
+        <v>1.47</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>4</v>
+      </c>
+      <c r="AV16">
+        <v>2</v>
+      </c>
+      <c r="AW16">
+        <v>3</v>
+      </c>
+      <c r="AX16">
+        <v>9</v>
+      </c>
+      <c r="AY16">
+        <v>7</v>
+      </c>
+      <c r="AZ16">
+        <v>11</v>
+      </c>
+      <c r="BA16">
+        <v>4</v>
+      </c>
+      <c r="BB16">
+        <v>6</v>
+      </c>
+      <c r="BC16">
+        <v>10</v>
+      </c>
+      <c r="BD16">
+        <v>1.63</v>
+      </c>
+      <c r="BE16">
+        <v>6.95</v>
+      </c>
+      <c r="BF16">
+        <v>2.88</v>
+      </c>
+      <c r="BG16">
+        <v>1.19</v>
+      </c>
+      <c r="BH16">
+        <v>4.1</v>
+      </c>
+      <c r="BI16">
+        <v>1.22</v>
+      </c>
+      <c r="BJ16">
+        <v>3.48</v>
+      </c>
+      <c r="BK16">
+        <v>1.44</v>
+      </c>
+      <c r="BL16">
+        <v>2.51</v>
+      </c>
+      <c r="BM16">
+        <v>1.76</v>
+      </c>
+      <c r="BN16">
+        <v>1.95</v>
+      </c>
+      <c r="BO16">
+        <v>2.19</v>
+      </c>
+      <c r="BP16">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="112">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['75']</t>
   </si>
 </sst>
 </file>
@@ -708,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4007,6 +4010,212 @@
         <v>1.57</v>
       </c>
     </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7785809</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>89</v>
+      </c>
+      <c r="P17" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q17">
+        <v>2.83</v>
+      </c>
+      <c r="R17">
+        <v>2.29</v>
+      </c>
+      <c r="S17">
+        <v>3.18</v>
+      </c>
+      <c r="T17">
+        <v>1.24</v>
+      </c>
+      <c r="U17">
+        <v>3.5</v>
+      </c>
+      <c r="V17">
+        <v>2.2</v>
+      </c>
+      <c r="W17">
+        <v>1.63</v>
+      </c>
+      <c r="X17">
+        <v>4.85</v>
+      </c>
+      <c r="Y17">
+        <v>1.13</v>
+      </c>
+      <c r="Z17">
+        <v>2.39</v>
+      </c>
+      <c r="AA17">
+        <v>3.65</v>
+      </c>
+      <c r="AB17">
+        <v>2.71</v>
+      </c>
+      <c r="AC17">
+        <v>1.01</v>
+      </c>
+      <c r="AD17">
+        <v>14.3</v>
+      </c>
+      <c r="AE17">
+        <v>1.14</v>
+      </c>
+      <c r="AF17">
+        <v>5.26</v>
+      </c>
+      <c r="AG17">
+        <v>1.5</v>
+      </c>
+      <c r="AH17">
+        <v>2.52</v>
+      </c>
+      <c r="AI17">
+        <v>1.41</v>
+      </c>
+      <c r="AJ17">
+        <v>2.69</v>
+      </c>
+      <c r="AK17">
+        <v>1.44</v>
+      </c>
+      <c r="AL17">
+        <v>1.27</v>
+      </c>
+      <c r="AM17">
+        <v>1.56</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>3</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>2</v>
+      </c>
+      <c r="AW17">
+        <v>8</v>
+      </c>
+      <c r="AX17">
+        <v>6</v>
+      </c>
+      <c r="AY17">
+        <v>8</v>
+      </c>
+      <c r="AZ17">
+        <v>8</v>
+      </c>
+      <c r="BA17">
+        <v>3</v>
+      </c>
+      <c r="BB17">
+        <v>8</v>
+      </c>
+      <c r="BC17">
+        <v>11</v>
+      </c>
+      <c r="BD17">
+        <v>1.91</v>
+      </c>
+      <c r="BE17">
+        <v>6.4</v>
+      </c>
+      <c r="BF17">
+        <v>2.08</v>
+      </c>
+      <c r="BG17">
+        <v>1.25</v>
+      </c>
+      <c r="BH17">
+        <v>3.45</v>
+      </c>
+      <c r="BI17">
+        <v>1.45</v>
+      </c>
+      <c r="BJ17">
+        <v>2.55</v>
+      </c>
+      <c r="BK17">
+        <v>1.73</v>
+      </c>
+      <c r="BL17">
+        <v>1.98</v>
+      </c>
+      <c r="BM17">
+        <v>2.12</v>
+      </c>
+      <c r="BN17">
+        <v>1.63</v>
+      </c>
+      <c r="BO17">
+        <v>2.65</v>
+      </c>
+      <c r="BP17">
+        <v>1.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="191">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -439,6 +439,15 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['14', '45+2', '37', '90+5']</t>
+  </si>
+  <si>
+    <t>['20', '25']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -569,6 +578,15 @@
   </si>
   <si>
     <t>['48', '73', '75']</t>
+  </si>
+  <si>
+    <t>['51', '54']</t>
+  </si>
+  <si>
+    <t>['48', '79']</t>
+  </si>
+  <si>
+    <t>['24']</t>
   </si>
 </sst>
 </file>
@@ -930,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP72"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1186,7 +1204,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1470,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.8</v>
@@ -1598,7 +1616,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1804,7 +1822,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1885,7 +1903,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2294,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2422,7 +2440,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2503,7 +2521,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ8">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2628,7 +2646,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2834,7 +2852,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3040,7 +3058,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3452,7 +3470,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3864,7 +3882,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3942,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ15">
         <v>1.4</v>
@@ -4070,7 +4088,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q16">
         <v>3.1</v>
@@ -4276,7 +4294,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4482,7 +4500,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4766,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0</v>
@@ -4894,7 +4912,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -4975,7 +4993,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ20">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR20">
         <v>1.5</v>
@@ -5100,7 +5118,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5181,7 +5199,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR21">
         <v>1.62</v>
@@ -5306,7 +5324,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5512,7 +5530,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5593,7 +5611,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ23">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>2.01</v>
@@ -5718,7 +5736,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5796,7 +5814,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ24">
         <v>1.6</v>
@@ -6130,7 +6148,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6211,7 +6229,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ26">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AR26">
         <v>0.7</v>
@@ -6336,7 +6354,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6748,7 +6766,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -6954,7 +6972,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7366,7 +7384,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7572,7 +7590,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -7650,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
         <v>1.5</v>
@@ -7984,7 +8002,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8190,7 +8208,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8602,7 +8620,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8680,7 +8698,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ38">
         <v>0.8</v>
@@ -8808,7 +8826,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -9220,7 +9238,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9507,7 +9525,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>1.44</v>
@@ -9838,7 +9856,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -9916,10 +9934,10 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
         <v>1.31</v>
@@ -10044,7 +10062,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10250,7 +10268,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10328,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.75</v>
@@ -10456,7 +10474,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10537,7 +10555,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ47">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -10662,7 +10680,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10868,7 +10886,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11280,7 +11298,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q51">
         <v>2.33</v>
@@ -12104,7 +12122,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12182,7 +12200,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ55">
         <v>1.4</v>
@@ -12722,7 +12740,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13134,7 +13152,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13215,7 +13233,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ60">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AR60">
         <v>1.03</v>
@@ -13340,7 +13358,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13418,10 +13436,10 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>2.18</v>
@@ -13546,7 +13564,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13752,7 +13770,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -13833,7 +13851,7 @@
         <v>2</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR63">
         <v>2.64</v>
@@ -13958,7 +13976,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14036,7 +14054,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ64">
         <v>0.75</v>
@@ -14164,7 +14182,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14576,7 +14594,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14782,7 +14800,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15194,7 +15212,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15606,7 +15624,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15763,6 +15781,624 @@
       </c>
       <c r="BP72">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7785876</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45822.45833333334</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>71</v>
+      </c>
+      <c r="H73" t="s">
+        <v>79</v>
+      </c>
+      <c r="I73">
+        <v>3</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>3</v>
+      </c>
+      <c r="L73">
+        <v>4</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73">
+        <v>6</v>
+      </c>
+      <c r="O73" t="s">
+        <v>141</v>
+      </c>
+      <c r="P73" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q73">
+        <v>2.05</v>
+      </c>
+      <c r="R73">
+        <v>2.2</v>
+      </c>
+      <c r="S73">
+        <v>4.5</v>
+      </c>
+      <c r="T73">
+        <v>1.18</v>
+      </c>
+      <c r="U73">
+        <v>4</v>
+      </c>
+      <c r="V73">
+        <v>2</v>
+      </c>
+      <c r="W73">
+        <v>1.78</v>
+      </c>
+      <c r="X73">
+        <v>4.25</v>
+      </c>
+      <c r="Y73">
+        <v>1.2</v>
+      </c>
+      <c r="Z73">
+        <v>1.61</v>
+      </c>
+      <c r="AA73">
+        <v>4</v>
+      </c>
+      <c r="AB73">
+        <v>4.33</v>
+      </c>
+      <c r="AC73">
+        <v>1.01</v>
+      </c>
+      <c r="AD73">
+        <v>23</v>
+      </c>
+      <c r="AE73">
+        <v>1.12</v>
+      </c>
+      <c r="AF73">
+        <v>6</v>
+      </c>
+      <c r="AG73">
+        <v>1.41</v>
+      </c>
+      <c r="AH73">
+        <v>2.69</v>
+      </c>
+      <c r="AI73">
+        <v>1.47</v>
+      </c>
+      <c r="AJ73">
+        <v>2.55</v>
+      </c>
+      <c r="AK73">
+        <v>1.22</v>
+      </c>
+      <c r="AL73">
+        <v>1.2</v>
+      </c>
+      <c r="AM73">
+        <v>2.3</v>
+      </c>
+      <c r="AN73">
+        <v>1.75</v>
+      </c>
+      <c r="AO73">
+        <v>1.5</v>
+      </c>
+      <c r="AP73">
+        <v>2</v>
+      </c>
+      <c r="AQ73">
+        <v>1.2</v>
+      </c>
+      <c r="AR73">
+        <v>2.07</v>
+      </c>
+      <c r="AS73">
+        <v>1.5</v>
+      </c>
+      <c r="AT73">
+        <v>3.57</v>
+      </c>
+      <c r="AU73">
+        <v>11</v>
+      </c>
+      <c r="AV73">
+        <v>4</v>
+      </c>
+      <c r="AW73">
+        <v>4</v>
+      </c>
+      <c r="AX73">
+        <v>5</v>
+      </c>
+      <c r="AY73">
+        <v>15</v>
+      </c>
+      <c r="AZ73">
+        <v>9</v>
+      </c>
+      <c r="BA73">
+        <v>10</v>
+      </c>
+      <c r="BB73">
+        <v>7</v>
+      </c>
+      <c r="BC73">
+        <v>17</v>
+      </c>
+      <c r="BD73">
+        <v>1.3</v>
+      </c>
+      <c r="BE73">
+        <v>7.5</v>
+      </c>
+      <c r="BF73">
+        <v>3.15</v>
+      </c>
+      <c r="BG73">
+        <v>1.16</v>
+      </c>
+      <c r="BH73">
+        <v>4.6</v>
+      </c>
+      <c r="BI73">
+        <v>1.29</v>
+      </c>
+      <c r="BJ73">
+        <v>3.15</v>
+      </c>
+      <c r="BK73">
+        <v>1.5</v>
+      </c>
+      <c r="BL73">
+        <v>2.42</v>
+      </c>
+      <c r="BM73">
+        <v>1.81</v>
+      </c>
+      <c r="BN73">
+        <v>1.95</v>
+      </c>
+      <c r="BO73">
+        <v>2.24</v>
+      </c>
+      <c r="BP73">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7785873</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45822.54166666666</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>83</v>
+      </c>
+      <c r="H74" t="s">
+        <v>82</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>2</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74">
+        <v>4</v>
+      </c>
+      <c r="O74" t="s">
+        <v>142</v>
+      </c>
+      <c r="P74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q74">
+        <v>5.5</v>
+      </c>
+      <c r="R74">
+        <v>2.38</v>
+      </c>
+      <c r="S74">
+        <v>2.11</v>
+      </c>
+      <c r="T74">
+        <v>1.34</v>
+      </c>
+      <c r="U74">
+        <v>3.2</v>
+      </c>
+      <c r="V74">
+        <v>2.44</v>
+      </c>
+      <c r="W74">
+        <v>1.55</v>
+      </c>
+      <c r="X74">
+        <v>4.5</v>
+      </c>
+      <c r="Y74">
+        <v>1.14</v>
+      </c>
+      <c r="Z74">
+        <v>5.41</v>
+      </c>
+      <c r="AA74">
+        <v>4</v>
+      </c>
+      <c r="AB74">
+        <v>1.46</v>
+      </c>
+      <c r="AC74">
+        <v>1</v>
+      </c>
+      <c r="AD74">
+        <v>15</v>
+      </c>
+      <c r="AE74">
+        <v>1.15</v>
+      </c>
+      <c r="AF74">
+        <v>4.5</v>
+      </c>
+      <c r="AG74">
+        <v>1.65</v>
+      </c>
+      <c r="AH74">
+        <v>2.25</v>
+      </c>
+      <c r="AI74">
+        <v>1.7</v>
+      </c>
+      <c r="AJ74">
+        <v>2.04</v>
+      </c>
+      <c r="AK74">
+        <v>1.23</v>
+      </c>
+      <c r="AL74">
+        <v>1.22</v>
+      </c>
+      <c r="AM74">
+        <v>1.17</v>
+      </c>
+      <c r="AN74">
+        <v>1.5</v>
+      </c>
+      <c r="AO74">
+        <v>2.2</v>
+      </c>
+      <c r="AP74">
+        <v>1.4</v>
+      </c>
+      <c r="AQ74">
+        <v>2</v>
+      </c>
+      <c r="AR74">
+        <v>1.26</v>
+      </c>
+      <c r="AS74">
+        <v>1.96</v>
+      </c>
+      <c r="AT74">
+        <v>3.22</v>
+      </c>
+      <c r="AU74">
+        <v>9</v>
+      </c>
+      <c r="AV74">
+        <v>8</v>
+      </c>
+      <c r="AW74">
+        <v>3</v>
+      </c>
+      <c r="AX74">
+        <v>6</v>
+      </c>
+      <c r="AY74">
+        <v>12</v>
+      </c>
+      <c r="AZ74">
+        <v>14</v>
+      </c>
+      <c r="BA74">
+        <v>5</v>
+      </c>
+      <c r="BB74">
+        <v>3</v>
+      </c>
+      <c r="BC74">
+        <v>8</v>
+      </c>
+      <c r="BD74">
+        <v>4.7</v>
+      </c>
+      <c r="BE74">
+        <v>10.75</v>
+      </c>
+      <c r="BF74">
+        <v>1.25</v>
+      </c>
+      <c r="BG74">
+        <v>1.14</v>
+      </c>
+      <c r="BH74">
+        <v>4.35</v>
+      </c>
+      <c r="BI74">
+        <v>1.26</v>
+      </c>
+      <c r="BJ74">
+        <v>3.22</v>
+      </c>
+      <c r="BK74">
+        <v>1.49</v>
+      </c>
+      <c r="BL74">
+        <v>2.36</v>
+      </c>
+      <c r="BM74">
+        <v>1.91</v>
+      </c>
+      <c r="BN74">
+        <v>1.86</v>
+      </c>
+      <c r="BO74">
+        <v>2.32</v>
+      </c>
+      <c r="BP74">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7785874</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45823.39583333334</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>2</v>
+      </c>
+      <c r="O75" t="s">
+        <v>143</v>
+      </c>
+      <c r="P75" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q75">
+        <v>2.35</v>
+      </c>
+      <c r="R75">
+        <v>2.39</v>
+      </c>
+      <c r="S75">
+        <v>4</v>
+      </c>
+      <c r="T75">
+        <v>1.27</v>
+      </c>
+      <c r="U75">
+        <v>3.3</v>
+      </c>
+      <c r="V75">
+        <v>2.25</v>
+      </c>
+      <c r="W75">
+        <v>1.55</v>
+      </c>
+      <c r="X75">
+        <v>5</v>
+      </c>
+      <c r="Y75">
+        <v>1.14</v>
+      </c>
+      <c r="Z75">
+        <v>1.75</v>
+      </c>
+      <c r="AA75">
+        <v>3.7</v>
+      </c>
+      <c r="AB75">
+        <v>3.75</v>
+      </c>
+      <c r="AC75">
+        <v>1.02</v>
+      </c>
+      <c r="AD75">
+        <v>15</v>
+      </c>
+      <c r="AE75">
+        <v>1.19</v>
+      </c>
+      <c r="AF75">
+        <v>4.6</v>
+      </c>
+      <c r="AG75">
+        <v>1.61</v>
+      </c>
+      <c r="AH75">
+        <v>2.25</v>
+      </c>
+      <c r="AI75">
+        <v>1.53</v>
+      </c>
+      <c r="AJ75">
+        <v>2.25</v>
+      </c>
+      <c r="AK75">
+        <v>1.22</v>
+      </c>
+      <c r="AL75">
+        <v>1.25</v>
+      </c>
+      <c r="AM75">
+        <v>2</v>
+      </c>
+      <c r="AN75">
+        <v>1.5</v>
+      </c>
+      <c r="AO75">
+        <v>0.75</v>
+      </c>
+      <c r="AP75">
+        <v>1.4</v>
+      </c>
+      <c r="AQ75">
+        <v>0.8</v>
+      </c>
+      <c r="AR75">
+        <v>1.82</v>
+      </c>
+      <c r="AS75">
+        <v>1.34</v>
+      </c>
+      <c r="AT75">
+        <v>3.16</v>
+      </c>
+      <c r="AU75">
+        <v>12</v>
+      </c>
+      <c r="AV75">
+        <v>4</v>
+      </c>
+      <c r="AW75">
+        <v>15</v>
+      </c>
+      <c r="AX75">
+        <v>6</v>
+      </c>
+      <c r="AY75">
+        <v>27</v>
+      </c>
+      <c r="AZ75">
+        <v>10</v>
+      </c>
+      <c r="BA75">
+        <v>8</v>
+      </c>
+      <c r="BB75">
+        <v>1</v>
+      </c>
+      <c r="BC75">
+        <v>9</v>
+      </c>
+      <c r="BD75">
+        <v>1.65</v>
+      </c>
+      <c r="BE75">
+        <v>6.7</v>
+      </c>
+      <c r="BF75">
+        <v>2.25</v>
+      </c>
+      <c r="BG75">
+        <v>1.13</v>
+      </c>
+      <c r="BH75">
+        <v>4.75</v>
+      </c>
+      <c r="BI75">
+        <v>1.26</v>
+      </c>
+      <c r="BJ75">
+        <v>3.35</v>
+      </c>
+      <c r="BK75">
+        <v>1.43</v>
+      </c>
+      <c r="BL75">
+        <v>2.55</v>
+      </c>
+      <c r="BM75">
+        <v>1.76</v>
+      </c>
+      <c r="BN75">
+        <v>1.98</v>
+      </c>
+      <c r="BO75">
+        <v>2.18</v>
+      </c>
+      <c r="BP75">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="199">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -448,6 +448,18 @@
     <t>['46']</t>
   </si>
   <si>
+    <t>['26', '53', '45+1']</t>
+  </si>
+  <si>
+    <t>['90+2', '73']</t>
+  </si>
+  <si>
+    <t>['37', '90']</t>
+  </si>
+  <si>
+    <t>['64', '81']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -587,6 +599,18 @@
   </si>
   <si>
     <t>['24']</t>
+  </si>
+  <si>
+    <t>['33', '49', '83', '90+8']</t>
+  </si>
+  <si>
+    <t>['38', '75']</t>
+  </si>
+  <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['6', '13']</t>
   </si>
 </sst>
 </file>
@@ -948,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1204,7 +1228,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1282,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>0.8</v>
@@ -1616,7 +1640,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1697,7 +1721,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ4">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1822,7 +1846,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2440,7 +2464,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2518,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
         <v>2</v>
@@ -2646,7 +2670,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2724,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2852,7 +2876,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -2930,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
         <v>1.4</v>
@@ -3058,7 +3082,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3345,7 +3369,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3470,7 +3494,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3757,7 +3781,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3882,7 +3906,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4088,7 +4112,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Q16">
         <v>3.1</v>
@@ -4166,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ16">
         <v>0.75</v>
@@ -4294,7 +4318,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4500,7 +4524,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4578,10 +4602,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR18">
         <v>2.04</v>
@@ -4787,7 +4811,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR19">
         <v>1.89</v>
@@ -4912,7 +4936,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5118,7 +5142,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5324,7 +5348,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5402,7 +5426,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ22">
         <v>0.8</v>
@@ -5530,7 +5554,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5736,7 +5760,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6020,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25">
         <v>0.8</v>
@@ -6148,7 +6172,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6354,7 +6378,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6638,7 +6662,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ28">
         <v>1.33</v>
@@ -6766,7 +6790,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -6847,7 +6871,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR29">
         <v>1.81</v>
@@ -6972,7 +6996,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7256,7 +7280,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ31">
         <v>1.4</v>
@@ -7384,7 +7408,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7462,7 +7486,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ32">
         <v>2.2</v>
@@ -7590,7 +7614,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -7671,7 +7695,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR33">
         <v>0.71</v>
@@ -7877,7 +7901,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8002,7 +8026,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8208,7 +8232,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8620,7 +8644,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8826,7 +8850,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -8904,7 +8928,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
         <v>0.75</v>
@@ -9113,7 +9137,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ40">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR40">
         <v>1.57</v>
@@ -9238,7 +9262,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9728,7 +9752,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ43">
         <v>2.2</v>
@@ -9856,7 +9880,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10062,7 +10086,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10140,10 +10164,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR45">
         <v>1.05</v>
@@ -10268,7 +10292,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10349,7 +10373,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR46">
         <v>2.41</v>
@@ -10474,7 +10498,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10680,7 +10704,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10758,7 +10782,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -10886,7 +10910,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11298,7 +11322,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Q51">
         <v>2.33</v>
@@ -11379,7 +11403,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ51">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR51">
         <v>1.23</v>
@@ -11585,7 +11609,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AR52">
         <v>1.9</v>
@@ -12122,7 +12146,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12406,7 +12430,7 @@
         <v>2.33</v>
       </c>
       <c r="AP56">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ56">
         <v>1.6</v>
@@ -12612,7 +12636,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -12740,7 +12764,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12818,7 +12842,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
         <v>2.2</v>
@@ -13027,7 +13051,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ59">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -13152,7 +13176,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13230,7 +13254,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ60">
         <v>2</v>
@@ -13358,7 +13382,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13564,7 +13588,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13642,10 +13666,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ62">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR62">
         <v>1.09</v>
@@ -13770,7 +13794,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -13848,7 +13872,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>1.2</v>
@@ -13976,7 +14000,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14057,7 +14081,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.22</v>
@@ -14182,7 +14206,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14594,7 +14618,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14800,7 +14824,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15212,7 +15236,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15624,7 +15648,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15830,7 +15854,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -15923,22 +15947,22 @@
         <v>3.57</v>
       </c>
       <c r="AU73">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW73">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY73">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ73">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA73">
         <v>10</v>
@@ -16036,7 +16060,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16242,7 +16266,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16335,22 +16359,22 @@
         <v>3.16</v>
       </c>
       <c r="AU75">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AV75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX75">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY75">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AZ75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA75">
         <v>8</v>
@@ -16399,6 +16423,1036 @@
       </c>
       <c r="BP75">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7785875</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45823.45833333334</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>70</v>
+      </c>
+      <c r="H76" t="s">
+        <v>73</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>3</v>
+      </c>
+      <c r="L76">
+        <v>3</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>7</v>
+      </c>
+      <c r="O76" t="s">
+        <v>144</v>
+      </c>
+      <c r="P76" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q76">
+        <v>2.6</v>
+      </c>
+      <c r="R76">
+        <v>2.49</v>
+      </c>
+      <c r="S76">
+        <v>3.45</v>
+      </c>
+      <c r="T76">
+        <v>1.29</v>
+      </c>
+      <c r="U76">
+        <v>3.3</v>
+      </c>
+      <c r="V76">
+        <v>2.23</v>
+      </c>
+      <c r="W76">
+        <v>1.6</v>
+      </c>
+      <c r="X76">
+        <v>5.3</v>
+      </c>
+      <c r="Y76">
+        <v>1.1</v>
+      </c>
+      <c r="Z76">
+        <v>2.07</v>
+      </c>
+      <c r="AA76">
+        <v>3.7</v>
+      </c>
+      <c r="AB76">
+        <v>2.88</v>
+      </c>
+      <c r="AC76">
+        <v>1.03</v>
+      </c>
+      <c r="AD76">
+        <v>12.8</v>
+      </c>
+      <c r="AE76">
+        <v>1.13</v>
+      </c>
+      <c r="AF76">
+        <v>4.6</v>
+      </c>
+      <c r="AG76">
+        <v>1.57</v>
+      </c>
+      <c r="AH76">
+        <v>2.15</v>
+      </c>
+      <c r="AI76">
+        <v>1.45</v>
+      </c>
+      <c r="AJ76">
+        <v>2.54</v>
+      </c>
+      <c r="AK76">
+        <v>1.29</v>
+      </c>
+      <c r="AL76">
+        <v>1.29</v>
+      </c>
+      <c r="AM76">
+        <v>1.5</v>
+      </c>
+      <c r="AN76">
+        <v>2</v>
+      </c>
+      <c r="AO76">
+        <v>1.5</v>
+      </c>
+      <c r="AP76">
+        <v>1.5</v>
+      </c>
+      <c r="AQ76">
+        <v>1.8</v>
+      </c>
+      <c r="AR76">
+        <v>2.38</v>
+      </c>
+      <c r="AS76">
+        <v>1.53</v>
+      </c>
+      <c r="AT76">
+        <v>3.91</v>
+      </c>
+      <c r="AU76">
+        <v>4</v>
+      </c>
+      <c r="AV76">
+        <v>6</v>
+      </c>
+      <c r="AW76">
+        <v>1</v>
+      </c>
+      <c r="AX76">
+        <v>1</v>
+      </c>
+      <c r="AY76">
+        <v>5</v>
+      </c>
+      <c r="AZ76">
+        <v>7</v>
+      </c>
+      <c r="BA76">
+        <v>5</v>
+      </c>
+      <c r="BB76">
+        <v>7</v>
+      </c>
+      <c r="BC76">
+        <v>12</v>
+      </c>
+      <c r="BD76">
+        <v>1.71</v>
+      </c>
+      <c r="BE76">
+        <v>8.6</v>
+      </c>
+      <c r="BF76">
+        <v>2.47</v>
+      </c>
+      <c r="BG76">
+        <v>1.19</v>
+      </c>
+      <c r="BH76">
+        <v>3.92</v>
+      </c>
+      <c r="BI76">
+        <v>1.33</v>
+      </c>
+      <c r="BJ76">
+        <v>2.8</v>
+      </c>
+      <c r="BK76">
+        <v>1.63</v>
+      </c>
+      <c r="BL76">
+        <v>2.24</v>
+      </c>
+      <c r="BM76">
+        <v>2.04</v>
+      </c>
+      <c r="BN76">
+        <v>1.75</v>
+      </c>
+      <c r="BO76">
+        <v>2.32</v>
+      </c>
+      <c r="BP76">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7785877</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45823.5</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>84</v>
+      </c>
+      <c r="H77" t="s">
+        <v>80</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>4</v>
+      </c>
+      <c r="O77" t="s">
+        <v>145</v>
+      </c>
+      <c r="P77" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q77">
+        <v>3.97</v>
+      </c>
+      <c r="R77">
+        <v>2.3</v>
+      </c>
+      <c r="S77">
+        <v>2.5</v>
+      </c>
+      <c r="T77">
+        <v>1.3</v>
+      </c>
+      <c r="U77">
+        <v>3.2</v>
+      </c>
+      <c r="V77">
+        <v>2.61</v>
+      </c>
+      <c r="W77">
+        <v>1.48</v>
+      </c>
+      <c r="X77">
+        <v>5.6</v>
+      </c>
+      <c r="Y77">
+        <v>1.08</v>
+      </c>
+      <c r="Z77">
+        <v>3.3</v>
+      </c>
+      <c r="AA77">
+        <v>3.6</v>
+      </c>
+      <c r="AB77">
+        <v>2.05</v>
+      </c>
+      <c r="AC77">
+        <v>1.03</v>
+      </c>
+      <c r="AD77">
+        <v>11</v>
+      </c>
+      <c r="AE77">
+        <v>1.2</v>
+      </c>
+      <c r="AF77">
+        <v>4.3</v>
+      </c>
+      <c r="AG77">
+        <v>1.7</v>
+      </c>
+      <c r="AH77">
+        <v>2.21</v>
+      </c>
+      <c r="AI77">
+        <v>1.56</v>
+      </c>
+      <c r="AJ77">
+        <v>2.27</v>
+      </c>
+      <c r="AK77">
+        <v>1.3</v>
+      </c>
+      <c r="AL77">
+        <v>1.3</v>
+      </c>
+      <c r="AM77">
+        <v>1.3</v>
+      </c>
+      <c r="AN77">
+        <v>0.25</v>
+      </c>
+      <c r="AO77">
+        <v>0</v>
+      </c>
+      <c r="AP77">
+        <v>0.4</v>
+      </c>
+      <c r="AQ77">
+        <v>0.2</v>
+      </c>
+      <c r="AR77">
+        <v>0.93</v>
+      </c>
+      <c r="AS77">
+        <v>1.29</v>
+      </c>
+      <c r="AT77">
+        <v>2.22</v>
+      </c>
+      <c r="AU77">
+        <v>4</v>
+      </c>
+      <c r="AV77">
+        <v>5</v>
+      </c>
+      <c r="AW77">
+        <v>9</v>
+      </c>
+      <c r="AX77">
+        <v>9</v>
+      </c>
+      <c r="AY77">
+        <v>13</v>
+      </c>
+      <c r="AZ77">
+        <v>14</v>
+      </c>
+      <c r="BA77">
+        <v>6</v>
+      </c>
+      <c r="BB77">
+        <v>3</v>
+      </c>
+      <c r="BC77">
+        <v>9</v>
+      </c>
+      <c r="BD77">
+        <v>2.47</v>
+      </c>
+      <c r="BE77">
+        <v>6.75</v>
+      </c>
+      <c r="BF77">
+        <v>1.81</v>
+      </c>
+      <c r="BG77">
+        <v>1.14</v>
+      </c>
+      <c r="BH77">
+        <v>4.6</v>
+      </c>
+      <c r="BI77">
+        <v>1.33</v>
+      </c>
+      <c r="BJ77">
+        <v>3.22</v>
+      </c>
+      <c r="BK77">
+        <v>1.62</v>
+      </c>
+      <c r="BL77">
+        <v>2.42</v>
+      </c>
+      <c r="BM77">
+        <v>1.81</v>
+      </c>
+      <c r="BN77">
+        <v>1.94</v>
+      </c>
+      <c r="BO77">
+        <v>2.24</v>
+      </c>
+      <c r="BP77">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7785878</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45823.5</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s">
+        <v>72</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="O78" t="s">
+        <v>110</v>
+      </c>
+      <c r="P78" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q78">
+        <v>3.84</v>
+      </c>
+      <c r="R78">
+        <v>2.25</v>
+      </c>
+      <c r="S78">
+        <v>2.54</v>
+      </c>
+      <c r="T78">
+        <v>1.3</v>
+      </c>
+      <c r="U78">
+        <v>3.22</v>
+      </c>
+      <c r="V78">
+        <v>2.3</v>
+      </c>
+      <c r="W78">
+        <v>1.5</v>
+      </c>
+      <c r="X78">
+        <v>5.8</v>
+      </c>
+      <c r="Y78">
+        <v>1.07</v>
+      </c>
+      <c r="Z78">
+        <v>2.9</v>
+      </c>
+      <c r="AA78">
+        <v>3.4</v>
+      </c>
+      <c r="AB78">
+        <v>2.13</v>
+      </c>
+      <c r="AC78">
+        <v>1.02</v>
+      </c>
+      <c r="AD78">
+        <v>12</v>
+      </c>
+      <c r="AE78">
+        <v>1.22</v>
+      </c>
+      <c r="AF78">
+        <v>3.95</v>
+      </c>
+      <c r="AG78">
+        <v>1.73</v>
+      </c>
+      <c r="AH78">
+        <v>2.16</v>
+      </c>
+      <c r="AI78">
+        <v>1.6</v>
+      </c>
+      <c r="AJ78">
+        <v>2.25</v>
+      </c>
+      <c r="AK78">
+        <v>1.3</v>
+      </c>
+      <c r="AL78">
+        <v>1.3</v>
+      </c>
+      <c r="AM78">
+        <v>1.33</v>
+      </c>
+      <c r="AN78">
+        <v>2</v>
+      </c>
+      <c r="AO78">
+        <v>0.75</v>
+      </c>
+      <c r="AP78">
+        <v>1.83</v>
+      </c>
+      <c r="AQ78">
+        <v>0.8</v>
+      </c>
+      <c r="AR78">
+        <v>1.42</v>
+      </c>
+      <c r="AS78">
+        <v>1.48</v>
+      </c>
+      <c r="AT78">
+        <v>2.9</v>
+      </c>
+      <c r="AU78">
+        <v>2</v>
+      </c>
+      <c r="AV78">
+        <v>6</v>
+      </c>
+      <c r="AW78">
+        <v>5</v>
+      </c>
+      <c r="AX78">
+        <v>6</v>
+      </c>
+      <c r="AY78">
+        <v>7</v>
+      </c>
+      <c r="AZ78">
+        <v>12</v>
+      </c>
+      <c r="BA78">
+        <v>3</v>
+      </c>
+      <c r="BB78">
+        <v>13</v>
+      </c>
+      <c r="BC78">
+        <v>16</v>
+      </c>
+      <c r="BD78">
+        <v>2.52</v>
+      </c>
+      <c r="BE78">
+        <v>7.8</v>
+      </c>
+      <c r="BF78">
+        <v>1.67</v>
+      </c>
+      <c r="BG78">
+        <v>1.16</v>
+      </c>
+      <c r="BH78">
+        <v>4.5</v>
+      </c>
+      <c r="BI78">
+        <v>1.22</v>
+      </c>
+      <c r="BJ78">
+        <v>3.3</v>
+      </c>
+      <c r="BK78">
+        <v>1.43</v>
+      </c>
+      <c r="BL78">
+        <v>2.45</v>
+      </c>
+      <c r="BM78">
+        <v>1.74</v>
+      </c>
+      <c r="BN78">
+        <v>1.96</v>
+      </c>
+      <c r="BO78">
+        <v>2.15</v>
+      </c>
+      <c r="BP78">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7785879</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45823.5</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s">
+        <v>81</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>3</v>
+      </c>
+      <c r="O79" t="s">
+        <v>146</v>
+      </c>
+      <c r="P79" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q79">
+        <v>2.15</v>
+      </c>
+      <c r="R79">
+        <v>2.32</v>
+      </c>
+      <c r="S79">
+        <v>4.25</v>
+      </c>
+      <c r="T79">
+        <v>1.25</v>
+      </c>
+      <c r="U79">
+        <v>3.3</v>
+      </c>
+      <c r="V79">
+        <v>2.36</v>
+      </c>
+      <c r="W79">
+        <v>1.55</v>
+      </c>
+      <c r="X79">
+        <v>5.5</v>
+      </c>
+      <c r="Y79">
+        <v>1.12</v>
+      </c>
+      <c r="Z79">
+        <v>1.61</v>
+      </c>
+      <c r="AA79">
+        <v>3.82</v>
+      </c>
+      <c r="AB79">
+        <v>4.28</v>
+      </c>
+      <c r="AC79">
+        <v>1.01</v>
+      </c>
+      <c r="AD79">
+        <v>11</v>
+      </c>
+      <c r="AE79">
+        <v>1.2</v>
+      </c>
+      <c r="AF79">
+        <v>4</v>
+      </c>
+      <c r="AG79">
+        <v>1.62</v>
+      </c>
+      <c r="AH79">
+        <v>2.25</v>
+      </c>
+      <c r="AI79">
+        <v>1.65</v>
+      </c>
+      <c r="AJ79">
+        <v>2.14</v>
+      </c>
+      <c r="AK79">
+        <v>1.25</v>
+      </c>
+      <c r="AL79">
+        <v>1.25</v>
+      </c>
+      <c r="AM79">
+        <v>2.1</v>
+      </c>
+      <c r="AN79">
+        <v>1.25</v>
+      </c>
+      <c r="AO79">
+        <v>0.2</v>
+      </c>
+      <c r="AP79">
+        <v>1.6</v>
+      </c>
+      <c r="AQ79">
+        <v>0.17</v>
+      </c>
+      <c r="AR79">
+        <v>1.13</v>
+      </c>
+      <c r="AS79">
+        <v>1.11</v>
+      </c>
+      <c r="AT79">
+        <v>2.24</v>
+      </c>
+      <c r="AU79">
+        <v>4</v>
+      </c>
+      <c r="AV79">
+        <v>5</v>
+      </c>
+      <c r="AW79">
+        <v>7</v>
+      </c>
+      <c r="AX79">
+        <v>2</v>
+      </c>
+      <c r="AY79">
+        <v>11</v>
+      </c>
+      <c r="AZ79">
+        <v>7</v>
+      </c>
+      <c r="BA79">
+        <v>5</v>
+      </c>
+      <c r="BB79">
+        <v>3</v>
+      </c>
+      <c r="BC79">
+        <v>8</v>
+      </c>
+      <c r="BD79">
+        <v>1.53</v>
+      </c>
+      <c r="BE79">
+        <v>8.4</v>
+      </c>
+      <c r="BF79">
+        <v>4.06</v>
+      </c>
+      <c r="BG79">
+        <v>1.16</v>
+      </c>
+      <c r="BH79">
+        <v>3.8</v>
+      </c>
+      <c r="BI79">
+        <v>1.38</v>
+      </c>
+      <c r="BJ79">
+        <v>3.1</v>
+      </c>
+      <c r="BK79">
+        <v>1.66</v>
+      </c>
+      <c r="BL79">
+        <v>2.34</v>
+      </c>
+      <c r="BM79">
+        <v>1.85</v>
+      </c>
+      <c r="BN79">
+        <v>1.85</v>
+      </c>
+      <c r="BO79">
+        <v>2.32</v>
+      </c>
+      <c r="BP79">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7785880</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45823.59375</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>76</v>
+      </c>
+      <c r="H80" t="s">
+        <v>74</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80">
+        <v>4</v>
+      </c>
+      <c r="O80" t="s">
+        <v>147</v>
+      </c>
+      <c r="P80" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q80">
+        <v>2.1</v>
+      </c>
+      <c r="R80">
+        <v>2.2</v>
+      </c>
+      <c r="S80">
+        <v>4</v>
+      </c>
+      <c r="T80">
+        <v>1.3</v>
+      </c>
+      <c r="U80">
+        <v>3.2</v>
+      </c>
+      <c r="V80">
+        <v>2.3</v>
+      </c>
+      <c r="W80">
+        <v>1.53</v>
+      </c>
+      <c r="X80">
+        <v>5.5</v>
+      </c>
+      <c r="Y80">
+        <v>1.13</v>
+      </c>
+      <c r="Z80">
+        <v>1.96</v>
+      </c>
+      <c r="AA80">
+        <v>3.6</v>
+      </c>
+      <c r="AB80">
+        <v>3.2</v>
+      </c>
+      <c r="AC80">
+        <v>1.03</v>
+      </c>
+      <c r="AD80">
+        <v>11.9</v>
+      </c>
+      <c r="AE80">
+        <v>1.14</v>
+      </c>
+      <c r="AF80">
+        <v>4.4</v>
+      </c>
+      <c r="AG80">
+        <v>1.65</v>
+      </c>
+      <c r="AH80">
+        <v>2.2</v>
+      </c>
+      <c r="AI80">
+        <v>1.53</v>
+      </c>
+      <c r="AJ80">
+        <v>2.29</v>
+      </c>
+      <c r="AK80">
+        <v>1.22</v>
+      </c>
+      <c r="AL80">
+        <v>1.3</v>
+      </c>
+      <c r="AM80">
+        <v>1.83</v>
+      </c>
+      <c r="AN80">
+        <v>1.8</v>
+      </c>
+      <c r="AO80">
+        <v>1</v>
+      </c>
+      <c r="AP80">
+        <v>1.67</v>
+      </c>
+      <c r="AQ80">
+        <v>1</v>
+      </c>
+      <c r="AR80">
+        <v>1.55</v>
+      </c>
+      <c r="AS80">
+        <v>1.53</v>
+      </c>
+      <c r="AT80">
+        <v>3.08</v>
+      </c>
+      <c r="AU80">
+        <v>6</v>
+      </c>
+      <c r="AV80">
+        <v>3</v>
+      </c>
+      <c r="AW80">
+        <v>4</v>
+      </c>
+      <c r="AX80">
+        <v>8</v>
+      </c>
+      <c r="AY80">
+        <v>10</v>
+      </c>
+      <c r="AZ80">
+        <v>11</v>
+      </c>
+      <c r="BA80">
+        <v>4</v>
+      </c>
+      <c r="BB80">
+        <v>4</v>
+      </c>
+      <c r="BC80">
+        <v>8</v>
+      </c>
+      <c r="BD80">
+        <v>1.64</v>
+      </c>
+      <c r="BE80">
+        <v>10.5</v>
+      </c>
+      <c r="BF80">
+        <v>2.47</v>
+      </c>
+      <c r="BG80">
+        <v>1.1</v>
+      </c>
+      <c r="BH80">
+        <v>4.9</v>
+      </c>
+      <c r="BI80">
+        <v>1.21</v>
+      </c>
+      <c r="BJ80">
+        <v>3.8</v>
+      </c>
+      <c r="BK80">
+        <v>1.46</v>
+      </c>
+      <c r="BL80">
+        <v>2.77</v>
+      </c>
+      <c r="BM80">
+        <v>1.63</v>
+      </c>
+      <c r="BN80">
+        <v>2.19</v>
+      </c>
+      <c r="BO80">
+        <v>1.97</v>
+      </c>
+      <c r="BP80">
+        <v>1.78</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -454,7 +454,7 @@
     <t>['90+2', '73']</t>
   </si>
   <si>
-    <t>['37', '90']</t>
+    <t>['37', '90+3']</t>
   </si>
   <si>
     <t>['64', '81']</t>
@@ -16359,22 +16359,22 @@
         <v>3.16</v>
       </c>
       <c r="AU75">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AV75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW75">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX75">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY75">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AZ75">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BA75">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="211">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,6 +460,27 @@
     <t>['64', '81']</t>
   </si>
   <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['20', '18', '59']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['43', '35']</t>
+  </si>
+  <si>
+    <t>['27', '82', '90+3']</t>
+  </si>
+  <si>
+    <t>['58', '68', '85']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -487,9 +508,6 @@
     <t>['33', '90+1']</t>
   </si>
   <si>
-    <t>['88']</t>
-  </si>
-  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -611,6 +629,24 @@
   </si>
   <si>
     <t>['6', '13']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['65', '78', '89']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['30', '52', '57', '83']</t>
+  </si>
+  <si>
+    <t>['29', '78']</t>
+  </si>
+  <si>
+    <t>['39', '64']</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP80"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1228,7 +1264,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1309,7 +1345,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1512,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1640,7 +1676,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1718,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4">
         <v>0.17</v>
@@ -1846,7 +1882,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1924,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ5">
         <v>0.8</v>
@@ -2130,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2339,7 +2375,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2464,7 +2500,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2670,7 +2706,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2876,7 +2912,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -2957,7 +2993,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3082,7 +3118,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3163,7 +3199,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3366,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12">
         <v>1.8</v>
@@ -3494,7 +3530,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3572,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ13">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3778,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ14">
         <v>0.8</v>
@@ -3906,7 +3942,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4112,7 +4148,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Q16">
         <v>3.1</v>
@@ -4193,7 +4229,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ16">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4318,7 +4354,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4396,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -4524,7 +4560,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4808,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
         <v>0.2</v>
@@ -4936,7 +4972,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5014,7 +5050,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ20">
         <v>0.8</v>
@@ -5142,7 +5178,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5220,10 +5256,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.62</v>
@@ -5348,7 +5384,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5429,7 +5465,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ22">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -5554,7 +5590,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5632,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23">
         <v>2</v>
@@ -5760,7 +5796,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5841,7 +5877,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ24">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>0.96</v>
@@ -6047,7 +6083,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR25">
         <v>1.44</v>
@@ -6172,7 +6208,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6250,7 +6286,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ26">
         <v>2</v>
@@ -6378,7 +6414,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6456,7 +6492,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6665,7 +6701,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0.62</v>
@@ -6790,7 +6826,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -6996,7 +7032,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7074,7 +7110,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ30">
         <v>1.4</v>
@@ -7283,7 +7319,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ31">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
         <v>1.81</v>
@@ -7408,7 +7444,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7489,7 +7525,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ32">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR32">
         <v>1.02</v>
@@ -7614,7 +7650,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -7898,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ34">
         <v>0.2</v>
@@ -8026,7 +8062,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8104,10 +8140,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -8232,7 +8268,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8310,7 +8346,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36">
         <v>1.4</v>
@@ -8519,7 +8555,7 @@
         <v>2</v>
       </c>
       <c r="AQ37">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR37">
         <v>1.82</v>
@@ -8644,7 +8680,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8725,7 +8761,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ38">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR38">
         <v>1.67</v>
@@ -8850,7 +8886,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -8931,7 +8967,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR39">
         <v>1.43</v>
@@ -9134,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>0.17</v>
@@ -9262,7 +9298,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9340,10 +9376,10 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ41">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1.1</v>
@@ -9546,7 +9582,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ42">
         <v>0.8</v>
@@ -9755,7 +9791,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ43">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR43">
         <v>1.63</v>
@@ -9880,7 +9916,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -9961,7 +9997,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ44">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
         <v>1.31</v>
@@ -10086,7 +10122,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10292,7 +10328,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10370,7 +10406,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ46">
         <v>0.8</v>
@@ -10498,7 +10534,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10576,7 +10612,7 @@
         <v>2.33</v>
       </c>
       <c r="AP47">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ47">
         <v>2</v>
@@ -10704,7 +10740,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10910,7 +10946,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -10988,10 +11024,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR49">
         <v>1.32</v>
@@ -11194,7 +11230,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ50">
         <v>1.4</v>
@@ -11322,7 +11358,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Q51">
         <v>2.33</v>
@@ -11400,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ51">
         <v>0.17</v>
@@ -11606,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ52">
         <v>0.2</v>
@@ -11815,7 +11851,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR53">
         <v>2.04</v>
@@ -12018,10 +12054,10 @@
         <v>0.33</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR54">
         <v>1.75</v>
@@ -12146,7 +12182,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12227,7 +12263,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ55">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR55">
         <v>1.75</v>
@@ -12433,7 +12469,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ56">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.81</v>
@@ -12764,7 +12800,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12845,7 +12881,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR58">
         <v>1.66</v>
@@ -13048,7 +13084,7 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ59">
         <v>0.17</v>
@@ -13176,7 +13212,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13382,7 +13418,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13460,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ61">
         <v>0.8</v>
@@ -13588,7 +13624,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13794,7 +13830,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -13875,7 +13911,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>2.64</v>
@@ -14000,7 +14036,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14206,7 +14242,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14284,10 +14320,10 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ65">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR65">
         <v>1.21</v>
@@ -14490,10 +14526,10 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ66">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.27</v>
@@ -14618,7 +14654,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14696,7 +14732,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ67">
         <v>1.4</v>
@@ -14824,7 +14860,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -14902,10 +14938,10 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.7</v>
@@ -15108,10 +15144,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ69">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR69">
         <v>1.65</v>
@@ -15236,7 +15272,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15317,7 +15353,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -15520,10 +15556,10 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ71">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR71">
         <v>1.65</v>
@@ -15648,7 +15684,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15726,10 +15762,10 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ72">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AR72">
         <v>1.45</v>
@@ -15854,7 +15890,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -15932,10 +15968,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ73">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>2.07</v>
@@ -16060,7 +16096,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16266,7 +16302,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16472,7 +16508,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16678,7 +16714,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16884,7 +16920,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -17090,7 +17126,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17296,7 +17332,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17453,6 +17489,1654 @@
       </c>
       <c r="BP80">
         <v>1.78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7785885</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>72</v>
+      </c>
+      <c r="H81" t="s">
+        <v>84</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81" t="s">
+        <v>148</v>
+      </c>
+      <c r="P81" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q81">
+        <v>1.6</v>
+      </c>
+      <c r="R81">
+        <v>2.59</v>
+      </c>
+      <c r="S81">
+        <v>6.5</v>
+      </c>
+      <c r="T81">
+        <v>1.22</v>
+      </c>
+      <c r="U81">
+        <v>3.55</v>
+      </c>
+      <c r="V81">
+        <v>2.15</v>
+      </c>
+      <c r="W81">
+        <v>1.65</v>
+      </c>
+      <c r="X81">
+        <v>4.9</v>
+      </c>
+      <c r="Y81">
+        <v>1.17</v>
+      </c>
+      <c r="Z81">
+        <v>1.4</v>
+      </c>
+      <c r="AA81">
+        <v>4.6</v>
+      </c>
+      <c r="AB81">
+        <v>6.93</v>
+      </c>
+      <c r="AC81">
+        <v>1.02</v>
+      </c>
+      <c r="AD81">
+        <v>14.5</v>
+      </c>
+      <c r="AE81">
+        <v>1.12</v>
+      </c>
+      <c r="AF81">
+        <v>4.75</v>
+      </c>
+      <c r="AG81">
+        <v>1.49</v>
+      </c>
+      <c r="AH81">
+        <v>2.45</v>
+      </c>
+      <c r="AI81">
+        <v>1.67</v>
+      </c>
+      <c r="AJ81">
+        <v>2.06</v>
+      </c>
+      <c r="AK81">
+        <v>1.16</v>
+      </c>
+      <c r="AL81">
+        <v>1.16</v>
+      </c>
+      <c r="AM81">
+        <v>2.88</v>
+      </c>
+      <c r="AN81">
+        <v>2.6</v>
+      </c>
+      <c r="AO81">
+        <v>0.8</v>
+      </c>
+      <c r="AP81">
+        <v>2.33</v>
+      </c>
+      <c r="AQ81">
+        <v>0.83</v>
+      </c>
+      <c r="AR81">
+        <v>1.64</v>
+      </c>
+      <c r="AS81">
+        <v>1.16</v>
+      </c>
+      <c r="AT81">
+        <v>2.8</v>
+      </c>
+      <c r="AU81">
+        <v>3</v>
+      </c>
+      <c r="AV81">
+        <v>2</v>
+      </c>
+      <c r="AW81">
+        <v>6</v>
+      </c>
+      <c r="AX81">
+        <v>4</v>
+      </c>
+      <c r="AY81">
+        <v>9</v>
+      </c>
+      <c r="AZ81">
+        <v>6</v>
+      </c>
+      <c r="BA81">
+        <v>5</v>
+      </c>
+      <c r="BB81">
+        <v>4</v>
+      </c>
+      <c r="BC81">
+        <v>9</v>
+      </c>
+      <c r="BD81">
+        <v>1.34</v>
+      </c>
+      <c r="BE81">
+        <v>7</v>
+      </c>
+      <c r="BF81">
+        <v>3.15</v>
+      </c>
+      <c r="BG81">
+        <v>1.19</v>
+      </c>
+      <c r="BH81">
+        <v>4.1</v>
+      </c>
+      <c r="BI81">
+        <v>1.19</v>
+      </c>
+      <c r="BJ81">
+        <v>3.7</v>
+      </c>
+      <c r="BK81">
+        <v>1.48</v>
+      </c>
+      <c r="BL81">
+        <v>2.71</v>
+      </c>
+      <c r="BM81">
+        <v>1.64</v>
+      </c>
+      <c r="BN81">
+        <v>2.15</v>
+      </c>
+      <c r="BO81">
+        <v>2.03</v>
+      </c>
+      <c r="BP81">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7785898</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>74</v>
+      </c>
+      <c r="H82" t="s">
+        <v>70</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>3</v>
+      </c>
+      <c r="N82">
+        <v>4</v>
+      </c>
+      <c r="O82" t="s">
+        <v>149</v>
+      </c>
+      <c r="P82" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q82">
+        <v>2.11</v>
+      </c>
+      <c r="R82">
+        <v>2.53</v>
+      </c>
+      <c r="S82">
+        <v>4.43</v>
+      </c>
+      <c r="T82">
+        <v>1.22</v>
+      </c>
+      <c r="U82">
+        <v>3.8</v>
+      </c>
+      <c r="V82">
+        <v>2.05</v>
+      </c>
+      <c r="W82">
+        <v>1.68</v>
+      </c>
+      <c r="X82">
+        <v>4.35</v>
+      </c>
+      <c r="Y82">
+        <v>1.2</v>
+      </c>
+      <c r="Z82">
+        <v>1.55</v>
+      </c>
+      <c r="AA82">
+        <v>4</v>
+      </c>
+      <c r="AB82">
+        <v>4.4</v>
+      </c>
+      <c r="AC82">
+        <v>1.02</v>
+      </c>
+      <c r="AD82">
+        <v>19</v>
+      </c>
+      <c r="AE82">
+        <v>1.11</v>
+      </c>
+      <c r="AF82">
+        <v>6.11</v>
+      </c>
+      <c r="AG82">
+        <v>1.37</v>
+      </c>
+      <c r="AH82">
+        <v>2.63</v>
+      </c>
+      <c r="AI82">
+        <v>1.5</v>
+      </c>
+      <c r="AJ82">
+        <v>2.35</v>
+      </c>
+      <c r="AK82">
+        <v>1.24</v>
+      </c>
+      <c r="AL82">
+        <v>1.24</v>
+      </c>
+      <c r="AM82">
+        <v>2.16</v>
+      </c>
+      <c r="AN82">
+        <v>1.6</v>
+      </c>
+      <c r="AO82">
+        <v>1.4</v>
+      </c>
+      <c r="AP82">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82">
+        <v>1.67</v>
+      </c>
+      <c r="AR82">
+        <v>1.71</v>
+      </c>
+      <c r="AS82">
+        <v>1.26</v>
+      </c>
+      <c r="AT82">
+        <v>2.97</v>
+      </c>
+      <c r="AU82">
+        <v>3</v>
+      </c>
+      <c r="AV82">
+        <v>7</v>
+      </c>
+      <c r="AW82">
+        <v>3</v>
+      </c>
+      <c r="AX82">
+        <v>4</v>
+      </c>
+      <c r="AY82">
+        <v>6</v>
+      </c>
+      <c r="AZ82">
+        <v>11</v>
+      </c>
+      <c r="BA82">
+        <v>7</v>
+      </c>
+      <c r="BB82">
+        <v>5</v>
+      </c>
+      <c r="BC82">
+        <v>12</v>
+      </c>
+      <c r="BD82">
+        <v>1.57</v>
+      </c>
+      <c r="BE82">
+        <v>6.75</v>
+      </c>
+      <c r="BF82">
+        <v>2.55</v>
+      </c>
+      <c r="BG82">
+        <v>1.19</v>
+      </c>
+      <c r="BH82">
+        <v>4.5</v>
+      </c>
+      <c r="BI82">
+        <v>1.24</v>
+      </c>
+      <c r="BJ82">
+        <v>3.34</v>
+      </c>
+      <c r="BK82">
+        <v>1.49</v>
+      </c>
+      <c r="BL82">
+        <v>2.39</v>
+      </c>
+      <c r="BM82">
+        <v>1.81</v>
+      </c>
+      <c r="BN82">
+        <v>1.95</v>
+      </c>
+      <c r="BO82">
+        <v>2.27</v>
+      </c>
+      <c r="BP82">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7785896</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>73</v>
+      </c>
+      <c r="H83" t="s">
+        <v>75</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="O83" t="s">
+        <v>89</v>
+      </c>
+      <c r="P83" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q83">
+        <v>2.85</v>
+      </c>
+      <c r="R83">
+        <v>2.3</v>
+      </c>
+      <c r="S83">
+        <v>3</v>
+      </c>
+      <c r="T83">
+        <v>1.25</v>
+      </c>
+      <c r="U83">
+        <v>3.75</v>
+      </c>
+      <c r="V83">
+        <v>2.14</v>
+      </c>
+      <c r="W83">
+        <v>1.66</v>
+      </c>
+      <c r="X83">
+        <v>4.5</v>
+      </c>
+      <c r="Y83">
+        <v>1.16</v>
+      </c>
+      <c r="Z83">
+        <v>2.38</v>
+      </c>
+      <c r="AA83">
+        <v>3.6</v>
+      </c>
+      <c r="AB83">
+        <v>2.5</v>
+      </c>
+      <c r="AC83">
+        <v>1.02</v>
+      </c>
+      <c r="AD83">
+        <v>14</v>
+      </c>
+      <c r="AE83">
+        <v>1.13</v>
+      </c>
+      <c r="AF83">
+        <v>5</v>
+      </c>
+      <c r="AG83">
+        <v>1.49</v>
+      </c>
+      <c r="AH83">
+        <v>2.5</v>
+      </c>
+      <c r="AI83">
+        <v>1.52</v>
+      </c>
+      <c r="AJ83">
+        <v>2.43</v>
+      </c>
+      <c r="AK83">
+        <v>1.22</v>
+      </c>
+      <c r="AL83">
+        <v>1.26</v>
+      </c>
+      <c r="AM83">
+        <v>1.57</v>
+      </c>
+      <c r="AN83">
+        <v>1.4</v>
+      </c>
+      <c r="AO83">
+        <v>2.2</v>
+      </c>
+      <c r="AP83">
+        <v>1.17</v>
+      </c>
+      <c r="AQ83">
+        <v>2.33</v>
+      </c>
+      <c r="AR83">
+        <v>1.67</v>
+      </c>
+      <c r="AS83">
+        <v>1.7</v>
+      </c>
+      <c r="AT83">
+        <v>3.37</v>
+      </c>
+      <c r="AU83">
+        <v>6</v>
+      </c>
+      <c r="AV83">
+        <v>4</v>
+      </c>
+      <c r="AW83">
+        <v>5</v>
+      </c>
+      <c r="AX83">
+        <v>10</v>
+      </c>
+      <c r="AY83">
+        <v>11</v>
+      </c>
+      <c r="AZ83">
+        <v>14</v>
+      </c>
+      <c r="BA83">
+        <v>1</v>
+      </c>
+      <c r="BB83">
+        <v>2</v>
+      </c>
+      <c r="BC83">
+        <v>3</v>
+      </c>
+      <c r="BD83">
+        <v>1.95</v>
+      </c>
+      <c r="BE83">
+        <v>6.75</v>
+      </c>
+      <c r="BF83">
+        <v>2.18</v>
+      </c>
+      <c r="BG83">
+        <v>1.14</v>
+      </c>
+      <c r="BH83">
+        <v>4.45</v>
+      </c>
+      <c r="BI83">
+        <v>1.26</v>
+      </c>
+      <c r="BJ83">
+        <v>3.15</v>
+      </c>
+      <c r="BK83">
+        <v>1.52</v>
+      </c>
+      <c r="BL83">
+        <v>2.39</v>
+      </c>
+      <c r="BM83">
+        <v>1.8</v>
+      </c>
+      <c r="BN83">
+        <v>1.91</v>
+      </c>
+      <c r="BO83">
+        <v>2.32</v>
+      </c>
+      <c r="BP83">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7785884</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
+        <v>80</v>
+      </c>
+      <c r="H84" t="s">
+        <v>83</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>3</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>4</v>
+      </c>
+      <c r="O84" t="s">
+        <v>150</v>
+      </c>
+      <c r="P84" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q84">
+        <v>2.67</v>
+      </c>
+      <c r="R84">
+        <v>2.24</v>
+      </c>
+      <c r="S84">
+        <v>3.5</v>
+      </c>
+      <c r="T84">
+        <v>1.33</v>
+      </c>
+      <c r="U84">
+        <v>3.31</v>
+      </c>
+      <c r="V84">
+        <v>2.45</v>
+      </c>
+      <c r="W84">
+        <v>1.55</v>
+      </c>
+      <c r="X84">
+        <v>5.25</v>
+      </c>
+      <c r="Y84">
+        <v>1.09</v>
+      </c>
+      <c r="Z84">
+        <v>2.15</v>
+      </c>
+      <c r="AA84">
+        <v>3.35</v>
+      </c>
+      <c r="AB84">
+        <v>2.92</v>
+      </c>
+      <c r="AC84">
+        <v>1.01</v>
+      </c>
+      <c r="AD84">
+        <v>11.5</v>
+      </c>
+      <c r="AE84">
+        <v>1.16</v>
+      </c>
+      <c r="AF84">
+        <v>3.9</v>
+      </c>
+      <c r="AG84">
+        <v>1.72</v>
+      </c>
+      <c r="AH84">
+        <v>1.99</v>
+      </c>
+      <c r="AI84">
+        <v>1.55</v>
+      </c>
+      <c r="AJ84">
+        <v>2.23</v>
+      </c>
+      <c r="AK84">
+        <v>1.22</v>
+      </c>
+      <c r="AL84">
+        <v>1.28</v>
+      </c>
+      <c r="AM84">
+        <v>1.72</v>
+      </c>
+      <c r="AN84">
+        <v>2.4</v>
+      </c>
+      <c r="AO84">
+        <v>1.6</v>
+      </c>
+      <c r="AP84">
+        <v>2.5</v>
+      </c>
+      <c r="AQ84">
+        <v>1.33</v>
+      </c>
+      <c r="AR84">
+        <v>1.45</v>
+      </c>
+      <c r="AS84">
+        <v>1.03</v>
+      </c>
+      <c r="AT84">
+        <v>2.48</v>
+      </c>
+      <c r="AU84">
+        <v>12</v>
+      </c>
+      <c r="AV84">
+        <v>6</v>
+      </c>
+      <c r="AW84">
+        <v>5</v>
+      </c>
+      <c r="AX84">
+        <v>4</v>
+      </c>
+      <c r="AY84">
+        <v>17</v>
+      </c>
+      <c r="AZ84">
+        <v>10</v>
+      </c>
+      <c r="BA84">
+        <v>2</v>
+      </c>
+      <c r="BB84">
+        <v>4</v>
+      </c>
+      <c r="BC84">
+        <v>6</v>
+      </c>
+      <c r="BD84">
+        <v>1.67</v>
+      </c>
+      <c r="BE84">
+        <v>6.75</v>
+      </c>
+      <c r="BF84">
+        <v>2.33</v>
+      </c>
+      <c r="BG84">
+        <v>1.21</v>
+      </c>
+      <c r="BH84">
+        <v>3.9</v>
+      </c>
+      <c r="BI84">
+        <v>1.36</v>
+      </c>
+      <c r="BJ84">
+        <v>2.8</v>
+      </c>
+      <c r="BK84">
+        <v>1.64</v>
+      </c>
+      <c r="BL84">
+        <v>2.05</v>
+      </c>
+      <c r="BM84">
+        <v>2.13</v>
+      </c>
+      <c r="BN84">
+        <v>1.77</v>
+      </c>
+      <c r="BO84">
+        <v>2.4</v>
+      </c>
+      <c r="BP84">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7785897</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s">
+        <v>79</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <v>5</v>
+      </c>
+      <c r="O85" t="s">
+        <v>151</v>
+      </c>
+      <c r="P85" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q85">
+        <v>4.1</v>
+      </c>
+      <c r="R85">
+        <v>2.28</v>
+      </c>
+      <c r="S85">
+        <v>2.43</v>
+      </c>
+      <c r="T85">
+        <v>1.28</v>
+      </c>
+      <c r="U85">
+        <v>3.25</v>
+      </c>
+      <c r="V85">
+        <v>2.25</v>
+      </c>
+      <c r="W85">
+        <v>1.55</v>
+      </c>
+      <c r="X85">
+        <v>5.5</v>
+      </c>
+      <c r="Y85">
+        <v>1.14</v>
+      </c>
+      <c r="Z85">
+        <v>3.56</v>
+      </c>
+      <c r="AA85">
+        <v>3.4</v>
+      </c>
+      <c r="AB85">
+        <v>1.96</v>
+      </c>
+      <c r="AC85">
+        <v>1.03</v>
+      </c>
+      <c r="AD85">
+        <v>12.8</v>
+      </c>
+      <c r="AE85">
+        <v>1.2</v>
+      </c>
+      <c r="AF85">
+        <v>4.33</v>
+      </c>
+      <c r="AG85">
+        <v>1.64</v>
+      </c>
+      <c r="AH85">
+        <v>2.29</v>
+      </c>
+      <c r="AI85">
+        <v>1.53</v>
+      </c>
+      <c r="AJ85">
+        <v>2.4</v>
+      </c>
+      <c r="AK85">
+        <v>1.28</v>
+      </c>
+      <c r="AL85">
+        <v>1.25</v>
+      </c>
+      <c r="AM85">
+        <v>1.28</v>
+      </c>
+      <c r="AN85">
+        <v>0.5</v>
+      </c>
+      <c r="AO85">
+        <v>1.2</v>
+      </c>
+      <c r="AP85">
+        <v>0.4</v>
+      </c>
+      <c r="AQ85">
+        <v>1.5</v>
+      </c>
+      <c r="AR85">
+        <v>1.27</v>
+      </c>
+      <c r="AS85">
+        <v>1.47</v>
+      </c>
+      <c r="AT85">
+        <v>2.74</v>
+      </c>
+      <c r="AU85">
+        <v>6</v>
+      </c>
+      <c r="AV85">
+        <v>7</v>
+      </c>
+      <c r="AW85">
+        <v>10</v>
+      </c>
+      <c r="AX85">
+        <v>4</v>
+      </c>
+      <c r="AY85">
+        <v>16</v>
+      </c>
+      <c r="AZ85">
+        <v>11</v>
+      </c>
+      <c r="BA85">
+        <v>9</v>
+      </c>
+      <c r="BB85">
+        <v>1</v>
+      </c>
+      <c r="BC85">
+        <v>10</v>
+      </c>
+      <c r="BD85">
+        <v>2.07</v>
+      </c>
+      <c r="BE85">
+        <v>6.5</v>
+      </c>
+      <c r="BF85">
+        <v>1.77</v>
+      </c>
+      <c r="BG85">
+        <v>1.21</v>
+      </c>
+      <c r="BH85">
+        <v>3.7</v>
+      </c>
+      <c r="BI85">
+        <v>1.33</v>
+      </c>
+      <c r="BJ85">
+        <v>2.7</v>
+      </c>
+      <c r="BK85">
+        <v>1.61</v>
+      </c>
+      <c r="BL85">
+        <v>2.08</v>
+      </c>
+      <c r="BM85">
+        <v>2.11</v>
+      </c>
+      <c r="BN85">
+        <v>1.68</v>
+      </c>
+      <c r="BO85">
+        <v>2.55</v>
+      </c>
+      <c r="BP85">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7785882</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>82</v>
+      </c>
+      <c r="H86" t="s">
+        <v>78</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>3</v>
+      </c>
+      <c r="L86">
+        <v>2</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <v>4</v>
+      </c>
+      <c r="O86" t="s">
+        <v>152</v>
+      </c>
+      <c r="P86" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q86">
+        <v>1.57</v>
+      </c>
+      <c r="R86">
+        <v>3.08</v>
+      </c>
+      <c r="S86">
+        <v>7.5</v>
+      </c>
+      <c r="T86">
+        <v>1.2</v>
+      </c>
+      <c r="U86">
+        <v>3.8</v>
+      </c>
+      <c r="V86">
+        <v>2.05</v>
+      </c>
+      <c r="W86">
+        <v>1.7</v>
+      </c>
+      <c r="X86">
+        <v>4.55</v>
+      </c>
+      <c r="Y86">
+        <v>1.18</v>
+      </c>
+      <c r="Z86">
+        <v>1.22</v>
+      </c>
+      <c r="AA86">
+        <v>6</v>
+      </c>
+      <c r="AB86">
+        <v>10.88</v>
+      </c>
+      <c r="AC86">
+        <v>1.01</v>
+      </c>
+      <c r="AD86">
+        <v>16.5</v>
+      </c>
+      <c r="AE86">
+        <v>1.13</v>
+      </c>
+      <c r="AF86">
+        <v>6.1</v>
+      </c>
+      <c r="AG86">
+        <v>1.44</v>
+      </c>
+      <c r="AH86">
+        <v>2.63</v>
+      </c>
+      <c r="AI86">
+        <v>1.83</v>
+      </c>
+      <c r="AJ86">
+        <v>1.85</v>
+      </c>
+      <c r="AK86">
+        <v>1</v>
+      </c>
+      <c r="AL86">
+        <v>1.09</v>
+      </c>
+      <c r="AM86">
+        <v>3.9</v>
+      </c>
+      <c r="AN86">
+        <v>3</v>
+      </c>
+      <c r="AO86">
+        <v>0.8</v>
+      </c>
+      <c r="AP86">
+        <v>2.6</v>
+      </c>
+      <c r="AQ86">
+        <v>0.83</v>
+      </c>
+      <c r="AR86">
+        <v>2.06</v>
+      </c>
+      <c r="AS86">
+        <v>1.64</v>
+      </c>
+      <c r="AT86">
+        <v>3.7</v>
+      </c>
+      <c r="AU86">
+        <v>9</v>
+      </c>
+      <c r="AV86">
+        <v>5</v>
+      </c>
+      <c r="AW86">
+        <v>8</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+      <c r="AY86">
+        <v>17</v>
+      </c>
+      <c r="AZ86">
+        <v>13</v>
+      </c>
+      <c r="BA86">
+        <v>4</v>
+      </c>
+      <c r="BB86">
+        <v>5</v>
+      </c>
+      <c r="BC86">
+        <v>9</v>
+      </c>
+      <c r="BD86">
+        <v>1.13</v>
+      </c>
+      <c r="BE86">
+        <v>11.5</v>
+      </c>
+      <c r="BF86">
+        <v>5.8</v>
+      </c>
+      <c r="BG86">
+        <v>1.11</v>
+      </c>
+      <c r="BH86">
+        <v>5.4</v>
+      </c>
+      <c r="BI86">
+        <v>1.2</v>
+      </c>
+      <c r="BJ86">
+        <v>3.8</v>
+      </c>
+      <c r="BK86">
+        <v>1.32</v>
+      </c>
+      <c r="BL86">
+        <v>2.78</v>
+      </c>
+      <c r="BM86">
+        <v>1.58</v>
+      </c>
+      <c r="BN86">
+        <v>2.25</v>
+      </c>
+      <c r="BO86">
+        <v>1.92</v>
+      </c>
+      <c r="BP86">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7785881</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>71</v>
+      </c>
+      <c r="H87" t="s">
+        <v>76</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" t="s">
+        <v>153</v>
+      </c>
+      <c r="P87" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q87">
+        <v>2.3</v>
+      </c>
+      <c r="R87">
+        <v>2.41</v>
+      </c>
+      <c r="S87">
+        <v>3.74</v>
+      </c>
+      <c r="T87">
+        <v>1.21</v>
+      </c>
+      <c r="U87">
+        <v>3.75</v>
+      </c>
+      <c r="V87">
+        <v>2.18</v>
+      </c>
+      <c r="W87">
+        <v>1.66</v>
+      </c>
+      <c r="X87">
+        <v>4.8</v>
+      </c>
+      <c r="Y87">
+        <v>1.15</v>
+      </c>
+      <c r="Z87">
+        <v>1.95</v>
+      </c>
+      <c r="AA87">
+        <v>4.11</v>
+      </c>
+      <c r="AB87">
+        <v>3.3</v>
+      </c>
+      <c r="AC87">
+        <v>1.01</v>
+      </c>
+      <c r="AD87">
+        <v>14.1</v>
+      </c>
+      <c r="AE87">
+        <v>1.15</v>
+      </c>
+      <c r="AF87">
+        <v>4.5</v>
+      </c>
+      <c r="AG87">
+        <v>1.44</v>
+      </c>
+      <c r="AH87">
+        <v>2.5</v>
+      </c>
+      <c r="AI87">
+        <v>1.5</v>
+      </c>
+      <c r="AJ87">
+        <v>2.52</v>
+      </c>
+      <c r="AK87">
+        <v>1.24</v>
+      </c>
+      <c r="AL87">
+        <v>1.27</v>
+      </c>
+      <c r="AM87">
+        <v>1.87</v>
+      </c>
+      <c r="AN87">
+        <v>2</v>
+      </c>
+      <c r="AO87">
+        <v>1.33</v>
+      </c>
+      <c r="AP87">
+        <v>2.17</v>
+      </c>
+      <c r="AQ87">
+        <v>1</v>
+      </c>
+      <c r="AR87">
+        <v>2.08</v>
+      </c>
+      <c r="AS87">
+        <v>1.74</v>
+      </c>
+      <c r="AT87">
+        <v>3.82</v>
+      </c>
+      <c r="AU87">
+        <v>5</v>
+      </c>
+      <c r="AV87">
+        <v>4</v>
+      </c>
+      <c r="AW87">
+        <v>8</v>
+      </c>
+      <c r="AX87">
+        <v>6</v>
+      </c>
+      <c r="AY87">
+        <v>13</v>
+      </c>
+      <c r="AZ87">
+        <v>10</v>
+      </c>
+      <c r="BA87">
+        <v>8</v>
+      </c>
+      <c r="BB87">
+        <v>5</v>
+      </c>
+      <c r="BC87">
+        <v>13</v>
+      </c>
+      <c r="BD87">
+        <v>1.74</v>
+      </c>
+      <c r="BE87">
+        <v>7</v>
+      </c>
+      <c r="BF87">
+        <v>2.28</v>
+      </c>
+      <c r="BG87">
+        <v>1.11</v>
+      </c>
+      <c r="BH87">
+        <v>4.6</v>
+      </c>
+      <c r="BI87">
+        <v>1.22</v>
+      </c>
+      <c r="BJ87">
+        <v>3.27</v>
+      </c>
+      <c r="BK87">
+        <v>1.4</v>
+      </c>
+      <c r="BL87">
+        <v>2.8</v>
+      </c>
+      <c r="BM87">
+        <v>1.81</v>
+      </c>
+      <c r="BN87">
+        <v>1.95</v>
+      </c>
+      <c r="BO87">
+        <v>2.2</v>
+      </c>
+      <c r="BP87">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7785883</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>85</v>
+      </c>
+      <c r="H88" t="s">
+        <v>77</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>3</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88">
+        <v>5</v>
+      </c>
+      <c r="O88" t="s">
+        <v>154</v>
+      </c>
+      <c r="P88" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q88">
+        <v>2.6</v>
+      </c>
+      <c r="R88">
+        <v>2.23</v>
+      </c>
+      <c r="S88">
+        <v>3.5</v>
+      </c>
+      <c r="T88">
+        <v>1.3</v>
+      </c>
+      <c r="U88">
+        <v>3.2</v>
+      </c>
+      <c r="V88">
+        <v>2.5</v>
+      </c>
+      <c r="W88">
+        <v>1.46</v>
+      </c>
+      <c r="X88">
+        <v>5.5</v>
+      </c>
+      <c r="Y88">
+        <v>1.11</v>
+      </c>
+      <c r="Z88">
+        <v>2.07</v>
+      </c>
+      <c r="AA88">
+        <v>3.45</v>
+      </c>
+      <c r="AB88">
+        <v>3.05</v>
+      </c>
+      <c r="AC88">
+        <v>1.02</v>
+      </c>
+      <c r="AD88">
+        <v>9</v>
+      </c>
+      <c r="AE88">
+        <v>1.22</v>
+      </c>
+      <c r="AF88">
+        <v>3.84</v>
+      </c>
+      <c r="AG88">
+        <v>1.67</v>
+      </c>
+      <c r="AH88">
+        <v>2.08</v>
+      </c>
+      <c r="AI88">
+        <v>1.57</v>
+      </c>
+      <c r="AJ88">
+        <v>2.3</v>
+      </c>
+      <c r="AK88">
+        <v>1.27</v>
+      </c>
+      <c r="AL88">
+        <v>1.3</v>
+      </c>
+      <c r="AM88">
+        <v>1.67</v>
+      </c>
+      <c r="AN88">
+        <v>0.2</v>
+      </c>
+      <c r="AO88">
+        <v>0.75</v>
+      </c>
+      <c r="AP88">
+        <v>0.67</v>
+      </c>
+      <c r="AQ88">
+        <v>0.6</v>
+      </c>
+      <c r="AR88">
+        <v>1.43</v>
+      </c>
+      <c r="AS88">
+        <v>1.5</v>
+      </c>
+      <c r="AT88">
+        <v>2.93</v>
+      </c>
+      <c r="AU88">
+        <v>7</v>
+      </c>
+      <c r="AV88">
+        <v>6</v>
+      </c>
+      <c r="AW88">
+        <v>7</v>
+      </c>
+      <c r="AX88">
+        <v>6</v>
+      </c>
+      <c r="AY88">
+        <v>14</v>
+      </c>
+      <c r="AZ88">
+        <v>12</v>
+      </c>
+      <c r="BA88">
+        <v>4</v>
+      </c>
+      <c r="BB88">
+        <v>3</v>
+      </c>
+      <c r="BC88">
+        <v>7</v>
+      </c>
+      <c r="BD88">
+        <v>1.6</v>
+      </c>
+      <c r="BE88">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF88">
+        <v>2.69</v>
+      </c>
+      <c r="BG88">
+        <v>1.16</v>
+      </c>
+      <c r="BH88">
+        <v>4.4</v>
+      </c>
+      <c r="BI88">
+        <v>1.29</v>
+      </c>
+      <c r="BJ88">
+        <v>3.5</v>
+      </c>
+      <c r="BK88">
+        <v>1.54</v>
+      </c>
+      <c r="BL88">
+        <v>2.6</v>
+      </c>
+      <c r="BM88">
+        <v>1.71</v>
+      </c>
+      <c r="BN88">
+        <v>2.04</v>
+      </c>
+      <c r="BO88">
+        <v>2.09</v>
+      </c>
+      <c r="BP88">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -478,7 +478,7 @@
     <t>['27', '82', '90+3']</t>
   </si>
   <si>
-    <t>['58', '68', '85']</t>
+    <t>['57', '67', '85']</t>
   </si>
   <si>
     <t>['2', '9']</t>
@@ -646,7 +646,7 @@
     <t>['29', '78']</t>
   </si>
   <si>
-    <t>['39', '64']</t>
+    <t>['37', '63']</t>
   </si>
 </sst>
 </file>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="217">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,18 @@
     <t>['57', '67', '85']</t>
   </si>
   <si>
+    <t>['58', '48']</t>
+  </si>
+  <si>
+    <t>['22', '90+2']</t>
+  </si>
+  <si>
+    <t>['6', '1', '26', '69', '83', '65']</t>
+  </si>
+  <si>
+    <t>['14', '69', '58', '71', '51']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -647,6 +659,12 @@
   </si>
   <si>
     <t>['37', '63']</t>
+  </si>
+  <si>
+    <t>['72', '70']</t>
+  </si>
+  <si>
+    <t>['42', '26', '45', '66']</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1264,7 +1282,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1342,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ2">
         <v>0.83</v>
@@ -1676,7 +1694,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1882,7 +1900,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1960,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>0.8</v>
@@ -2169,7 +2187,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2372,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2500,7 +2518,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2578,10 +2596,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2706,7 +2724,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2784,10 +2802,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2912,7 +2930,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -2990,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10">
         <v>1.67</v>
@@ -3118,7 +3136,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3530,7 +3548,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3817,7 +3835,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ14">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3942,7 +3960,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4023,7 +4041,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ15">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4354,7 +4372,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4435,7 +4453,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4560,7 +4578,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4638,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18">
         <v>0.17</v>
@@ -4847,7 +4865,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR19">
         <v>1.89</v>
@@ -4972,7 +4990,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5178,7 +5196,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5256,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5384,7 +5402,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5462,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>0.83</v>
@@ -5590,7 +5608,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5671,7 +5689,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR23">
         <v>2.01</v>
@@ -5796,7 +5814,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5874,10 +5892,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR24">
         <v>0.96</v>
@@ -6080,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ25">
         <v>0.83</v>
@@ -6208,7 +6226,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6289,7 +6307,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR26">
         <v>0.7</v>
@@ -6414,7 +6432,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6495,7 +6513,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR27">
         <v>1.17</v>
@@ -6698,7 +6716,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -6826,7 +6844,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -6907,7 +6925,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR29">
         <v>1.81</v>
@@ -7032,7 +7050,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7113,7 +7131,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ30">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.53</v>
@@ -7316,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1.67</v>
@@ -7444,7 +7462,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7650,7 +7668,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -7937,7 +7955,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ34">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8062,7 +8080,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8268,7 +8286,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8346,10 +8364,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.48</v>
@@ -8680,7 +8698,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8758,7 +8776,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
         <v>0.83</v>
@@ -8886,7 +8904,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -8964,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ39">
         <v>0.6</v>
@@ -9298,7 +9316,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9379,7 +9397,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR41">
         <v>1.1</v>
@@ -9788,7 +9806,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>2.33</v>
@@ -9916,7 +9934,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10122,7 +10140,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10328,7 +10346,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10409,7 +10427,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ46">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR46">
         <v>2.41</v>
@@ -10534,7 +10552,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10615,7 +10633,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -10740,7 +10758,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10818,10 +10836,10 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR48">
         <v>0.78</v>
@@ -10946,7 +10964,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11024,7 +11042,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
         <v>0.6</v>
@@ -11233,7 +11251,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ50">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
         <v>1.65</v>
@@ -11645,7 +11663,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ52">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR52">
         <v>1.9</v>
@@ -12182,7 +12200,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12260,7 +12278,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ55">
         <v>1.67</v>
@@ -12466,10 +12484,10 @@
         <v>2.33</v>
       </c>
       <c r="AP56">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR56">
         <v>1.81</v>
@@ -12672,10 +12690,10 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR57">
         <v>1.63</v>
@@ -12800,7 +12818,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12878,7 +12896,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ58">
         <v>2.33</v>
@@ -13212,7 +13230,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13293,7 +13311,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ60">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR60">
         <v>1.03</v>
@@ -13418,7 +13436,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13624,7 +13642,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13702,7 +13720,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ62">
         <v>1.8</v>
@@ -13830,7 +13848,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -13908,7 +13926,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -14036,7 +14054,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14117,7 +14135,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR64">
         <v>1.22</v>
@@ -14242,7 +14260,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14529,7 +14547,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR66">
         <v>1.27</v>
@@ -14654,7 +14672,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14735,7 +14753,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ67">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR67">
         <v>1.72</v>
@@ -14860,7 +14878,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -14938,7 +14956,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15272,7 +15290,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15684,7 +15702,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15890,7 +15908,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -16096,7 +16114,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16177,7 +16195,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR74">
         <v>1.26</v>
@@ -16302,7 +16320,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16380,7 +16398,7 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ75">
         <v>0.8</v>
@@ -16508,7 +16526,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16586,7 +16604,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ76">
         <v>1.8</v>
@@ -16714,7 +16732,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16795,7 +16813,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ77">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR77">
         <v>0.93</v>
@@ -16920,7 +16938,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -16998,10 +17016,10 @@
         <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17126,7 +17144,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17204,7 +17222,7 @@
         <v>0.2</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ79">
         <v>0.17</v>
@@ -17332,7 +17350,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17410,10 +17428,10 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR80">
         <v>1.55</v>
@@ -17538,7 +17556,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q81">
         <v>1.6</v>
@@ -17744,7 +17762,7 @@
         <v>149</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q82">
         <v>2.11</v>
@@ -17950,7 +17968,7 @@
         <v>89</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q83">
         <v>2.85</v>
@@ -18028,7 +18046,7 @@
         <v>2.2</v>
       </c>
       <c r="AP83">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>2.33</v>
@@ -18237,7 +18255,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR84">
         <v>1.45</v>
@@ -18362,7 +18380,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>4.1</v>
@@ -18568,7 +18586,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>1.57</v>
@@ -18980,7 +18998,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19137,6 +19155,1242 @@
       </c>
       <c r="BP88">
         <v>1.73</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7785906</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45829.375</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>78</v>
+      </c>
+      <c r="H89" t="s">
+        <v>80</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>2</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>3</v>
+      </c>
+      <c r="O89" t="s">
+        <v>155</v>
+      </c>
+      <c r="P89" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q89">
+        <v>2.55</v>
+      </c>
+      <c r="R89">
+        <v>2.3</v>
+      </c>
+      <c r="S89">
+        <v>3.5</v>
+      </c>
+      <c r="T89">
+        <v>1.31</v>
+      </c>
+      <c r="U89">
+        <v>3.3</v>
+      </c>
+      <c r="V89">
+        <v>2.37</v>
+      </c>
+      <c r="W89">
+        <v>1.5</v>
+      </c>
+      <c r="X89">
+        <v>6</v>
+      </c>
+      <c r="Y89">
+        <v>1.12</v>
+      </c>
+      <c r="Z89">
+        <v>2.05</v>
+      </c>
+      <c r="AA89">
+        <v>3.4</v>
+      </c>
+      <c r="AB89">
+        <v>3.05</v>
+      </c>
+      <c r="AC89">
+        <v>1.01</v>
+      </c>
+      <c r="AD89">
+        <v>11</v>
+      </c>
+      <c r="AE89">
+        <v>1.16</v>
+      </c>
+      <c r="AF89">
+        <v>4.15</v>
+      </c>
+      <c r="AG89">
+        <v>1.65</v>
+      </c>
+      <c r="AH89">
+        <v>2.05</v>
+      </c>
+      <c r="AI89">
+        <v>1.61</v>
+      </c>
+      <c r="AJ89">
+        <v>2.28</v>
+      </c>
+      <c r="AK89">
+        <v>1.26</v>
+      </c>
+      <c r="AL89">
+        <v>1.26</v>
+      </c>
+      <c r="AM89">
+        <v>1.74</v>
+      </c>
+      <c r="AN89">
+        <v>1.6</v>
+      </c>
+      <c r="AO89">
+        <v>0.2</v>
+      </c>
+      <c r="AP89">
+        <v>1.83</v>
+      </c>
+      <c r="AQ89">
+        <v>0.17</v>
+      </c>
+      <c r="AR89">
+        <v>1.17</v>
+      </c>
+      <c r="AS89">
+        <v>1.37</v>
+      </c>
+      <c r="AT89">
+        <v>2.54</v>
+      </c>
+      <c r="AU89">
+        <v>6</v>
+      </c>
+      <c r="AV89">
+        <v>7</v>
+      </c>
+      <c r="AW89">
+        <v>9</v>
+      </c>
+      <c r="AX89">
+        <v>4</v>
+      </c>
+      <c r="AY89">
+        <v>15</v>
+      </c>
+      <c r="AZ89">
+        <v>11</v>
+      </c>
+      <c r="BA89">
+        <v>8</v>
+      </c>
+      <c r="BB89">
+        <v>6</v>
+      </c>
+      <c r="BC89">
+        <v>14</v>
+      </c>
+      <c r="BD89">
+        <v>1.88</v>
+      </c>
+      <c r="BE89">
+        <v>7</v>
+      </c>
+      <c r="BF89">
+        <v>2.4</v>
+      </c>
+      <c r="BG89">
+        <v>1.16</v>
+      </c>
+      <c r="BH89">
+        <v>4.5</v>
+      </c>
+      <c r="BI89">
+        <v>1.28</v>
+      </c>
+      <c r="BJ89">
+        <v>3.34</v>
+      </c>
+      <c r="BK89">
+        <v>1.45</v>
+      </c>
+      <c r="BL89">
+        <v>2.48</v>
+      </c>
+      <c r="BM89">
+        <v>1.79</v>
+      </c>
+      <c r="BN89">
+        <v>1.92</v>
+      </c>
+      <c r="BO89">
+        <v>2.23</v>
+      </c>
+      <c r="BP89">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7785899</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45829.375</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>70</v>
+      </c>
+      <c r="H90" t="s">
+        <v>71</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>2</v>
+      </c>
+      <c r="M90">
+        <v>2</v>
+      </c>
+      <c r="N90">
+        <v>4</v>
+      </c>
+      <c r="O90" t="s">
+        <v>156</v>
+      </c>
+      <c r="P90" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q90">
+        <v>3.96</v>
+      </c>
+      <c r="R90">
+        <v>2.51</v>
+      </c>
+      <c r="S90">
+        <v>2.3</v>
+      </c>
+      <c r="T90">
+        <v>1.21</v>
+      </c>
+      <c r="U90">
+        <v>4.33</v>
+      </c>
+      <c r="V90">
+        <v>1.95</v>
+      </c>
+      <c r="W90">
+        <v>1.75</v>
+      </c>
+      <c r="X90">
+        <v>4</v>
+      </c>
+      <c r="Y90">
+        <v>1.22</v>
+      </c>
+      <c r="Z90">
+        <v>3.25</v>
+      </c>
+      <c r="AA90">
+        <v>3.75</v>
+      </c>
+      <c r="AB90">
+        <v>1.75</v>
+      </c>
+      <c r="AC90">
+        <v>1.01</v>
+      </c>
+      <c r="AD90">
+        <v>17</v>
+      </c>
+      <c r="AE90">
+        <v>1.11</v>
+      </c>
+      <c r="AF90">
+        <v>5.8</v>
+      </c>
+      <c r="AG90">
+        <v>1.33</v>
+      </c>
+      <c r="AH90">
+        <v>2.84</v>
+      </c>
+      <c r="AI90">
+        <v>1.33</v>
+      </c>
+      <c r="AJ90">
+        <v>2.8</v>
+      </c>
+      <c r="AK90">
+        <v>1.23</v>
+      </c>
+      <c r="AL90">
+        <v>1.24</v>
+      </c>
+      <c r="AM90">
+        <v>1.28</v>
+      </c>
+      <c r="AN90">
+        <v>1.5</v>
+      </c>
+      <c r="AO90">
+        <v>1.4</v>
+      </c>
+      <c r="AP90">
+        <v>1.4</v>
+      </c>
+      <c r="AQ90">
+        <v>1.33</v>
+      </c>
+      <c r="AR90">
+        <v>2.01</v>
+      </c>
+      <c r="AS90">
+        <v>2.21</v>
+      </c>
+      <c r="AT90">
+        <v>4.22</v>
+      </c>
+      <c r="AU90">
+        <v>6</v>
+      </c>
+      <c r="AV90">
+        <v>8</v>
+      </c>
+      <c r="AW90">
+        <v>3</v>
+      </c>
+      <c r="AX90">
+        <v>0</v>
+      </c>
+      <c r="AY90">
+        <v>9</v>
+      </c>
+      <c r="AZ90">
+        <v>8</v>
+      </c>
+      <c r="BA90">
+        <v>6</v>
+      </c>
+      <c r="BB90">
+        <v>3</v>
+      </c>
+      <c r="BC90">
+        <v>9</v>
+      </c>
+      <c r="BD90">
+        <v>2.23</v>
+      </c>
+      <c r="BE90">
+        <v>8.6</v>
+      </c>
+      <c r="BF90">
+        <v>1.62</v>
+      </c>
+      <c r="BG90">
+        <v>1.15</v>
+      </c>
+      <c r="BH90">
+        <v>4.6</v>
+      </c>
+      <c r="BI90">
+        <v>1.22</v>
+      </c>
+      <c r="BJ90">
+        <v>3.4</v>
+      </c>
+      <c r="BK90">
+        <v>1.45</v>
+      </c>
+      <c r="BL90">
+        <v>2.57</v>
+      </c>
+      <c r="BM90">
+        <v>1.74</v>
+      </c>
+      <c r="BN90">
+        <v>1.95</v>
+      </c>
+      <c r="BO90">
+        <v>2.24</v>
+      </c>
+      <c r="BP90">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7785905</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45829.45833333334</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>76</v>
+      </c>
+      <c r="H91" t="s">
+        <v>72</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>102</v>
+      </c>
+      <c r="P91" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q91">
+        <v>2.51</v>
+      </c>
+      <c r="R91">
+        <v>2.34</v>
+      </c>
+      <c r="S91">
+        <v>4.08</v>
+      </c>
+      <c r="T91">
+        <v>1.26</v>
+      </c>
+      <c r="U91">
+        <v>3.3</v>
+      </c>
+      <c r="V91">
+        <v>2.34</v>
+      </c>
+      <c r="W91">
+        <v>1.52</v>
+      </c>
+      <c r="X91">
+        <v>4.8</v>
+      </c>
+      <c r="Y91">
+        <v>1.12</v>
+      </c>
+      <c r="Z91">
+        <v>1.83</v>
+      </c>
+      <c r="AA91">
+        <v>3.8</v>
+      </c>
+      <c r="AB91">
+        <v>3.45</v>
+      </c>
+      <c r="AC91">
+        <v>1</v>
+      </c>
+      <c r="AD91">
+        <v>12</v>
+      </c>
+      <c r="AE91">
+        <v>1.16</v>
+      </c>
+      <c r="AF91">
+        <v>4.35</v>
+      </c>
+      <c r="AG91">
+        <v>1.61</v>
+      </c>
+      <c r="AH91">
+        <v>2.1</v>
+      </c>
+      <c r="AI91">
+        <v>1.56</v>
+      </c>
+      <c r="AJ91">
+        <v>2.3</v>
+      </c>
+      <c r="AK91">
+        <v>1.26</v>
+      </c>
+      <c r="AL91">
+        <v>1.25</v>
+      </c>
+      <c r="AM91">
+        <v>1.8</v>
+      </c>
+      <c r="AN91">
+        <v>1.67</v>
+      </c>
+      <c r="AO91">
+        <v>0.8</v>
+      </c>
+      <c r="AP91">
+        <v>1.86</v>
+      </c>
+      <c r="AQ91">
+        <v>0.67</v>
+      </c>
+      <c r="AR91">
+        <v>1.53</v>
+      </c>
+      <c r="AS91">
+        <v>1.5</v>
+      </c>
+      <c r="AT91">
+        <v>3.03</v>
+      </c>
+      <c r="AU91">
+        <v>7</v>
+      </c>
+      <c r="AV91">
+        <v>3</v>
+      </c>
+      <c r="AW91">
+        <v>5</v>
+      </c>
+      <c r="AX91">
+        <v>5</v>
+      </c>
+      <c r="AY91">
+        <v>12</v>
+      </c>
+      <c r="AZ91">
+        <v>8</v>
+      </c>
+      <c r="BA91">
+        <v>3</v>
+      </c>
+      <c r="BB91">
+        <v>5</v>
+      </c>
+      <c r="BC91">
+        <v>8</v>
+      </c>
+      <c r="BD91">
+        <v>1.53</v>
+      </c>
+      <c r="BE91">
+        <v>7</v>
+      </c>
+      <c r="BF91">
+        <v>2.63</v>
+      </c>
+      <c r="BG91">
+        <v>1.17</v>
+      </c>
+      <c r="BH91">
+        <v>4.35</v>
+      </c>
+      <c r="BI91">
+        <v>1.22</v>
+      </c>
+      <c r="BJ91">
+        <v>3.5</v>
+      </c>
+      <c r="BK91">
+        <v>1.53</v>
+      </c>
+      <c r="BL91">
+        <v>2.54</v>
+      </c>
+      <c r="BM91">
+        <v>1.71</v>
+      </c>
+      <c r="BN91">
+        <v>2.05</v>
+      </c>
+      <c r="BO91">
+        <v>2.13</v>
+      </c>
+      <c r="BP91">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7785901</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45829.45833333334</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>73</v>
+      </c>
+      <c r="H92" t="s">
+        <v>82</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3</v>
+      </c>
+      <c r="K92">
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>4</v>
+      </c>
+      <c r="N92">
+        <v>4</v>
+      </c>
+      <c r="O92" t="s">
+        <v>89</v>
+      </c>
+      <c r="P92" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q92">
+        <v>4.5</v>
+      </c>
+      <c r="R92">
+        <v>2.4</v>
+      </c>
+      <c r="S92">
+        <v>2.1</v>
+      </c>
+      <c r="T92">
+        <v>1.26</v>
+      </c>
+      <c r="U92">
+        <v>3.75</v>
+      </c>
+      <c r="V92">
+        <v>2.42</v>
+      </c>
+      <c r="W92">
+        <v>1.62</v>
+      </c>
+      <c r="X92">
+        <v>5.05</v>
+      </c>
+      <c r="Y92">
+        <v>1.15</v>
+      </c>
+      <c r="Z92">
+        <v>4.9</v>
+      </c>
+      <c r="AA92">
+        <v>4</v>
+      </c>
+      <c r="AB92">
+        <v>1.54</v>
+      </c>
+      <c r="AC92">
+        <v>1.02</v>
+      </c>
+      <c r="AD92">
+        <v>17</v>
+      </c>
+      <c r="AE92">
+        <v>1.13</v>
+      </c>
+      <c r="AF92">
+        <v>4.9</v>
+      </c>
+      <c r="AG92">
+        <v>1.65</v>
+      </c>
+      <c r="AH92">
+        <v>2.05</v>
+      </c>
+      <c r="AI92">
+        <v>1.55</v>
+      </c>
+      <c r="AJ92">
+        <v>2.2</v>
+      </c>
+      <c r="AK92">
+        <v>1.22</v>
+      </c>
+      <c r="AL92">
+        <v>1.22</v>
+      </c>
+      <c r="AM92">
+        <v>1.16</v>
+      </c>
+      <c r="AN92">
+        <v>1.17</v>
+      </c>
+      <c r="AO92">
+        <v>2</v>
+      </c>
+      <c r="AP92">
+        <v>1</v>
+      </c>
+      <c r="AQ92">
+        <v>2.14</v>
+      </c>
+      <c r="AR92">
+        <v>1.68</v>
+      </c>
+      <c r="AS92">
+        <v>1.94</v>
+      </c>
+      <c r="AT92">
+        <v>3.62</v>
+      </c>
+      <c r="AU92">
+        <v>5</v>
+      </c>
+      <c r="AV92">
+        <v>8</v>
+      </c>
+      <c r="AW92">
+        <v>12</v>
+      </c>
+      <c r="AX92">
+        <v>9</v>
+      </c>
+      <c r="AY92">
+        <v>17</v>
+      </c>
+      <c r="AZ92">
+        <v>17</v>
+      </c>
+      <c r="BA92">
+        <v>4</v>
+      </c>
+      <c r="BB92">
+        <v>4</v>
+      </c>
+      <c r="BC92">
+        <v>8</v>
+      </c>
+      <c r="BD92">
+        <v>3.86</v>
+      </c>
+      <c r="BE92">
+        <v>8.6</v>
+      </c>
+      <c r="BF92">
+        <v>1.4</v>
+      </c>
+      <c r="BG92">
+        <v>1.13</v>
+      </c>
+      <c r="BH92">
+        <v>4.75</v>
+      </c>
+      <c r="BI92">
+        <v>1.26</v>
+      </c>
+      <c r="BJ92">
+        <v>3.5</v>
+      </c>
+      <c r="BK92">
+        <v>1.46</v>
+      </c>
+      <c r="BL92">
+        <v>2.57</v>
+      </c>
+      <c r="BM92">
+        <v>1.77</v>
+      </c>
+      <c r="BN92">
+        <v>2</v>
+      </c>
+      <c r="BO92">
+        <v>2.19</v>
+      </c>
+      <c r="BP92">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7785902</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45829.45833333334</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
+        <v>77</v>
+      </c>
+      <c r="H93" t="s">
+        <v>83</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>4</v>
+      </c>
+      <c r="L93">
+        <v>6</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>7</v>
+      </c>
+      <c r="O93" t="s">
+        <v>157</v>
+      </c>
+      <c r="P93" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q93">
+        <v>2.9</v>
+      </c>
+      <c r="R93">
+        <v>2.3</v>
+      </c>
+      <c r="S93">
+        <v>3.18</v>
+      </c>
+      <c r="T93">
+        <v>1.35</v>
+      </c>
+      <c r="U93">
+        <v>3.11</v>
+      </c>
+      <c r="V93">
+        <v>2.4</v>
+      </c>
+      <c r="W93">
+        <v>1.42</v>
+      </c>
+      <c r="X93">
+        <v>6.25</v>
+      </c>
+      <c r="Y93">
+        <v>1.12</v>
+      </c>
+      <c r="Z93">
+        <v>2.33</v>
+      </c>
+      <c r="AA93">
+        <v>3.21</v>
+      </c>
+      <c r="AB93">
+        <v>2.78</v>
+      </c>
+      <c r="AC93">
+        <v>1.02</v>
+      </c>
+      <c r="AD93">
+        <v>10</v>
+      </c>
+      <c r="AE93">
+        <v>1.18</v>
+      </c>
+      <c r="AF93">
+        <v>3.9</v>
+      </c>
+      <c r="AG93">
+        <v>1.82</v>
+      </c>
+      <c r="AH93">
+        <v>1.88</v>
+      </c>
+      <c r="AI93">
+        <v>1.6</v>
+      </c>
+      <c r="AJ93">
+        <v>2.25</v>
+      </c>
+      <c r="AK93">
+        <v>1.3</v>
+      </c>
+      <c r="AL93">
+        <v>1.28</v>
+      </c>
+      <c r="AM93">
+        <v>1.45</v>
+      </c>
+      <c r="AN93">
+        <v>1.83</v>
+      </c>
+      <c r="AO93">
+        <v>1.33</v>
+      </c>
+      <c r="AP93">
+        <v>2</v>
+      </c>
+      <c r="AQ93">
+        <v>1.14</v>
+      </c>
+      <c r="AR93">
+        <v>1.3</v>
+      </c>
+      <c r="AS93">
+        <v>1.11</v>
+      </c>
+      <c r="AT93">
+        <v>2.41</v>
+      </c>
+      <c r="AU93">
+        <v>10</v>
+      </c>
+      <c r="AV93">
+        <v>5</v>
+      </c>
+      <c r="AW93">
+        <v>3</v>
+      </c>
+      <c r="AX93">
+        <v>4</v>
+      </c>
+      <c r="AY93">
+        <v>13</v>
+      </c>
+      <c r="AZ93">
+        <v>9</v>
+      </c>
+      <c r="BA93">
+        <v>9</v>
+      </c>
+      <c r="BB93">
+        <v>2</v>
+      </c>
+      <c r="BC93">
+        <v>11</v>
+      </c>
+      <c r="BD93">
+        <v>1.84</v>
+      </c>
+      <c r="BE93">
+        <v>7.8</v>
+      </c>
+      <c r="BF93">
+        <v>2.28</v>
+      </c>
+      <c r="BG93">
+        <v>1.18</v>
+      </c>
+      <c r="BH93">
+        <v>4.1</v>
+      </c>
+      <c r="BI93">
+        <v>1.28</v>
+      </c>
+      <c r="BJ93">
+        <v>3.3</v>
+      </c>
+      <c r="BK93">
+        <v>1.54</v>
+      </c>
+      <c r="BL93">
+        <v>2.25</v>
+      </c>
+      <c r="BM93">
+        <v>1.93</v>
+      </c>
+      <c r="BN93">
+        <v>1.78</v>
+      </c>
+      <c r="BO93">
+        <v>2.45</v>
+      </c>
+      <c r="BP93">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7785904</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45829.45833333334</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
+        <v>75</v>
+      </c>
+      <c r="H94" t="s">
+        <v>74</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+      <c r="L94">
+        <v>5</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>6</v>
+      </c>
+      <c r="O94" t="s">
+        <v>158</v>
+      </c>
+      <c r="P94" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q94">
+        <v>2.5</v>
+      </c>
+      <c r="R94">
+        <v>2.48</v>
+      </c>
+      <c r="S94">
+        <v>3.35</v>
+      </c>
+      <c r="T94">
+        <v>1.23</v>
+      </c>
+      <c r="U94">
+        <v>3.8</v>
+      </c>
+      <c r="V94">
+        <v>2.28</v>
+      </c>
+      <c r="W94">
+        <v>1.71</v>
+      </c>
+      <c r="X94">
+        <v>4.5</v>
+      </c>
+      <c r="Y94">
+        <v>1.15</v>
+      </c>
+      <c r="Z94">
+        <v>2.01</v>
+      </c>
+      <c r="AA94">
+        <v>3.68</v>
+      </c>
+      <c r="AB94">
+        <v>3.03</v>
+      </c>
+      <c r="AC94">
+        <v>1.01</v>
+      </c>
+      <c r="AD94">
+        <v>12</v>
+      </c>
+      <c r="AE94">
+        <v>1.11</v>
+      </c>
+      <c r="AF94">
+        <v>5.3</v>
+      </c>
+      <c r="AG94">
+        <v>1.53</v>
+      </c>
+      <c r="AH94">
+        <v>2.25</v>
+      </c>
+      <c r="AI94">
+        <v>1.4</v>
+      </c>
+      <c r="AJ94">
+        <v>2.75</v>
+      </c>
+      <c r="AK94">
+        <v>1.22</v>
+      </c>
+      <c r="AL94">
+        <v>1.26</v>
+      </c>
+      <c r="AM94">
+        <v>1.7</v>
+      </c>
+      <c r="AN94">
+        <v>1.4</v>
+      </c>
+      <c r="AO94">
+        <v>1</v>
+      </c>
+      <c r="AP94">
+        <v>1.67</v>
+      </c>
+      <c r="AQ94">
+        <v>0.83</v>
+      </c>
+      <c r="AR94">
+        <v>2.04</v>
+      </c>
+      <c r="AS94">
+        <v>1.47</v>
+      </c>
+      <c r="AT94">
+        <v>3.51</v>
+      </c>
+      <c r="AU94">
+        <v>14</v>
+      </c>
+      <c r="AV94">
+        <v>5</v>
+      </c>
+      <c r="AW94">
+        <v>5</v>
+      </c>
+      <c r="AX94">
+        <v>7</v>
+      </c>
+      <c r="AY94">
+        <v>19</v>
+      </c>
+      <c r="AZ94">
+        <v>12</v>
+      </c>
+      <c r="BA94">
+        <v>4</v>
+      </c>
+      <c r="BB94">
+        <v>2</v>
+      </c>
+      <c r="BC94">
+        <v>6</v>
+      </c>
+      <c r="BD94">
+        <v>2.12</v>
+      </c>
+      <c r="BE94">
+        <v>6.75</v>
+      </c>
+      <c r="BF94">
+        <v>2.07</v>
+      </c>
+      <c r="BG94">
+        <v>1.17</v>
+      </c>
+      <c r="BH94">
+        <v>4.3</v>
+      </c>
+      <c r="BI94">
+        <v>1.3</v>
+      </c>
+      <c r="BJ94">
+        <v>3.28</v>
+      </c>
+      <c r="BK94">
+        <v>1.5</v>
+      </c>
+      <c r="BL94">
+        <v>2.38</v>
+      </c>
+      <c r="BM94">
+        <v>1.8</v>
+      </c>
+      <c r="BN94">
+        <v>1.89</v>
+      </c>
+      <c r="BO94">
+        <v>2.23</v>
+      </c>
+      <c r="BP94">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -493,6 +493,9 @@
     <t>['14', '69', '58', '71', '51']</t>
   </si>
   <si>
+    <t>['33']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -665,6 +668,9 @@
   </si>
   <si>
     <t>['42', '26', '45', '66']</t>
+  </si>
+  <si>
+    <t>['26', '78']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1282,7 +1288,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1694,7 +1700,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1900,7 +1906,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1981,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2518,7 +2524,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2724,7 +2730,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2930,7 +2936,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3136,7 +3142,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3214,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3548,7 +3554,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3960,7 +3966,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4372,7 +4378,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4578,7 +4584,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4990,7 +4996,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5071,7 +5077,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR20">
         <v>1.5</v>
@@ -5196,7 +5202,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5402,7 +5408,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5608,7 +5614,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5814,7 +5820,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6226,7 +6232,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6432,7 +6438,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6844,7 +6850,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -6922,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
         <v>0.67</v>
@@ -7050,7 +7056,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7462,7 +7468,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7668,7 +7674,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -8080,7 +8086,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8286,7 +8292,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8570,7 +8576,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>0.83</v>
@@ -8698,7 +8704,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8904,7 +8910,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -9316,7 +9322,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9603,7 +9609,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
         <v>1.44</v>
@@ -9934,7 +9940,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10140,7 +10146,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10346,7 +10352,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10552,7 +10558,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10758,7 +10764,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10964,7 +10970,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11866,7 +11872,7 @@
         <v>1.33</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
         <v>0.83</v>
@@ -12200,7 +12206,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12818,7 +12824,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13230,7 +13236,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13436,7 +13442,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13517,7 +13523,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR61">
         <v>2.18</v>
@@ -13642,7 +13648,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13848,7 +13854,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -14054,7 +14060,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14260,7 +14266,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14672,7 +14678,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14878,7 +14884,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15290,7 +15296,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15368,7 +15374,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70">
         <v>0.6</v>
@@ -15702,7 +15708,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15908,7 +15914,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -16114,7 +16120,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16320,7 +16326,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16401,7 +16407,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ75">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR75">
         <v>1.82</v>
@@ -16526,7 +16532,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16732,7 +16738,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16938,7 +16944,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -17144,7 +17150,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17350,7 +17356,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17556,7 +17562,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>1.6</v>
@@ -17762,7 +17768,7 @@
         <v>149</v>
       </c>
       <c r="P82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>2.11</v>
@@ -17968,7 +17974,7 @@
         <v>89</v>
       </c>
       <c r="P83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q83">
         <v>2.85</v>
@@ -18380,7 +18386,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>4.1</v>
@@ -18586,7 +18592,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q86">
         <v>1.57</v>
@@ -18998,7 +19004,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19410,7 +19416,7 @@
         <v>156</v>
       </c>
       <c r="P90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>3.96</v>
@@ -19822,7 +19828,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>4.5</v>
@@ -20234,7 +20240,7 @@
         <v>158</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20391,6 +20397,212 @@
       </c>
       <c r="BP94">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7785903</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s">
+        <v>85</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>2</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>2</v>
+      </c>
+      <c r="N95">
+        <v>3</v>
+      </c>
+      <c r="O95" t="s">
+        <v>159</v>
+      </c>
+      <c r="P95" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q95">
+        <v>2.1</v>
+      </c>
+      <c r="R95">
+        <v>2.55</v>
+      </c>
+      <c r="S95">
+        <v>3.8</v>
+      </c>
+      <c r="T95">
+        <v>1.18</v>
+      </c>
+      <c r="U95">
+        <v>4.33</v>
+      </c>
+      <c r="V95">
+        <v>2.28</v>
+      </c>
+      <c r="W95">
+        <v>1.6</v>
+      </c>
+      <c r="X95">
+        <v>4.1</v>
+      </c>
+      <c r="Y95">
+        <v>1.2</v>
+      </c>
+      <c r="Z95">
+        <v>1.7</v>
+      </c>
+      <c r="AA95">
+        <v>4.1</v>
+      </c>
+      <c r="AB95">
+        <v>3.8</v>
+      </c>
+      <c r="AC95">
+        <v>1.01</v>
+      </c>
+      <c r="AD95">
+        <v>17</v>
+      </c>
+      <c r="AE95">
+        <v>1.11</v>
+      </c>
+      <c r="AF95">
+        <v>6</v>
+      </c>
+      <c r="AG95">
+        <v>1.36</v>
+      </c>
+      <c r="AH95">
+        <v>2.43</v>
+      </c>
+      <c r="AI95">
+        <v>1.52</v>
+      </c>
+      <c r="AJ95">
+        <v>2.72</v>
+      </c>
+      <c r="AK95">
+        <v>1.22</v>
+      </c>
+      <c r="AL95">
+        <v>1.27</v>
+      </c>
+      <c r="AM95">
+        <v>2.1</v>
+      </c>
+      <c r="AN95">
+        <v>2</v>
+      </c>
+      <c r="AO95">
+        <v>0.8</v>
+      </c>
+      <c r="AP95">
+        <v>1.67</v>
+      </c>
+      <c r="AQ95">
+        <v>1.17</v>
+      </c>
+      <c r="AR95">
+        <v>2.13</v>
+      </c>
+      <c r="AS95">
+        <v>1.28</v>
+      </c>
+      <c r="AT95">
+        <v>3.41</v>
+      </c>
+      <c r="AU95">
+        <v>4</v>
+      </c>
+      <c r="AV95">
+        <v>8</v>
+      </c>
+      <c r="AW95">
+        <v>7</v>
+      </c>
+      <c r="AX95">
+        <v>4</v>
+      </c>
+      <c r="AY95">
+        <v>11</v>
+      </c>
+      <c r="AZ95">
+        <v>12</v>
+      </c>
+      <c r="BA95">
+        <v>7</v>
+      </c>
+      <c r="BB95">
+        <v>2</v>
+      </c>
+      <c r="BC95">
+        <v>9</v>
+      </c>
+      <c r="BD95">
+        <v>1.8</v>
+      </c>
+      <c r="BE95">
+        <v>6.65</v>
+      </c>
+      <c r="BF95">
+        <v>2.46</v>
+      </c>
+      <c r="BG95">
+        <v>1.15</v>
+      </c>
+      <c r="BH95">
+        <v>4.4</v>
+      </c>
+      <c r="BI95">
+        <v>1.24</v>
+      </c>
+      <c r="BJ95">
+        <v>3.34</v>
+      </c>
+      <c r="BK95">
+        <v>1.48</v>
+      </c>
+      <c r="BL95">
+        <v>2.49</v>
+      </c>
+      <c r="BM95">
+        <v>1.83</v>
+      </c>
+      <c r="BN95">
+        <v>1.89</v>
+      </c>
+      <c r="BO95">
+        <v>2.31</v>
+      </c>
+      <c r="BP95">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,9 @@
     <t>['33']</t>
   </si>
   <si>
+    <t>['69']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -671,6 +674,9 @@
   </si>
   <si>
     <t>['26', '78']</t>
+  </si>
+  <si>
+    <t>['44', '52', '21', '24']</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP95"/>
+  <dimension ref="A1:BP96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1288,7 +1294,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1700,7 +1706,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1781,7 +1787,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ4">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1906,7 +1912,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2524,7 +2530,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2730,7 +2736,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2936,7 +2942,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3142,7 +3148,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3554,7 +3560,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3966,7 +3972,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4250,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16">
         <v>0.6</v>
@@ -4378,7 +4384,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4584,7 +4590,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4665,7 +4671,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ18">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR18">
         <v>2.04</v>
@@ -4996,7 +5002,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5202,7 +5208,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5408,7 +5414,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5614,7 +5620,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5820,7 +5826,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6232,7 +6238,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6438,7 +6444,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6850,7 +6856,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -7056,7 +7062,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7468,7 +7474,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7546,7 +7552,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32">
         <v>2.33</v>
@@ -7674,7 +7680,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -8086,7 +8092,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8292,7 +8298,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8704,7 +8710,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8910,7 +8916,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -9197,7 +9203,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR40">
         <v>1.57</v>
@@ -9322,7 +9328,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9940,7 +9946,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10146,7 +10152,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10224,7 +10230,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ45">
         <v>1.8</v>
@@ -10352,7 +10358,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10558,7 +10564,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10764,7 +10770,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10970,7 +10976,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11463,7 +11469,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ51">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR51">
         <v>1.23</v>
@@ -12206,7 +12212,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12824,7 +12830,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13111,7 +13117,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ59">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -13236,7 +13242,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13314,7 +13320,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ60">
         <v>2.14</v>
@@ -13442,7 +13448,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13648,7 +13654,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13854,7 +13860,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -14060,7 +14066,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14266,7 +14272,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14678,7 +14684,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14884,7 +14890,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15296,7 +15302,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15708,7 +15714,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15914,7 +15920,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -16120,7 +16126,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16326,7 +16332,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16532,7 +16538,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16738,7 +16744,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16816,7 +16822,7 @@
         <v>0</v>
       </c>
       <c r="AP77">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ77">
         <v>0.17</v>
@@ -16944,7 +16950,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -17150,7 +17156,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17231,7 +17237,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ79">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR79">
         <v>1.13</v>
@@ -17356,7 +17362,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17562,7 +17568,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q81">
         <v>1.6</v>
@@ -17768,7 +17774,7 @@
         <v>149</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q82">
         <v>2.11</v>
@@ -17974,7 +17980,7 @@
         <v>89</v>
       </c>
       <c r="P83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q83">
         <v>2.85</v>
@@ -18386,7 +18392,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>4.1</v>
@@ -18592,7 +18598,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q86">
         <v>1.57</v>
@@ -19004,7 +19010,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19416,7 +19422,7 @@
         <v>156</v>
       </c>
       <c r="P90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q90">
         <v>3.96</v>
@@ -19828,7 +19834,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>4.5</v>
@@ -20240,7 +20246,7 @@
         <v>158</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20446,7 +20452,7 @@
         <v>159</v>
       </c>
       <c r="P95" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20603,6 +20609,212 @@
       </c>
       <c r="BP95">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7785900</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45831.58333333334</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>84</v>
+      </c>
+      <c r="H96" t="s">
+        <v>81</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>4</v>
+      </c>
+      <c r="N96">
+        <v>5</v>
+      </c>
+      <c r="O96" t="s">
+        <v>160</v>
+      </c>
+      <c r="P96" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q96">
+        <v>3.15</v>
+      </c>
+      <c r="R96">
+        <v>2.28</v>
+      </c>
+      <c r="S96">
+        <v>2.74</v>
+      </c>
+      <c r="T96">
+        <v>1.25</v>
+      </c>
+      <c r="U96">
+        <v>3.4</v>
+      </c>
+      <c r="V96">
+        <v>2.4</v>
+      </c>
+      <c r="W96">
+        <v>1.55</v>
+      </c>
+      <c r="X96">
+        <v>4.4</v>
+      </c>
+      <c r="Y96">
+        <v>1.15</v>
+      </c>
+      <c r="Z96">
+        <v>2.4</v>
+      </c>
+      <c r="AA96">
+        <v>3.76</v>
+      </c>
+      <c r="AB96">
+        <v>2.35</v>
+      </c>
+      <c r="AC96">
+        <v>1</v>
+      </c>
+      <c r="AD96">
+        <v>15</v>
+      </c>
+      <c r="AE96">
+        <v>1.17</v>
+      </c>
+      <c r="AF96">
+        <v>4.8</v>
+      </c>
+      <c r="AG96">
+        <v>1.57</v>
+      </c>
+      <c r="AH96">
+        <v>2.3</v>
+      </c>
+      <c r="AI96">
+        <v>1.5</v>
+      </c>
+      <c r="AJ96">
+        <v>2.45</v>
+      </c>
+      <c r="AK96">
+        <v>1.29</v>
+      </c>
+      <c r="AL96">
+        <v>1.29</v>
+      </c>
+      <c r="AM96">
+        <v>1.44</v>
+      </c>
+      <c r="AN96">
+        <v>0.4</v>
+      </c>
+      <c r="AO96">
+        <v>0.17</v>
+      </c>
+      <c r="AP96">
+        <v>0.33</v>
+      </c>
+      <c r="AQ96">
+        <v>0.57</v>
+      </c>
+      <c r="AR96">
+        <v>1.09</v>
+      </c>
+      <c r="AS96">
+        <v>1.11</v>
+      </c>
+      <c r="AT96">
+        <v>2.2</v>
+      </c>
+      <c r="AU96">
+        <v>6</v>
+      </c>
+      <c r="AV96">
+        <v>6</v>
+      </c>
+      <c r="AW96">
+        <v>5</v>
+      </c>
+      <c r="AX96">
+        <v>6</v>
+      </c>
+      <c r="AY96">
+        <v>11</v>
+      </c>
+      <c r="AZ96">
+        <v>12</v>
+      </c>
+      <c r="BA96">
+        <v>3</v>
+      </c>
+      <c r="BB96">
+        <v>5</v>
+      </c>
+      <c r="BC96">
+        <v>8</v>
+      </c>
+      <c r="BD96">
+        <v>1.66</v>
+      </c>
+      <c r="BE96">
+        <v>6.75</v>
+      </c>
+      <c r="BF96">
+        <v>2.9</v>
+      </c>
+      <c r="BG96">
+        <v>1.23</v>
+      </c>
+      <c r="BH96">
+        <v>3.7</v>
+      </c>
+      <c r="BI96">
+        <v>1.37</v>
+      </c>
+      <c r="BJ96">
+        <v>2.65</v>
+      </c>
+      <c r="BK96">
+        <v>1.68</v>
+      </c>
+      <c r="BL96">
+        <v>2.08</v>
+      </c>
+      <c r="BM96">
+        <v>2</v>
+      </c>
+      <c r="BN96">
+        <v>1.71</v>
+      </c>
+      <c r="BO96">
+        <v>2.79</v>
+      </c>
+      <c r="BP96">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -20751,10 +20751,10 @@
         <v>2.2</v>
       </c>
       <c r="AU96">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW96">
         <v>5</v>
@@ -20763,10 +20763,10 @@
         <v>6</v>
       </c>
       <c r="AY96">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ96">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA96">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -20751,10 +20751,10 @@
         <v>2.2</v>
       </c>
       <c r="AU96">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV96">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW96">
         <v>5</v>
@@ -20763,10 +20763,10 @@
         <v>6</v>
       </c>
       <c r="AY96">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ96">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA96">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,12 @@
     <t>['69']</t>
   </si>
   <si>
+    <t>['32', '17', '7']</t>
+  </si>
+  <si>
+    <t>['74', '83']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -677,6 +683,12 @@
   </si>
   <si>
     <t>['44', '52', '21', '24']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
+    <t>['16', '32']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP96"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1294,7 +1306,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1375,7 +1387,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ2">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1578,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.83</v>
@@ -1706,7 +1718,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1912,7 +1924,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2530,7 +2542,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2736,7 +2748,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2942,7 +2954,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3148,7 +3160,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3560,7 +3572,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3972,7 +3984,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4050,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15">
         <v>1.33</v>
@@ -4259,7 +4271,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ16">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4384,7 +4396,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4590,7 +4602,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -4874,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0.17</v>
@@ -5002,7 +5014,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5208,7 +5220,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5414,7 +5426,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5620,7 +5632,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5826,7 +5838,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6113,7 +6125,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ25">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR25">
         <v>1.44</v>
@@ -6238,7 +6250,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6444,7 +6456,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6856,7 +6868,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -7062,7 +7074,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7474,7 +7486,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7680,7 +7692,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -7758,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
         <v>1.8</v>
@@ -8092,7 +8104,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8298,7 +8310,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8585,7 +8597,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ37">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR37">
         <v>1.82</v>
@@ -8710,7 +8722,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8916,7 +8928,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -8997,7 +9009,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ39">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR39">
         <v>1.43</v>
@@ -9328,7 +9340,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9946,7 +9958,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10024,7 +10036,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ44">
         <v>1.5</v>
@@ -10152,7 +10164,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10358,7 +10370,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10436,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.67</v>
@@ -10564,7 +10576,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10770,7 +10782,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10976,7 +10988,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11057,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="AQ49">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR49">
         <v>1.32</v>
@@ -12087,7 +12099,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR54">
         <v>1.75</v>
@@ -12212,7 +12224,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12830,7 +12842,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13242,7 +13254,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13448,7 +13460,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13526,7 +13538,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>1.17</v>
@@ -13654,7 +13666,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13860,7 +13872,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -14066,7 +14078,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14144,7 +14156,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>0.67</v>
@@ -14272,7 +14284,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14353,7 +14365,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ65">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR65">
         <v>1.21</v>
@@ -14684,7 +14696,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14890,7 +14902,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15302,7 +15314,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15383,7 +15395,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -15714,7 +15726,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15920,7 +15932,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -15998,7 +16010,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16126,7 +16138,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16204,7 +16216,7 @@
         <v>2.2</v>
       </c>
       <c r="AP74">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
         <v>2.14</v>
@@ -16332,7 +16344,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16538,7 +16550,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16744,7 +16756,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16950,7 +16962,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -17156,7 +17168,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17362,7 +17374,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17568,7 +17580,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>1.6</v>
@@ -17649,7 +17661,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ81">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -17774,7 +17786,7 @@
         <v>149</v>
       </c>
       <c r="P82" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>2.11</v>
@@ -17980,7 +17992,7 @@
         <v>89</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>2.85</v>
@@ -18392,7 +18404,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>4.1</v>
@@ -18598,7 +18610,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q86">
         <v>1.57</v>
@@ -18882,7 +18894,7 @@
         <v>1.33</v>
       </c>
       <c r="AP87">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -19010,7 +19022,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19091,7 +19103,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ88">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AR88">
         <v>1.43</v>
@@ -19422,7 +19434,7 @@
         <v>156</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q90">
         <v>3.96</v>
@@ -19834,7 +19846,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>4.5</v>
@@ -20246,7 +20258,7 @@
         <v>158</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20452,7 +20464,7 @@
         <v>159</v>
       </c>
       <c r="P95" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20658,7 +20670,7 @@
         <v>160</v>
       </c>
       <c r="P96" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q96">
         <v>3.15</v>
@@ -20815,6 +20827,418 @@
       </c>
       <c r="BP96">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7785907</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45836.375</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>83</v>
+      </c>
+      <c r="H97" t="s">
+        <v>84</v>
+      </c>
+      <c r="I97">
+        <v>3</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>3</v>
+      </c>
+      <c r="L97">
+        <v>3</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>4</v>
+      </c>
+      <c r="O97" t="s">
+        <v>161</v>
+      </c>
+      <c r="P97" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q97">
+        <v>2.08</v>
+      </c>
+      <c r="R97">
+        <v>2.31</v>
+      </c>
+      <c r="S97">
+        <v>4.7</v>
+      </c>
+      <c r="T97">
+        <v>1.3</v>
+      </c>
+      <c r="U97">
+        <v>3.2</v>
+      </c>
+      <c r="V97">
+        <v>2.55</v>
+      </c>
+      <c r="W97">
+        <v>1.5</v>
+      </c>
+      <c r="X97">
+        <v>6.15</v>
+      </c>
+      <c r="Y97">
+        <v>1.11</v>
+      </c>
+      <c r="Z97">
+        <v>1.59</v>
+      </c>
+      <c r="AA97">
+        <v>4.15</v>
+      </c>
+      <c r="AB97">
+        <v>5</v>
+      </c>
+      <c r="AC97">
+        <v>1.03</v>
+      </c>
+      <c r="AD97">
+        <v>11</v>
+      </c>
+      <c r="AE97">
+        <v>1.2</v>
+      </c>
+      <c r="AF97">
+        <v>4</v>
+      </c>
+      <c r="AG97">
+        <v>1.73</v>
+      </c>
+      <c r="AH97">
+        <v>2.1</v>
+      </c>
+      <c r="AI97">
+        <v>1.81</v>
+      </c>
+      <c r="AJ97">
+        <v>1.98</v>
+      </c>
+      <c r="AK97">
+        <v>1.18</v>
+      </c>
+      <c r="AL97">
+        <v>1.24</v>
+      </c>
+      <c r="AM97">
+        <v>2.2</v>
+      </c>
+      <c r="AN97">
+        <v>1.4</v>
+      </c>
+      <c r="AO97">
+        <v>0.83</v>
+      </c>
+      <c r="AP97">
+        <v>1.67</v>
+      </c>
+      <c r="AQ97">
+        <v>0.71</v>
+      </c>
+      <c r="AR97">
+        <v>1.34</v>
+      </c>
+      <c r="AS97">
+        <v>1.1</v>
+      </c>
+      <c r="AT97">
+        <v>2.44</v>
+      </c>
+      <c r="AU97">
+        <v>5</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>3</v>
+      </c>
+      <c r="AX97">
+        <v>4</v>
+      </c>
+      <c r="AY97">
+        <v>8</v>
+      </c>
+      <c r="AZ97">
+        <v>6</v>
+      </c>
+      <c r="BA97">
+        <v>3</v>
+      </c>
+      <c r="BB97">
+        <v>6</v>
+      </c>
+      <c r="BC97">
+        <v>9</v>
+      </c>
+      <c r="BD97">
+        <v>1.59</v>
+      </c>
+      <c r="BE97">
+        <v>8.1</v>
+      </c>
+      <c r="BF97">
+        <v>2.65</v>
+      </c>
+      <c r="BG97">
+        <v>1.27</v>
+      </c>
+      <c r="BH97">
+        <v>3.25</v>
+      </c>
+      <c r="BI97">
+        <v>1.41</v>
+      </c>
+      <c r="BJ97">
+        <v>2.65</v>
+      </c>
+      <c r="BK97">
+        <v>2.08</v>
+      </c>
+      <c r="BL97">
+        <v>1.9</v>
+      </c>
+      <c r="BM97">
+        <v>2</v>
+      </c>
+      <c r="BN97">
+        <v>1.56</v>
+      </c>
+      <c r="BO97">
+        <v>2.5</v>
+      </c>
+      <c r="BP97">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7785908</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45836.375</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
+        <v>71</v>
+      </c>
+      <c r="H98" t="s">
+        <v>77</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>2</v>
+      </c>
+      <c r="N98">
+        <v>4</v>
+      </c>
+      <c r="O98" t="s">
+        <v>162</v>
+      </c>
+      <c r="P98" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q98">
+        <v>1.77</v>
+      </c>
+      <c r="R98">
+        <v>3.05</v>
+      </c>
+      <c r="S98">
+        <v>5.75</v>
+      </c>
+      <c r="T98">
+        <v>1.18</v>
+      </c>
+      <c r="U98">
+        <v>4.4</v>
+      </c>
+      <c r="V98">
+        <v>1.94</v>
+      </c>
+      <c r="W98">
+        <v>1.9</v>
+      </c>
+      <c r="X98">
+        <v>3.6</v>
+      </c>
+      <c r="Y98">
+        <v>1.22</v>
+      </c>
+      <c r="Z98">
+        <v>1.33</v>
+      </c>
+      <c r="AA98">
+        <v>5</v>
+      </c>
+      <c r="AB98">
+        <v>7.75</v>
+      </c>
+      <c r="AC98">
+        <v>1.01</v>
+      </c>
+      <c r="AD98">
+        <v>23</v>
+      </c>
+      <c r="AE98">
+        <v>1.05</v>
+      </c>
+      <c r="AF98">
+        <v>5.7</v>
+      </c>
+      <c r="AG98">
+        <v>1.3</v>
+      </c>
+      <c r="AH98">
+        <v>3.2</v>
+      </c>
+      <c r="AI98">
+        <v>1.53</v>
+      </c>
+      <c r="AJ98">
+        <v>2.25</v>
+      </c>
+      <c r="AK98">
+        <v>1.07</v>
+      </c>
+      <c r="AL98">
+        <v>1.14</v>
+      </c>
+      <c r="AM98">
+        <v>3.1</v>
+      </c>
+      <c r="AN98">
+        <v>2.17</v>
+      </c>
+      <c r="AO98">
+        <v>0.6</v>
+      </c>
+      <c r="AP98">
+        <v>2</v>
+      </c>
+      <c r="AQ98">
+        <v>0.67</v>
+      </c>
+      <c r="AR98">
+        <v>2.01</v>
+      </c>
+      <c r="AS98">
+        <v>1.48</v>
+      </c>
+      <c r="AT98">
+        <v>3.49</v>
+      </c>
+      <c r="AU98">
+        <v>12</v>
+      </c>
+      <c r="AV98">
+        <v>8</v>
+      </c>
+      <c r="AW98">
+        <v>9</v>
+      </c>
+      <c r="AX98">
+        <v>6</v>
+      </c>
+      <c r="AY98">
+        <v>21</v>
+      </c>
+      <c r="AZ98">
+        <v>14</v>
+      </c>
+      <c r="BA98">
+        <v>18</v>
+      </c>
+      <c r="BB98">
+        <v>5</v>
+      </c>
+      <c r="BC98">
+        <v>23</v>
+      </c>
+      <c r="BD98">
+        <v>1.21</v>
+      </c>
+      <c r="BE98">
+        <v>9.5</v>
+      </c>
+      <c r="BF98">
+        <v>5.75</v>
+      </c>
+      <c r="BG98">
+        <v>1.14</v>
+      </c>
+      <c r="BH98">
+        <v>5.45</v>
+      </c>
+      <c r="BI98">
+        <v>1.25</v>
+      </c>
+      <c r="BJ98">
+        <v>3.8</v>
+      </c>
+      <c r="BK98">
+        <v>1.32</v>
+      </c>
+      <c r="BL98">
+        <v>2.77</v>
+      </c>
+      <c r="BM98">
+        <v>1.63</v>
+      </c>
+      <c r="BN98">
+        <v>2.19</v>
+      </c>
+      <c r="BO98">
+        <v>1.98</v>
+      </c>
+      <c r="BP98">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="230">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,6 +505,18 @@
     <t>['74', '83']</t>
   </si>
   <si>
+    <t>['79']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['16', '57']</t>
+  </si>
+  <si>
+    <t>['49', '72']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -661,9 +673,6 @@
     <t>['65', '78', '89']</t>
   </si>
   <si>
-    <t>['89']</t>
-  </si>
-  <si>
     <t>['30', '52', '57', '83']</t>
   </si>
   <si>
@@ -685,10 +694,16 @@
     <t>['44', '52', '21', '24']</t>
   </si>
   <si>
-    <t>['79']</t>
-  </si>
-  <si>
     <t>['16', '32']</t>
+  </si>
+  <si>
+    <t>['45', '58']</t>
+  </si>
+  <si>
+    <t>['31', '12', '53', '68']</t>
+  </si>
+  <si>
+    <t>['19', '43']</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1321,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1718,7 +1733,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1796,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ4">
         <v>0.57</v>
@@ -1924,7 +1939,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2208,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
         <v>1.14</v>
@@ -2417,7 +2432,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2542,7 +2557,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2748,7 +2763,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2954,7 +2969,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3035,7 +3050,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ10">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3160,7 +3175,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3444,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3572,7 +3587,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3650,10 +3665,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ13">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3856,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ14">
         <v>0.67</v>
@@ -3984,7 +3999,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4396,7 +4411,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4602,7 +4617,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -5014,7 +5029,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5092,7 +5107,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ20">
         <v>1.17</v>
@@ -5220,7 +5235,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5301,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR21">
         <v>1.62</v>
@@ -5426,7 +5441,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5632,7 +5647,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5710,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23">
         <v>2.14</v>
@@ -5838,7 +5853,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6250,7 +6265,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6456,7 +6471,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6534,7 +6549,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ27">
         <v>0.83</v>
@@ -6868,7 +6883,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -7074,7 +7089,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7152,7 +7167,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>1.33</v>
@@ -7361,7 +7376,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR31">
         <v>1.81</v>
@@ -7486,7 +7501,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7567,7 +7582,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ32">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR32">
         <v>1.02</v>
@@ -7692,7 +7707,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -7773,7 +7788,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR33">
         <v>0.71</v>
@@ -7976,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ34">
         <v>0.17</v>
@@ -8104,7 +8119,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8182,10 +8197,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR35">
         <v>2.01</v>
@@ -8310,7 +8325,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8722,7 +8737,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8928,7 +8943,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -9212,7 +9227,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ40">
         <v>0.57</v>
@@ -9340,7 +9355,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9624,7 +9639,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ42">
         <v>1.17</v>
@@ -9833,7 +9848,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR43">
         <v>1.63</v>
@@ -9958,7 +9973,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10039,7 +10054,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR44">
         <v>1.31</v>
@@ -10164,7 +10179,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10245,7 +10260,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ45">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.05</v>
@@ -10370,7 +10385,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10576,7 +10591,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10654,7 +10669,7 @@
         <v>2.33</v>
       </c>
       <c r="AP47">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ47">
         <v>2.14</v>
@@ -10782,7 +10797,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -10988,7 +11003,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11272,7 +11287,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11684,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ52">
         <v>0.17</v>
@@ -12096,7 +12111,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ54">
         <v>0.71</v>
@@ -12224,7 +12239,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12305,7 +12320,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ55">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR55">
         <v>1.75</v>
@@ -12842,7 +12857,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -12923,7 +12938,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ58">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR58">
         <v>1.66</v>
@@ -13126,7 +13141,7 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ59">
         <v>0.57</v>
@@ -13254,7 +13269,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13460,7 +13475,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13666,7 +13681,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13747,7 +13762,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ62">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR62">
         <v>1.09</v>
@@ -13872,7 +13887,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -13953,7 +13968,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR63">
         <v>2.64</v>
@@ -14078,7 +14093,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14284,7 +14299,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14568,7 +14583,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ66">
         <v>1.14</v>
@@ -14696,7 +14711,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14774,7 +14789,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ67">
         <v>1.33</v>
@@ -14902,7 +14917,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15186,7 +15201,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ69">
         <v>0.83</v>
@@ -15314,7 +15329,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15598,10 +15613,10 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ71">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR71">
         <v>1.65</v>
@@ -15726,7 +15741,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15804,10 +15819,10 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ72">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR72">
         <v>1.45</v>
@@ -15932,7 +15947,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -16013,7 +16028,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR73">
         <v>2.07</v>
@@ -16138,7 +16153,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16344,7 +16359,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16550,7 +16565,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16631,7 +16646,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ76">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR76">
         <v>2.38</v>
@@ -16756,7 +16771,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16962,7 +16977,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -17168,7 +17183,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17374,7 +17389,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17580,7 +17595,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q81">
         <v>1.6</v>
@@ -17658,7 +17673,7 @@
         <v>0.8</v>
       </c>
       <c r="AP81">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ81">
         <v>0.71</v>
@@ -17786,7 +17801,7 @@
         <v>149</v>
       </c>
       <c r="P82" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q82">
         <v>2.11</v>
@@ -17864,10 +17879,10 @@
         <v>1.4</v>
       </c>
       <c r="AP82">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ82">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR82">
         <v>1.71</v>
@@ -17992,7 +18007,7 @@
         <v>89</v>
       </c>
       <c r="P83" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="Q83">
         <v>2.85</v>
@@ -18073,7 +18088,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AR83">
         <v>1.67</v>
@@ -18276,7 +18291,7 @@
         <v>1.6</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ84">
         <v>1.14</v>
@@ -18404,7 +18419,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>4.1</v>
@@ -18482,10 +18497,10 @@
         <v>1.2</v>
       </c>
       <c r="AP85">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR85">
         <v>1.27</v>
@@ -18610,7 +18625,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q86">
         <v>1.57</v>
@@ -18688,7 +18703,7 @@
         <v>0.8</v>
       </c>
       <c r="AP86">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ86">
         <v>0.83</v>
@@ -19022,7 +19037,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19434,7 +19449,7 @@
         <v>156</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q90">
         <v>3.96</v>
@@ -19846,7 +19861,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q92">
         <v>4.5</v>
@@ -20258,7 +20273,7 @@
         <v>158</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20464,7 +20479,7 @@
         <v>159</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20670,7 +20685,7 @@
         <v>160</v>
       </c>
       <c r="P96" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q96">
         <v>3.15</v>
@@ -20876,7 +20891,7 @@
         <v>161</v>
       </c>
       <c r="P97" t="s">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="Q97">
         <v>2.08</v>
@@ -21082,7 +21097,7 @@
         <v>162</v>
       </c>
       <c r="P98" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q98">
         <v>1.77</v>
@@ -21239,6 +21254,1036 @@
       </c>
       <c r="BP98">
         <v>1.77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7785913</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45836.45833333334</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>81</v>
+      </c>
+      <c r="H99" t="s">
+        <v>76</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>163</v>
+      </c>
+      <c r="P99" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q99">
+        <v>4.4</v>
+      </c>
+      <c r="R99">
+        <v>2.27</v>
+      </c>
+      <c r="S99">
+        <v>2.29</v>
+      </c>
+      <c r="T99">
+        <v>1.29</v>
+      </c>
+      <c r="U99">
+        <v>3.2</v>
+      </c>
+      <c r="V99">
+        <v>2.47</v>
+      </c>
+      <c r="W99">
+        <v>1.5</v>
+      </c>
+      <c r="X99">
+        <v>5.5</v>
+      </c>
+      <c r="Y99">
+        <v>1.11</v>
+      </c>
+      <c r="Z99">
+        <v>3.53</v>
+      </c>
+      <c r="AA99">
+        <v>3.41</v>
+      </c>
+      <c r="AB99">
+        <v>1.91</v>
+      </c>
+      <c r="AC99">
+        <v>1.01</v>
+      </c>
+      <c r="AD99">
+        <v>13</v>
+      </c>
+      <c r="AE99">
+        <v>1.22</v>
+      </c>
+      <c r="AF99">
+        <v>4.2</v>
+      </c>
+      <c r="AG99">
+        <v>1.79</v>
+      </c>
+      <c r="AH99">
+        <v>1.91</v>
+      </c>
+      <c r="AI99">
+        <v>1.7</v>
+      </c>
+      <c r="AJ99">
+        <v>2.1</v>
+      </c>
+      <c r="AK99">
+        <v>2</v>
+      </c>
+      <c r="AL99">
+        <v>1.24</v>
+      </c>
+      <c r="AM99">
+        <v>1.22</v>
+      </c>
+      <c r="AN99">
+        <v>0.4</v>
+      </c>
+      <c r="AO99">
+        <v>1</v>
+      </c>
+      <c r="AP99">
+        <v>0.5</v>
+      </c>
+      <c r="AQ99">
+        <v>1</v>
+      </c>
+      <c r="AR99">
+        <v>1.45</v>
+      </c>
+      <c r="AS99">
+        <v>1.63</v>
+      </c>
+      <c r="AT99">
+        <v>3.08</v>
+      </c>
+      <c r="AU99">
+        <v>5</v>
+      </c>
+      <c r="AV99">
+        <v>6</v>
+      </c>
+      <c r="AW99">
+        <v>2</v>
+      </c>
+      <c r="AX99">
+        <v>4</v>
+      </c>
+      <c r="AY99">
+        <v>7</v>
+      </c>
+      <c r="AZ99">
+        <v>10</v>
+      </c>
+      <c r="BA99">
+        <v>1</v>
+      </c>
+      <c r="BB99">
+        <v>4</v>
+      </c>
+      <c r="BC99">
+        <v>5</v>
+      </c>
+      <c r="BD99">
+        <v>3.45</v>
+      </c>
+      <c r="BE99">
+        <v>6.75</v>
+      </c>
+      <c r="BF99">
+        <v>1.48</v>
+      </c>
+      <c r="BG99">
+        <v>1.17</v>
+      </c>
+      <c r="BH99">
+        <v>3.9</v>
+      </c>
+      <c r="BI99">
+        <v>1.38</v>
+      </c>
+      <c r="BJ99">
+        <v>3.02</v>
+      </c>
+      <c r="BK99">
+        <v>1.72</v>
+      </c>
+      <c r="BL99">
+        <v>2.29</v>
+      </c>
+      <c r="BM99">
+        <v>1.95</v>
+      </c>
+      <c r="BN99">
+        <v>1.82</v>
+      </c>
+      <c r="BO99">
+        <v>2.45</v>
+      </c>
+      <c r="BP99">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7785909</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45836.45833333334</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>82</v>
+      </c>
+      <c r="H100" t="s">
+        <v>79</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100" t="s">
+        <v>89</v>
+      </c>
+      <c r="P100" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q100">
+        <v>1.61</v>
+      </c>
+      <c r="R100">
+        <v>3</v>
+      </c>
+      <c r="S100">
+        <v>5.6</v>
+      </c>
+      <c r="T100">
+        <v>1.18</v>
+      </c>
+      <c r="U100">
+        <v>4.5</v>
+      </c>
+      <c r="V100">
+        <v>1.8</v>
+      </c>
+      <c r="W100">
+        <v>1.88</v>
+      </c>
+      <c r="X100">
+        <v>3.3</v>
+      </c>
+      <c r="Y100">
+        <v>1.24</v>
+      </c>
+      <c r="Z100">
+        <v>1.25</v>
+      </c>
+      <c r="AA100">
+        <v>5.8</v>
+      </c>
+      <c r="AB100">
+        <v>7.9</v>
+      </c>
+      <c r="AC100">
+        <v>1.01</v>
+      </c>
+      <c r="AD100">
+        <v>26</v>
+      </c>
+      <c r="AE100">
+        <v>1.09</v>
+      </c>
+      <c r="AF100">
+        <v>6.3</v>
+      </c>
+      <c r="AG100">
+        <v>1.31</v>
+      </c>
+      <c r="AH100">
+        <v>3.15</v>
+      </c>
+      <c r="AI100">
+        <v>1.57</v>
+      </c>
+      <c r="AJ100">
+        <v>2.25</v>
+      </c>
+      <c r="AK100">
+        <v>1.08</v>
+      </c>
+      <c r="AL100">
+        <v>1.13</v>
+      </c>
+      <c r="AM100">
+        <v>3.6</v>
+      </c>
+      <c r="AN100">
+        <v>2.6</v>
+      </c>
+      <c r="AO100">
+        <v>1.5</v>
+      </c>
+      <c r="AP100">
+        <v>2.33</v>
+      </c>
+      <c r="AQ100">
+        <v>1.43</v>
+      </c>
+      <c r="AR100">
+        <v>2.13</v>
+      </c>
+      <c r="AS100">
+        <v>1.48</v>
+      </c>
+      <c r="AT100">
+        <v>3.61</v>
+      </c>
+      <c r="AU100">
+        <v>3</v>
+      </c>
+      <c r="AV100">
+        <v>4</v>
+      </c>
+      <c r="AW100">
+        <v>11</v>
+      </c>
+      <c r="AX100">
+        <v>9</v>
+      </c>
+      <c r="AY100">
+        <v>14</v>
+      </c>
+      <c r="AZ100">
+        <v>13</v>
+      </c>
+      <c r="BA100">
+        <v>4</v>
+      </c>
+      <c r="BB100">
+        <v>4</v>
+      </c>
+      <c r="BC100">
+        <v>8</v>
+      </c>
+      <c r="BD100">
+        <v>1.15</v>
+      </c>
+      <c r="BE100">
+        <v>12.75</v>
+      </c>
+      <c r="BF100">
+        <v>6.7</v>
+      </c>
+      <c r="BG100">
+        <v>1.13</v>
+      </c>
+      <c r="BH100">
+        <v>4.4</v>
+      </c>
+      <c r="BI100">
+        <v>1.26</v>
+      </c>
+      <c r="BJ100">
+        <v>3.3</v>
+      </c>
+      <c r="BK100">
+        <v>1.44</v>
+      </c>
+      <c r="BL100">
+        <v>2.48</v>
+      </c>
+      <c r="BM100">
+        <v>1.77</v>
+      </c>
+      <c r="BN100">
+        <v>1.98</v>
+      </c>
+      <c r="BO100">
+        <v>2.19</v>
+      </c>
+      <c r="BP100">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7785914</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45836.45833333334</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>74</v>
+      </c>
+      <c r="H101" t="s">
+        <v>73</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>2</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101" t="s">
+        <v>164</v>
+      </c>
+      <c r="P101" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q101">
+        <v>2.15</v>
+      </c>
+      <c r="R101">
+        <v>2.5</v>
+      </c>
+      <c r="S101">
+        <v>3.2</v>
+      </c>
+      <c r="T101">
+        <v>1.23</v>
+      </c>
+      <c r="U101">
+        <v>4</v>
+      </c>
+      <c r="V101">
+        <v>2.11</v>
+      </c>
+      <c r="W101">
+        <v>1.78</v>
+      </c>
+      <c r="X101">
+        <v>4</v>
+      </c>
+      <c r="Y101">
+        <v>1.18</v>
+      </c>
+      <c r="Z101">
+        <v>1.94</v>
+      </c>
+      <c r="AA101">
+        <v>3.9</v>
+      </c>
+      <c r="AB101">
+        <v>3.05</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>16.5</v>
+      </c>
+      <c r="AE101">
+        <v>1.12</v>
+      </c>
+      <c r="AF101">
+        <v>6</v>
+      </c>
+      <c r="AG101">
+        <v>1.41</v>
+      </c>
+      <c r="AH101">
+        <v>2.69</v>
+      </c>
+      <c r="AI101">
+        <v>1.38</v>
+      </c>
+      <c r="AJ101">
+        <v>2.8</v>
+      </c>
+      <c r="AK101">
+        <v>1.25</v>
+      </c>
+      <c r="AL101">
+        <v>1.22</v>
+      </c>
+      <c r="AM101">
+        <v>1.75</v>
+      </c>
+      <c r="AN101">
+        <v>1.33</v>
+      </c>
+      <c r="AO101">
+        <v>1.8</v>
+      </c>
+      <c r="AP101">
+        <v>1.14</v>
+      </c>
+      <c r="AQ101">
+        <v>2</v>
+      </c>
+      <c r="AR101">
+        <v>1.57</v>
+      </c>
+      <c r="AS101">
+        <v>1.47</v>
+      </c>
+      <c r="AT101">
+        <v>3.04</v>
+      </c>
+      <c r="AU101">
+        <v>2</v>
+      </c>
+      <c r="AV101">
+        <v>7</v>
+      </c>
+      <c r="AW101">
+        <v>3</v>
+      </c>
+      <c r="AX101">
+        <v>6</v>
+      </c>
+      <c r="AY101">
+        <v>5</v>
+      </c>
+      <c r="AZ101">
+        <v>13</v>
+      </c>
+      <c r="BA101">
+        <v>6</v>
+      </c>
+      <c r="BB101">
+        <v>4</v>
+      </c>
+      <c r="BC101">
+        <v>10</v>
+      </c>
+      <c r="BD101">
+        <v>1.65</v>
+      </c>
+      <c r="BE101">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF101">
+        <v>2.45</v>
+      </c>
+      <c r="BG101">
+        <v>1.16</v>
+      </c>
+      <c r="BH101">
+        <v>4.75</v>
+      </c>
+      <c r="BI101">
+        <v>1.22</v>
+      </c>
+      <c r="BJ101">
+        <v>3.5</v>
+      </c>
+      <c r="BK101">
+        <v>1.56</v>
+      </c>
+      <c r="BL101">
+        <v>2.45</v>
+      </c>
+      <c r="BM101">
+        <v>1.76</v>
+      </c>
+      <c r="BN101">
+        <v>2</v>
+      </c>
+      <c r="BO101">
+        <v>2.2</v>
+      </c>
+      <c r="BP101">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7785911</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45836.45833333334</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s">
+        <v>70</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>2</v>
+      </c>
+      <c r="K102">
+        <v>3</v>
+      </c>
+      <c r="L102">
+        <v>2</v>
+      </c>
+      <c r="M102">
+        <v>4</v>
+      </c>
+      <c r="N102">
+        <v>6</v>
+      </c>
+      <c r="O102" t="s">
+        <v>165</v>
+      </c>
+      <c r="P102" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q102">
+        <v>2.85</v>
+      </c>
+      <c r="R102">
+        <v>2.31</v>
+      </c>
+      <c r="S102">
+        <v>2.9</v>
+      </c>
+      <c r="T102">
+        <v>1.29</v>
+      </c>
+      <c r="U102">
+        <v>3.3</v>
+      </c>
+      <c r="V102">
+        <v>2.2</v>
+      </c>
+      <c r="W102">
+        <v>1.58</v>
+      </c>
+      <c r="X102">
+        <v>5</v>
+      </c>
+      <c r="Y102">
+        <v>1.15</v>
+      </c>
+      <c r="Z102">
+        <v>2.13</v>
+      </c>
+      <c r="AA102">
+        <v>3.65</v>
+      </c>
+      <c r="AB102">
+        <v>2.8</v>
+      </c>
+      <c r="AC102">
+        <v>1</v>
+      </c>
+      <c r="AD102">
+        <v>12</v>
+      </c>
+      <c r="AE102">
+        <v>1.19</v>
+      </c>
+      <c r="AF102">
+        <v>4.33</v>
+      </c>
+      <c r="AG102">
+        <v>1.5</v>
+      </c>
+      <c r="AH102">
+        <v>2.41</v>
+      </c>
+      <c r="AI102">
+        <v>1.53</v>
+      </c>
+      <c r="AJ102">
+        <v>2.43</v>
+      </c>
+      <c r="AK102">
+        <v>1.25</v>
+      </c>
+      <c r="AL102">
+        <v>1.25</v>
+      </c>
+      <c r="AM102">
+        <v>1.5</v>
+      </c>
+      <c r="AN102">
+        <v>2.5</v>
+      </c>
+      <c r="AO102">
+        <v>1.67</v>
+      </c>
+      <c r="AP102">
+        <v>2.14</v>
+      </c>
+      <c r="AQ102">
+        <v>1.86</v>
+      </c>
+      <c r="AR102">
+        <v>1.6</v>
+      </c>
+      <c r="AS102">
+        <v>1.29</v>
+      </c>
+      <c r="AT102">
+        <v>2.89</v>
+      </c>
+      <c r="AU102">
+        <v>4</v>
+      </c>
+      <c r="AV102">
+        <v>8</v>
+      </c>
+      <c r="AW102">
+        <v>9</v>
+      </c>
+      <c r="AX102">
+        <v>7</v>
+      </c>
+      <c r="AY102">
+        <v>13</v>
+      </c>
+      <c r="AZ102">
+        <v>15</v>
+      </c>
+      <c r="BA102">
+        <v>6</v>
+      </c>
+      <c r="BB102">
+        <v>3</v>
+      </c>
+      <c r="BC102">
+        <v>9</v>
+      </c>
+      <c r="BD102">
+        <v>1.95</v>
+      </c>
+      <c r="BE102">
+        <v>6.65</v>
+      </c>
+      <c r="BF102">
+        <v>2.26</v>
+      </c>
+      <c r="BG102">
+        <v>1.16</v>
+      </c>
+      <c r="BH102">
+        <v>4.25</v>
+      </c>
+      <c r="BI102">
+        <v>1.26</v>
+      </c>
+      <c r="BJ102">
+        <v>3.22</v>
+      </c>
+      <c r="BK102">
+        <v>1.69</v>
+      </c>
+      <c r="BL102">
+        <v>2.33</v>
+      </c>
+      <c r="BM102">
+        <v>1.89</v>
+      </c>
+      <c r="BN102">
+        <v>1.85</v>
+      </c>
+      <c r="BO102">
+        <v>2.38</v>
+      </c>
+      <c r="BP102">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7785912</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45836.45833333334</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" t="s">
+        <v>75</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+      <c r="L103">
+        <v>2</v>
+      </c>
+      <c r="M103">
+        <v>2</v>
+      </c>
+      <c r="N103">
+        <v>4</v>
+      </c>
+      <c r="O103" t="s">
+        <v>166</v>
+      </c>
+      <c r="P103" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q103">
+        <v>2.9</v>
+      </c>
+      <c r="R103">
+        <v>2.45</v>
+      </c>
+      <c r="S103">
+        <v>2.94</v>
+      </c>
+      <c r="T103">
+        <v>1.24</v>
+      </c>
+      <c r="U103">
+        <v>3.3</v>
+      </c>
+      <c r="V103">
+        <v>2.38</v>
+      </c>
+      <c r="W103">
+        <v>1.55</v>
+      </c>
+      <c r="X103">
+        <v>4.6</v>
+      </c>
+      <c r="Y103">
+        <v>1.12</v>
+      </c>
+      <c r="Z103">
+        <v>2.34</v>
+      </c>
+      <c r="AA103">
+        <v>3.78</v>
+      </c>
+      <c r="AB103">
+        <v>2.45</v>
+      </c>
+      <c r="AC103">
+        <v>1</v>
+      </c>
+      <c r="AD103">
+        <v>12</v>
+      </c>
+      <c r="AE103">
+        <v>1.17</v>
+      </c>
+      <c r="AF103">
+        <v>4.6</v>
+      </c>
+      <c r="AG103">
+        <v>1.57</v>
+      </c>
+      <c r="AH103">
+        <v>2.15</v>
+      </c>
+      <c r="AI103">
+        <v>1.48</v>
+      </c>
+      <c r="AJ103">
+        <v>2.35</v>
+      </c>
+      <c r="AK103">
+        <v>1.51</v>
+      </c>
+      <c r="AL103">
+        <v>1.27</v>
+      </c>
+      <c r="AM103">
+        <v>1.5</v>
+      </c>
+      <c r="AN103">
+        <v>2.33</v>
+      </c>
+      <c r="AO103">
+        <v>2.33</v>
+      </c>
+      <c r="AP103">
+        <v>2.14</v>
+      </c>
+      <c r="AQ103">
+        <v>2.14</v>
+      </c>
+      <c r="AR103">
+        <v>1.61</v>
+      </c>
+      <c r="AS103">
+        <v>1.69</v>
+      </c>
+      <c r="AT103">
+        <v>3.3</v>
+      </c>
+      <c r="AU103">
+        <v>3</v>
+      </c>
+      <c r="AV103">
+        <v>4</v>
+      </c>
+      <c r="AW103">
+        <v>1</v>
+      </c>
+      <c r="AX103">
+        <v>6</v>
+      </c>
+      <c r="AY103">
+        <v>4</v>
+      </c>
+      <c r="AZ103">
+        <v>10</v>
+      </c>
+      <c r="BA103">
+        <v>7</v>
+      </c>
+      <c r="BB103">
+        <v>8</v>
+      </c>
+      <c r="BC103">
+        <v>15</v>
+      </c>
+      <c r="BD103">
+        <v>1.74</v>
+      </c>
+      <c r="BE103">
+        <v>6.8</v>
+      </c>
+      <c r="BF103">
+        <v>2.79</v>
+      </c>
+      <c r="BG103">
+        <v>1.18</v>
+      </c>
+      <c r="BH103">
+        <v>4.1</v>
+      </c>
+      <c r="BI103">
+        <v>1.34</v>
+      </c>
+      <c r="BJ103">
+        <v>2.98</v>
+      </c>
+      <c r="BK103">
+        <v>1.59</v>
+      </c>
+      <c r="BL103">
+        <v>2.27</v>
+      </c>
+      <c r="BM103">
+        <v>1.97</v>
+      </c>
+      <c r="BN103">
+        <v>1.78</v>
+      </c>
+      <c r="BO103">
+        <v>2.4</v>
+      </c>
+      <c r="BP103">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -20987,19 +20987,19 @@
         <v>5</v>
       </c>
       <c r="AV97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX97">
         <v>4</v>
       </c>
       <c r="AY97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA97">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway First Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,9 @@
     <t>['49', '72']</t>
   </si>
   <si>
+    <t>['35', '60']</t>
+  </si>
+  <si>
     <t>['2', '9']</t>
   </si>
   <si>
@@ -697,13 +700,19 @@
     <t>['16', '32']</t>
   </si>
   <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['45', '58']</t>
   </si>
   <si>
     <t>['31', '12', '53', '68']</t>
   </si>
   <si>
-    <t>['19', '43']</t>
+    <t>['43', '19']</t>
+  </si>
+  <si>
+    <t>['77']</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1321,7 +1330,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1608,7 +1617,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1733,7 +1742,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1939,7 +1948,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2557,7 +2566,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2763,7 +2772,7 @@
         <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2969,7 +2978,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3175,7 +3184,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3587,7 +3596,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3999,7 +4008,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -4411,7 +4420,7 @@
         <v>89</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.83</v>
@@ -4489,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
         <v>0.83</v>
@@ -4617,7 +4626,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -5029,7 +5038,7 @@
         <v>101</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q20">
         <v>2.5</v>
@@ -5235,7 +5244,7 @@
         <v>102</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>2.71</v>
@@ -5441,7 +5450,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>2.62</v>
@@ -5522,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -5647,7 +5656,7 @@
         <v>89</v>
       </c>
       <c r="P23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>3.38</v>
@@ -5853,7 +5862,7 @@
         <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6265,7 +6274,7 @@
         <v>89</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>4.53</v>
@@ -6343,7 +6352,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>2.14</v>
@@ -6471,7 +6480,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -6883,7 +6892,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q29">
         <v>3.48</v>
@@ -7089,7 +7098,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>4.68</v>
@@ -7501,7 +7510,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q32">
         <v>3.9</v>
@@ -7707,7 +7716,7 @@
         <v>89</v>
       </c>
       <c r="P33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -8119,7 +8128,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
@@ -8325,7 +8334,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q36">
         <v>3.45</v>
@@ -8737,7 +8746,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8818,7 +8827,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR38">
         <v>1.67</v>
@@ -8943,7 +8952,7 @@
         <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -9355,7 +9364,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q41">
         <v>1.93</v>
@@ -9433,7 +9442,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.14</v>
@@ -9973,7 +9982,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q44">
         <v>3.2</v>
@@ -10179,7 +10188,7 @@
         <v>118</v>
       </c>
       <c r="P45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q45">
         <v>3.5</v>
@@ -10385,7 +10394,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>2.27</v>
@@ -10591,7 +10600,7 @@
         <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q47">
         <v>7.37</v>
@@ -10797,7 +10806,7 @@
         <v>120</v>
       </c>
       <c r="P48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q48">
         <v>3.07</v>
@@ -11003,7 +11012,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>2.72</v>
@@ -11493,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
         <v>0.57</v>
@@ -11908,7 +11917,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR53">
         <v>2.04</v>
@@ -12239,7 +12248,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>2.59</v>
@@ -12857,7 +12866,7 @@
         <v>98</v>
       </c>
       <c r="P58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -13269,7 +13278,7 @@
         <v>89</v>
       </c>
       <c r="P60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13475,7 +13484,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>2.13</v>
@@ -13681,7 +13690,7 @@
         <v>132</v>
       </c>
       <c r="P62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q62">
         <v>2.7</v>
@@ -13887,7 +13896,7 @@
         <v>89</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>2.48</v>
@@ -14093,7 +14102,7 @@
         <v>133</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>3.75</v>
@@ -14299,7 +14308,7 @@
         <v>134</v>
       </c>
       <c r="P65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>1.99</v>
@@ -14377,7 +14386,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ65">
         <v>0.71</v>
@@ -14711,7 +14720,7 @@
         <v>136</v>
       </c>
       <c r="P67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>3.11</v>
@@ -14917,7 +14926,7 @@
         <v>137</v>
       </c>
       <c r="P68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>3.55</v>
@@ -15204,7 +15213,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ69">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR69">
         <v>1.65</v>
@@ -15329,7 +15338,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15741,7 +15750,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15947,7 +15956,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>2.05</v>
@@ -16153,7 +16162,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>5.5</v>
@@ -16359,7 +16368,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>2.35</v>
@@ -16565,7 +16574,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -16771,7 +16780,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q77">
         <v>3.97</v>
@@ -16977,7 +16986,7 @@
         <v>110</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>3.84</v>
@@ -17183,7 +17192,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>2.15</v>
@@ -17389,7 +17398,7 @@
         <v>147</v>
       </c>
       <c r="P80" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q80">
         <v>2.1</v>
@@ -17595,7 +17604,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>1.6</v>
@@ -17801,7 +17810,7 @@
         <v>149</v>
       </c>
       <c r="P82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>2.11</v>
@@ -18419,7 +18428,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>4.1</v>
@@ -18625,7 +18634,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q86">
         <v>1.57</v>
@@ -18706,7 +18715,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ86">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR86">
         <v>2.06</v>
@@ -19037,7 +19046,7 @@
         <v>154</v>
       </c>
       <c r="P88" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19115,7 +19124,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
         <v>0.67</v>
@@ -19449,7 +19458,7 @@
         <v>156</v>
       </c>
       <c r="P90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>3.96</v>
@@ -19861,7 +19870,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>4.5</v>
@@ -20273,7 +20282,7 @@
         <v>158</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>2.5</v>
@@ -20479,7 +20488,7 @@
         <v>159</v>
       </c>
       <c r="P95" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20685,7 +20694,7 @@
         <v>160</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q96">
         <v>3.15</v>
@@ -20987,19 +20996,19 @@
         <v>5</v>
       </c>
       <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
         <v>3</v>
-      </c>
-      <c r="AW97">
-        <v>2</v>
       </c>
       <c r="AX97">
         <v>4</v>
       </c>
       <c r="AY97">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA97">
         <v>3</v>
@@ -21097,7 +21106,7 @@
         <v>162</v>
       </c>
       <c r="P98" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q98">
         <v>1.77</v>
@@ -21303,7 +21312,7 @@
         <v>163</v>
       </c>
       <c r="P99" t="s">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="Q99">
         <v>4.4</v>
@@ -21715,7 +21724,7 @@
         <v>164</v>
       </c>
       <c r="P101" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q101">
         <v>2.15</v>
@@ -21921,7 +21930,7 @@
         <v>165</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q102">
         <v>2.85</v>
@@ -22127,7 +22136,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q103">
         <v>2.9</v>
@@ -22284,6 +22293,212 @@
       </c>
       <c r="BP103">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7785910</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
+        <v>85</v>
+      </c>
+      <c r="H104" t="s">
+        <v>78</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>167</v>
+      </c>
+      <c r="P104" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q104">
+        <v>2.79</v>
+      </c>
+      <c r="R104">
+        <v>2.25</v>
+      </c>
+      <c r="S104">
+        <v>3.44</v>
+      </c>
+      <c r="T104">
+        <v>1.25</v>
+      </c>
+      <c r="U104">
+        <v>3.2</v>
+      </c>
+      <c r="V104">
+        <v>2.4</v>
+      </c>
+      <c r="W104">
+        <v>1.53</v>
+      </c>
+      <c r="X104">
+        <v>5.8</v>
+      </c>
+      <c r="Y104">
+        <v>1.13</v>
+      </c>
+      <c r="Z104">
+        <v>2.25</v>
+      </c>
+      <c r="AA104">
+        <v>3.5</v>
+      </c>
+      <c r="AB104">
+        <v>2.7</v>
+      </c>
+      <c r="AC104">
+        <v>1.03</v>
+      </c>
+      <c r="AD104">
+        <v>11</v>
+      </c>
+      <c r="AE104">
+        <v>1.17</v>
+      </c>
+      <c r="AF104">
+        <v>4.3</v>
+      </c>
+      <c r="AG104">
+        <v>1.55</v>
+      </c>
+      <c r="AH104">
+        <v>2.25</v>
+      </c>
+      <c r="AI104">
+        <v>1.53</v>
+      </c>
+      <c r="AJ104">
+        <v>2.4</v>
+      </c>
+      <c r="AK104">
+        <v>1.29</v>
+      </c>
+      <c r="AL104">
+        <v>1.26</v>
+      </c>
+      <c r="AM104">
+        <v>1.62</v>
+      </c>
+      <c r="AN104">
+        <v>0.67</v>
+      </c>
+      <c r="AO104">
+        <v>0.83</v>
+      </c>
+      <c r="AP104">
+        <v>1</v>
+      </c>
+      <c r="AQ104">
+        <v>0.71</v>
+      </c>
+      <c r="AR104">
+        <v>1.47</v>
+      </c>
+      <c r="AS104">
+        <v>1.64</v>
+      </c>
+      <c r="AT104">
+        <v>3.11</v>
+      </c>
+      <c r="AU104">
+        <v>5</v>
+      </c>
+      <c r="AV104">
+        <v>3</v>
+      </c>
+      <c r="AW104">
+        <v>4</v>
+      </c>
+      <c r="AX104">
+        <v>4</v>
+      </c>
+      <c r="AY104">
+        <v>9</v>
+      </c>
+      <c r="AZ104">
+        <v>7</v>
+      </c>
+      <c r="BA104">
+        <v>2</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>6</v>
+      </c>
+      <c r="BD104">
+        <v>1.86</v>
+      </c>
+      <c r="BE104">
+        <v>7.7</v>
+      </c>
+      <c r="BF104">
+        <v>2.35</v>
+      </c>
+      <c r="BG104">
+        <v>1.19</v>
+      </c>
+      <c r="BH104">
+        <v>4.35</v>
+      </c>
+      <c r="BI104">
+        <v>1.25</v>
+      </c>
+      <c r="BJ104">
+        <v>2.95</v>
+      </c>
+      <c r="BK104">
+        <v>1.54</v>
+      </c>
+      <c r="BL104">
+        <v>2.32</v>
+      </c>
+      <c r="BM104">
+        <v>1.87</v>
+      </c>
+      <c r="BN104">
+        <v>1.87</v>
+      </c>
+      <c r="BO104">
+        <v>2.34</v>
+      </c>
+      <c r="BP104">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>
